--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="O2" t="n">
         <v>1.24</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
         <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Q4" t="n">
         <v>1.22</v>
@@ -1413,7 +1413,7 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
         <v>1.18</v>
@@ -1658,7 +1658,7 @@
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>1.29</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O7" t="n">
         <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Q7" t="n">
         <v>1.2</v>
@@ -2178,7 +2178,7 @@
         <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q8" t="n">
         <v>1.2</v>
@@ -2420,7 +2420,7 @@
         <v>1.07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="O2" t="n">
         <v>1.24</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="O4" t="n">
         <v>1.22</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>1.29</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
         <v>1.22</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q5" t="n">
         <v>1.18</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
         <v>1.07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FK Tukums 2000</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>2.68</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>2.42</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="J2" t="n">
-        <v>1.06</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.09</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07</v>
+        <v>2.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.07</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
-        <v>1.36</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>FK Tukums 2000</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hammarby TFF</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1377,218 +1377,218 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -1610,22 +1610,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>FBK Karlstad</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>Hammarby TFF</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -1864,22 +1864,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trelleborgs</t>
+          <t>AFC Eskilstuna</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -2113,34 +2113,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Kristianstads</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>Trelleborgs</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
         <v>1.04</v>
       </c>
-      <c r="G7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.38</v>
-      </c>
       <c r="K7" t="n">
         <v>1000</v>
       </c>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O7" t="n">
         <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Q7" t="n">
         <v>1.2</v>
@@ -2166,7 +2166,7 @@
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2178,7 +2178,7 @@
         <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -2372,28 +2372,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hassleholms IF</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="O8" t="n">
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="Q8" t="n">
         <v>1.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2432,7 +2432,7 @@
         <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,261 +2604,515 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Hassleholms IF</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Tvaakers</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:37:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Novorizontino</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-24 07:28:39</t>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -863,10 +863,10 @@
         <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="I2" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J2" t="n">
         <v>3.85</v>
@@ -887,7 +887,7 @@
         <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q2" t="n">
         <v>1.55</v>
@@ -929,10 +929,10 @@
         <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF2" t="n">
         <v>26</v>
@@ -962,19 +962,19 @@
         <v>19</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT2" t="n">
         <v>14</v>
@@ -986,10 +986,10 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX2" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.2</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -998,19 +998,19 @@
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD2" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
         <v>12.5</v>
@@ -1028,59 +1028,59 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>85</v>
       </c>
       <c r="BM2" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO2" t="n">
         <v>5</v>
       </c>
       <c r="BP2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>30</v>
       </c>
       <c r="BS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV2" t="n">
         <v>19</v>
       </c>
-      <c r="BT2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>28</v>
       </c>
       <c r="BY2" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="CA2" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
         <v>1.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>2.38</v>
       </c>
       <c r="I2" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="J2" t="n">
         <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
@@ -887,25 +887,25 @@
         <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W2" t="n">
         <v>1.5</v>
@@ -935,7 +935,7 @@
         <v>27</v>
       </c>
       <c r="AF2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG2" t="n">
         <v>15.5</v>
@@ -947,7 +947,7 @@
         <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK2" t="n">
         <v>32</v>
@@ -959,64 +959,64 @@
         <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO2" t="n">
         <v>15.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT2" t="n">
         <v>4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>14</v>
       </c>
       <c r="AU2" t="n">
         <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AW2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA2" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BB2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD2" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BE2" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="n">
         <v>4.9</v>
@@ -1043,7 +1043,7 @@
         <v>5</v>
       </c>
       <c r="BP2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BQ2" t="n">
         <v>1.01</v>
@@ -1058,7 +1058,7 @@
         <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
         <v>19</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>1.98</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="J3" t="n">
-        <v>1.06</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36</v>
+        <v>2.66</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -1365,220 +1365,220 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>950</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M4" t="n">
         <v>1.04</v>
       </c>
-      <c r="G4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -1619,160 +1619,160 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="J5" t="n">
         <v>1.09</v>
       </c>
-      <c r="G5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.04</v>
-      </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.33</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>1.32</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1781,13 +1781,13 @@
         <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI5" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
@@ -1799,50 +1799,50 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS5" t="n">
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW5" t="n">
         <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY5" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA5" t="n">
         <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -1873,160 +1873,160 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.09</v>
+        <v>2.36</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>2.58</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="S6" t="n">
-        <v>1.18</v>
+        <v>2.28</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
         <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2035,13 +2035,13 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI6" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK6" t="n">
         <v>1.01</v>
@@ -2053,50 +2053,50 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO6" t="n">
         <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS6" t="n">
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW6" t="n">
         <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY6" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA6" t="n">
         <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.09</v>
+        <v>4.8</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.09</v>
+        <v>1.62</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>1.85</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>1.29</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.2</v>
+        <v>1.59</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -2381,160 +2381,160 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>2.86</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>2.06</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.33</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>1.21</v>
+        <v>2.22</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2543,13 +2543,13 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI8" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK8" t="n">
         <v>1.01</v>
@@ -2561,7 +2561,7 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO8" t="n">
         <v>1.01</v>
@@ -2579,13 +2579,13 @@
         <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU8" t="n">
         <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -2635,237 +2635,237 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.09</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="H9" t="n">
-        <v>1.09</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="O9" t="n">
         <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
-        <v>1.07</v>
+        <v>1.51</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.89</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,244 +2875,752 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="P10" t="n">
         <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Icelandic 3 Deild</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Augnablik</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>KH Hlidarendi</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:53:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.19</v>
@@ -893,16 +893,16 @@
         <v>1.58</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
         <v>1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="V2" t="n">
         <v>1.64</v>
@@ -959,7 +959,7 @@
         <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO2" t="n">
         <v>15.5</v>
@@ -968,10 +968,10 @@
         <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
         <v>4.5</v>
@@ -1025,10 +1025,10 @@
         <v>3.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL2" t="n">
         <v>85</v>
@@ -1040,7 +1040,7 @@
         <v>6.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BP2" t="n">
         <v>23</v>
@@ -1055,10 +1055,10 @@
         <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
         <v>19</v>
@@ -1076,11 +1076,11 @@
         <v>17</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>2.38</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>4.3</v>
@@ -1150,7 +1150,7 @@
         <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
         <v>1.63</v>
@@ -1165,22 +1165,22 @@
         <v>1.29</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>12.5</v>
@@ -1189,13 +1189,13 @@
         <v>25</v>
       </c>
       <c r="AF3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
         <v>38</v>
@@ -1219,58 +1219,58 @@
         <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AX3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD3" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="BE3" t="n">
         <v>4.7</v>
       </c>
-      <c r="AU3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6</v>
-      </c>
       <c r="BF3" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="BH3" t="n">
         <v>4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="I4" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.27</v>
@@ -1395,25 +1395,25 @@
         <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q4" t="n">
         <v>1.66</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
         <v>2.66</v>
       </c>
       <c r="T4" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
         <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="W4" t="n">
         <v>1.16</v>
@@ -1422,25 +1422,25 @@
         <v>25</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AB4" t="n">
         <v>29</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AF4" t="n">
         <v>65</v>
@@ -1470,43 +1470,43 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
         <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
         <v>1.01</v>
@@ -1524,19 +1524,19 @@
         <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
         <v>4.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,40 +1545,40 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="BO4" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>60</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>60</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="BV4" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>28</v>
       </c>
       <c r="BY4" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,239 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hammarby TFF</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.98</v>
+        <v>1.84</v>
       </c>
       <c r="G5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K5" t="n">
         <v>4.4</v>
       </c>
-      <c r="H5" t="n">
+      <c r="L5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.96</v>
       </c>
-      <c r="I5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="X5" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="n">
         <v>4.6</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X5" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BI5" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM5" t="n">
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BS5" t="n">
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.5</v>
+        <v>38</v>
       </c>
       <c r="BW5" t="n">
         <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="BY5" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -1864,34 +1864,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>FBK Karlstad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>Hammarby TFF</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="H6" t="n">
-        <v>2.58</v>
+        <v>1.97</v>
       </c>
       <c r="I6" t="n">
-        <v>3.25</v>
+        <v>2.24</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
@@ -1900,203 +1900,203 @@
         <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.56</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.52</v>
-      </c>
       <c r="U6" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
         <v>28</v>
       </c>
       <c r="Y6" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AB6" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK6" t="n">
         <v>44</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>26</v>
-      </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN6" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="AO6" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH6" t="n">
         <v>4.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BY6" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>17.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -2118,239 +2118,239 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trelleborgs</t>
+          <t>AFC Eskilstuna</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.8</v>
+        <v>2.36</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.62</v>
+        <v>2.58</v>
       </c>
       <c r="I7" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="V7" t="n">
-        <v>2.18</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="X7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD7" t="n">
         <v>14</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AE7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF7" t="n">
         <v>21</v>
       </c>
-      <c r="AB7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>55</v>
-      </c>
       <c r="AG7" t="n">
-        <v>26</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
         <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="AK7" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AN7" t="n">
-        <v>80</v>
+        <v>16.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU7" t="n">
         <v>3.9</v>
       </c>
-      <c r="AY7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>44</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BV7" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA7" t="n">
         <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Kristianstads</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>Trelleborgs</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.86</v>
+        <v>4.3</v>
       </c>
       <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AX8" t="n">
         <v>3.9</v>
       </c>
-      <c r="H8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="AY8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG8" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="n">
+      <c r="BH8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>44</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT8" t="n">
         <v>4.7</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X8" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT8" t="n">
+      <c r="BU8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>18</v>
+      </c>
+      <c r="CA8" t="n">
         <v>6</v>
       </c>
-      <c r="BU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hassleholms IF</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.12</v>
+        <v>2.74</v>
       </c>
       <c r="H9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X9" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI9" t="n">
         <v>3.3</v>
       </c>
-      <c r="I9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X9" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO9" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>6.4</v>
       </c>
-      <c r="BN9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BR9" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="BV9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BX9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,498 +3129,3292 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Hassleholms IF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="O11" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>1.08</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Galway Utd</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X12" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Wexford F.C</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Kerry FC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Longford</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Waterford</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Derry City</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Drogheda</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bohemians</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>St Patricks</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Icelandic 3 Deild</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>KV Vesturbaejar</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Vidir Gardur</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Icelandic 3 Deild</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Augnablik</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>KH Hlidarendi</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Novorizontino</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>2026-06-24 13:53:57</t>
+      <c r="Q23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,7 +863,7 @@
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I2" t="n">
         <v>2.56</v>
@@ -872,13 +872,13 @@
         <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
         <v>5.4</v>
@@ -941,7 +941,7 @@
         <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI2" t="n">
         <v>34</v>
@@ -998,10 +998,10 @@
         <v>11.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
@@ -1010,7 +1010,7 @@
         <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.24</v>
@@ -1183,7 +1183,7 @@
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
@@ -1219,22 +1219,22 @@
         <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT3" t="n">
         <v>4</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV3" t="n">
         <v>3.6</v>
@@ -1246,31 +1246,31 @@
         <v>4.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AZ3" t="n">
         <v>4</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD3" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BE3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF3" t="n">
         <v>4.5</v>
       </c>
-      <c r="BD3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BH3" t="n">
         <v>4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
         <v>2.66</v>
       </c>
       <c r="T4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
         <v>2.06</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="G5" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
         <v>3.7</v>
@@ -1631,49 +1631,49 @@
         <v>4.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
         <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.68</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.67</v>
-      </c>
       <c r="U5" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
         <v>19</v>
@@ -1685,43 +1685,43 @@
         <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
         <v>60</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
         <v>38</v>
       </c>
       <c r="AM5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
         <v>55</v>
@@ -1781,10 +1781,10 @@
         <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ5" t="n">
         <v>11</v>
@@ -1793,7 +1793,7 @@
         <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BM5" t="n">
         <v>1.01</v>
@@ -1805,19 +1805,19 @@
         <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BS5" t="n">
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
@@ -1829,7 +1829,7 @@
         <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.19</v>
@@ -2172,7 +2172,7 @@
         <v>1.52</v>
       </c>
       <c r="U7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
         <v>1.44</v>
@@ -2187,7 +2187,7 @@
         <v>17.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
         <v>48</v>
@@ -2220,7 +2220,7 @@
         <v>42</v>
       </c>
       <c r="AK7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
         <v>34</v>
@@ -2235,58 +2235,58 @@
         <v>19.5</v>
       </c>
       <c r="AP7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR7" t="n">
         <v>5.3</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AS7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT7" t="n">
         <v>4.8</v>
       </c>
-      <c r="AR7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="AU7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB7" t="n">
         <v>5.8</v>
       </c>
-      <c r="AT7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BC7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE7" t="n">
         <v>6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH7" t="n">
         <v>4.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -2405,22 +2405,22 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="R8" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
         <v>1.71</v>
@@ -2429,7 +2429,7 @@
         <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="W8" t="n">
         <v>1.17</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I9" t="n">
         <v>2.96</v>
@@ -2686,7 +2686,7 @@
         <v>1.51</v>
       </c>
       <c r="W9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X9" t="n">
         <v>24</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
         <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R11" t="n">
         <v>1.51</v>
@@ -3236,7 +3236,7 @@
         <v>26</v>
       </c>
       <c r="AK11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
         <v>32</v>
@@ -3251,28 +3251,28 @@
         <v>38</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AV11" t="n">
         <v>4</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
         <v>3.9</v>
@@ -3293,16 +3293,16 @@
         <v>4.1</v>
       </c>
       <c r="BD11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG11" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.5</v>
       </c>
       <c r="BH11" t="n">
         <v>4.6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
         <v>4.4</v>
@@ -3433,13 +3433,13 @@
         <v>1.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="U12" t="n">
         <v>1.8</v>
@@ -3517,43 +3517,43 @@
         <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="AW12" t="n">
         <v>4.9</v>
       </c>
       <c r="AX12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AY12" t="n">
-        <v>8</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
         <v>4.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC12" t="n">
         <v>12</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.5</v>
+        <v>27</v>
       </c>
       <c r="BE12" t="n">
         <v>4.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG12" t="n">
         <v>4.9</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,55 +3642,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>1.7</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="R13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3699,118 +3699,118 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,175 +3896,175 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G14" t="n">
         <v>1.63</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.04</v>
-      </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="K14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.24</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>1.96</v>
+        <v>2.58</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -4150,67 +4150,67 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2.82</v>
       </c>
       <c r="H15" t="n">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -4404,67 +4404,67 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="G16" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="H16" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
-        <v>2.08</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>1.24</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V16" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -4658,67 +4658,67 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>1.24</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,31 +4912,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G18" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="I18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -4945,22 +4945,22 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.08</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>1.44</v>
+        <v>2.66</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,127 +5166,127 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
         <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>1.92</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P19" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V19" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR19" t="n">
         <v>1.01</v>
@@ -5295,34 +5295,34 @@
         <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW19" t="n">
         <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
         <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD19" t="n">
         <v>1.01</v>
@@ -5331,61 +5331,61 @@
         <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG19" t="n">
         <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK19" t="n">
         <v>1.01</v>
       </c>
       <c r="BL19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM19" t="n">
         <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ19" t="n">
         <v>1.01</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS19" t="n">
         <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU19" t="n">
         <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW19" t="n">
         <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>3.1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I20" t="n">
         <v>3.05</v>
@@ -5447,202 +5447,202 @@
         <v>3.7</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P20" t="n">
         <v>1.79</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -5707,22 +5707,22 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="O21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="S21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,28 +5928,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,28 +5961,28 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="O22" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="P22" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
@@ -6153,21 +6153,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,234 +6177,234 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P23" t="n">
         <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,1531 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Leiknir R</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IR Reykjavik</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:13:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Fylkir</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HK Kopavogur</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:13:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Icelandic 2 Deild</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Throttur Vogar</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Fjolnir</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:13:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Icelandic 2 Deild</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Selfoss</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Haukar</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:13:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Icelandic 3 Deild</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>KV Vesturbaejar</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Vidir Gardur</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:13:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB29"/>
+  <dimension ref="A1:CB30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,7 +878,7 @@
         <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
         <v>5.4</v>
@@ -989,7 +989,7 @@
         <v>17.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>17.5</v>
+        <v>4.3</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
         <v>10</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BI2" t="n">
         <v>3.5</v>
@@ -1031,10 +1031,10 @@
         <v>6.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
@@ -1043,19 +1043,19 @@
         <v>5.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU2" t="n">
         <v>5</v>
@@ -1064,13 +1064,13 @@
         <v>19</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX2" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>17</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
@@ -1219,22 +1219,22 @@
         <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT3" t="n">
         <v>4</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AV3" t="n">
         <v>3.6</v>
@@ -1246,31 +1246,31 @@
         <v>4.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AZ3" t="n">
         <v>4</v>
       </c>
       <c r="BA3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC3" t="n">
+      <c r="BD3" t="n">
         <v>4.6</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BE3" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BH3" t="n">
         <v>4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -1473,58 +1473,58 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BH4" t="n">
         <v>4.7</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
@@ -1643,16 +1643,16 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
         <v>1.42</v>
@@ -1664,10 +1664,10 @@
         <v>1.68</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W5" t="n">
         <v>1.92</v>
@@ -1676,7 +1676,7 @@
         <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
         <v>40</v>
@@ -1685,13 +1685,13 @@
         <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
         <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
         <v>60</v>
@@ -1703,7 +1703,7 @@
         <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
         <v>65</v>
@@ -1712,7 +1712,7 @@
         <v>28</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
         <v>38</v>
@@ -1727,58 +1727,58 @@
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
         <v>4.4</v>
@@ -1787,7 +1787,7 @@
         <v>2.96</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
@@ -1817,13 +1817,13 @@
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>1.62</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -2414,13 +2414,13 @@
         <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="R8" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="T8" t="n">
         <v>1.71</v>
@@ -2429,7 +2429,7 @@
         <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="W8" t="n">
         <v>1.17</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
         <v>1.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
         <v>1.11</v>
@@ -3508,7 +3508,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="AR12" t="n">
         <v>4.8</v>
@@ -3517,7 +3517,7 @@
         <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU12" t="n">
         <v>9.4</v>
@@ -3529,31 +3529,31 @@
         <v>4.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
         <v>4.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
         <v>12</v>
       </c>
       <c r="BD12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE12" t="n">
         <v>4.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG12" t="n">
         <v>4.9</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.9</v>
@@ -3672,7 +3672,7 @@
         <v>1.37</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
         <v>3.65</v>
@@ -3687,130 +3687,130 @@
         <v>1.91</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W13" t="n">
         <v>2.42</v>
       </c>
       <c r="X13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y13" t="n">
         <v>21</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>29</v>
       </c>
       <c r="Z13" t="n">
         <v>75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK13" t="n">
         <v>19.5</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>22</v>
       </c>
       <c r="AL13" t="n">
         <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN13" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.6</v>
+        <v>12.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.7</v>
+        <v>17</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.86</v>
+        <v>7.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.98</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.32</v>
+        <v>6.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.42</v>
+        <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.98</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY13" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.72</v>
+        <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.98</v>
+        <v>7.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.58</v>
+        <v>13.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.82</v>
+        <v>6.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.98</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.98</v>
+        <v>7.8</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -3908,19 +3908,19 @@
         <v>1.58</v>
       </c>
       <c r="G14" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="I14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
         <v>4.7</v>
       </c>
       <c r="K14" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.21</v>
@@ -3929,7 +3929,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>2.74</v>
       </c>
       <c r="O14" t="n">
         <v>1.13</v>
@@ -3938,7 +3938,7 @@
         <v>2.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R14" t="n">
         <v>1.54</v>
@@ -3947,7 +3947,7 @@
         <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U14" t="n">
         <v>2.12</v>
@@ -3956,7 +3956,7 @@
         <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X14" t="n">
         <v>40</v>
@@ -4070,55 +4070,55 @@
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -4162,10 +4162,10 @@
         <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="H15" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I15" t="n">
         <v>4.2</v>
@@ -4177,7 +4177,7 @@
         <v>5.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
@@ -4192,7 +4192,7 @@
         <v>1.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R15" t="n">
         <v>1.21</v>
@@ -4210,7 +4210,7 @@
         <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4324,55 +4324,55 @@
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -4404,127 +4404,127 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="G16" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="H16" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="O16" t="n">
         <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V16" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR16" t="n">
         <v>1.01</v>
@@ -4533,34 +4533,34 @@
         <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW16" t="n">
         <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
         <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD16" t="n">
         <v>1.01</v>
@@ -4569,64 +4569,64 @@
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG16" t="n">
         <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -4658,229 +4658,229 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="G17" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I17" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
         <v>1.29</v>
       </c>
       <c r="P17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW17" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -4912,67 +4912,67 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.36</v>
+        <v>1.96</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -5166,127 +5166,127 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="G19" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>3.85</v>
+        <v>2.92</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="T19" t="n">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="X19" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
         <v>1.01</v>
@@ -5295,34 +5295,34 @@
         <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
         <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
         <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
         <v>1.01</v>
@@ -5331,61 +5331,61 @@
         <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
         <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
         <v>1.01</v>
       </c>
       <c r="BL19" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
         <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
         <v>1.01</v>
       </c>
       <c r="BR19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
         <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
         <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
         <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>3.1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="I20" t="n">
         <v>3.05</v>
@@ -5471,10 +5471,10 @@
         <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V20" t="n">
         <v>1.48</v>
@@ -5594,55 +5594,55 @@
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,28 +5674,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5707,28 +5707,28 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="O21" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="P21" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
@@ -5899,14 +5899,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,22 +5961,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P22" t="n">
         <v>1.26</v>
       </c>
-      <c r="O22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Q22" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,28 +6215,28 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="P23" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="S23" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -6457,7 +6457,7 @@
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -6469,22 +6469,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="O24" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="R24" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -6610,55 +6610,55 @@
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
         <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,28 +6690,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -6723,22 +6723,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="P25" t="n">
         <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -6864,65 +6864,65 @@
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -6977,22 +6977,22 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O26" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="R26" t="n">
         <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7198,22 +7198,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
@@ -7231,22 +7231,22 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="P27" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="R27" t="n">
         <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -7485,19 +7485,19 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="S28" t="n">
         <v>1.05</v>
@@ -7684,261 +7684,515 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HFX Wanderers</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:24:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Novorizontino</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB29" t="inlineStr">
-        <is>
-          <t>2026-06-24 18:13:46</t>
+      <c r="F30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB30"/>
+  <dimension ref="A1:CB31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,10 +860,10 @@
         <v>2.78</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I2" t="n">
         <v>2.56</v>
@@ -887,19 +887,19 @@
         <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="U2" t="n">
         <v>2.62</v>
@@ -908,7 +908,7 @@
         <v>1.64</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
         <v>28</v>
@@ -968,37 +968,37 @@
         <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS2" t="n">
         <v>4.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AU2" t="n">
         <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
         <v>17.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
         <v>11.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
         <v>4.7</v>
@@ -1007,7 +1007,7 @@
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE2" t="n">
         <v>4.8</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
@@ -1046,13 +1046,13 @@
         <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
@@ -1061,7 +1061,7 @@
         <v>5</v>
       </c>
       <c r="BV2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BW2" t="n">
         <v>6.2</v>
@@ -1070,7 +1070,7 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BZ2" t="n">
         <v>17</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -1114,79 +1114,79 @@
         <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I3" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="J3" t="n">
         <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
         <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V3" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="W3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
         <v>30</v>
       </c>
       <c r="AB3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
         <v>34</v>
@@ -1195,10 +1195,10 @@
         <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ3" t="n">
         <v>80</v>
@@ -1216,67 +1216,67 @@
         <v>40</v>
       </c>
       <c r="AO3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AW3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>4</v>
-      </c>
       <c r="BI3" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.6</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BN3" t="n">
         <v>7.6</v>
@@ -1297,44 +1297,44 @@
         <v>4</v>
       </c>
       <c r="BP3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>7</v>
       </c>
       <c r="BT3" t="n">
         <v>5.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>5.1</v>
       </c>
       <c r="G4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
         <v>1.52</v>
@@ -1377,7 +1377,7 @@
         <v>1.64</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
         <v>5.7</v>
@@ -1416,7 +1416,7 @@
         <v>2.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
         <v>25</v>
@@ -1482,7 +1482,7 @@
         <v>3.35</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="AT4" t="n">
         <v>3</v>
@@ -1494,7 +1494,7 @@
         <v>3.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="AX4" t="n">
         <v>3.2</v>
@@ -1524,7 +1524,7 @@
         <v>3.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BH4" t="n">
         <v>4.7</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,226 +1610,226 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>Santiago City</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Provincial Ovalle FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="S5" t="n">
-        <v>2.72</v>
+        <v>1.24</v>
       </c>
       <c r="T5" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
         <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
         <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
         <v>1.01</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,239 +1864,239 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hammarby TFF</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25</v>
+        <v>1.64</v>
       </c>
       <c r="G6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX6" t="n">
         <v>3.95</v>
       </c>
-      <c r="H6" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X6" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5</v>
-      </c>
       <c r="AY6" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="AZ6" t="n">
         <v>4.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>130</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BO6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BS6" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -2118,184 +2118,184 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>FBK Karlstad</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>Hammarby TFF</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.36</v>
+        <v>3.35</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.58</v>
+        <v>1.95</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>2.24</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
         <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL7" t="n">
         <v>48</v>
       </c>
-      <c r="AB7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>34</v>
-      </c>
       <c r="AM7" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN7" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AU7" t="n">
         <v>4.1</v>
       </c>
       <c r="AV7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG7" t="n">
         <v>4.5</v>
       </c>
-      <c r="AW7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5</v>
-      </c>
       <c r="BH7" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BK7" t="n">
         <v>4.6</v>
@@ -2304,53 +2304,53 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY7" t="n">
         <v>6.6</v>
       </c>
-      <c r="BU7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>7</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="CA7" t="n">
         <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -2372,246 +2372,246 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trelleborgs</t>
+          <t>AFC Eskilstuna</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.3</v>
+        <v>2.36</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>2.92</v>
       </c>
       <c r="H8" t="n">
-        <v>1.62</v>
+        <v>2.58</v>
       </c>
       <c r="I8" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.7</v>
-      </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>2.18</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z8" t="n">
         <v>24</v>
       </c>
-      <c r="Y8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD8" t="n">
         <v>14</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AE8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF8" t="n">
         <v>21</v>
       </c>
-      <c r="AB8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>55</v>
-      </c>
       <c r="AG8" t="n">
-        <v>26</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AL8" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AN8" t="n">
-        <v>80</v>
+        <v>16.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AX8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU8" t="n">
         <v>3.9</v>
       </c>
-      <c r="AY8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>44</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BV8" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA8" t="n">
         <v>6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IK Brage</t>
+          <t>Kristianstads</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Trelleborgs</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.78</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>2.66</v>
+        <v>1.62</v>
       </c>
       <c r="I9" t="n">
-        <v>2.96</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="T9" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="U9" t="n">
-        <v>2.66</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.51</v>
+        <v>2.18</v>
       </c>
       <c r="W9" t="n">
-        <v>1.56</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>24</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AH9" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>970</v>
+        <v>80</v>
       </c>
       <c r="AO9" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA9" t="n">
         <v>3.8</v>
       </c>
-      <c r="AV9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BB9" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="BF9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BG9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK9" t="n">
         <v>4.9</v>
       </c>
-      <c r="BH9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BO9" t="n">
         <v>4.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU9" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY9" t="n">
         <v>6.8</v>
       </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,244 +2875,244 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>3.9</v>
+        <v>2.78</v>
       </c>
       <c r="H10" t="n">
-        <v>2.06</v>
+        <v>2.66</v>
       </c>
       <c r="I10" t="n">
-        <v>2.64</v>
+        <v>2.96</v>
       </c>
       <c r="J10" t="n">
-        <v>2.74</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
         <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="T10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.51</v>
       </c>
-      <c r="U10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.6</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA10" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AB10" t="n">
         <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF10" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL10" t="n">
         <v>36</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>44</v>
       </c>
       <c r="AM10" t="n">
         <v>70</v>
       </c>
       <c r="AN10" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AO10" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="AU10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI10" t="n">
         <v>3.3</v>
       </c>
-      <c r="AV10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BH10" t="n">
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
         <v>4.7</v>
       </c>
-      <c r="BI10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>4</v>
-      </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>6.4</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>7.4</v>
       </c>
-      <c r="BO10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hassleholms IF</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>2.84</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18</v>
+        <v>3.6</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>2.48</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
         <v>4.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="R11" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="U11" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="W11" t="n">
-        <v>1.84</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Y11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z11" t="n">
         <v>23</v>
       </c>
-      <c r="Z11" t="n">
-        <v>38</v>
-      </c>
       <c r="AA11" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AB11" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AC11" t="n">
         <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="AF11" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AJ11" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN11" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AO11" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT11" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV11" t="n">
         <v>3.75</v>
       </c>
-      <c r="AU11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY11" t="n">
         <v>4</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.6</v>
       </c>
       <c r="AZ11" t="n">
         <v>4</v>
       </c>
       <c r="BA11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC11" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BD11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF11" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE11" t="n">
+      <c r="BG11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
         <v>4.7</v>
       </c>
-      <c r="BF11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BX11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BZ11" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,129 +3383,129 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Hassleholms IF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="G12" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="H12" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
         <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="T12" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>2.88</v>
+        <v>1.89</v>
       </c>
       <c r="X12" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y12" t="n">
         <v>22</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL12" t="n">
         <v>32</v>
       </c>
-      <c r="Z12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>300</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>42</v>
-      </c>
       <c r="AM12" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="AP12" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>4.4</v>
@@ -3514,113 +3514,113 @@
         <v>4.8</v>
       </c>
       <c r="AS12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW12" t="n">
         <v>5</v>
       </c>
-      <c r="AT12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AX12" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="AY12" t="n">
-        <v>9</v>
+        <v>3.85</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="BG12" t="n">
         <v>4.9</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -3637,180 +3637,180 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N13" t="n">
         <v>4.4</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.65</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U13" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="X13" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Z13" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA13" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AE13" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF13" t="n">
         <v>10.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI13" t="n">
         <v>120</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM13" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AO13" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP13" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17</v>
+        <v>4.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="AS13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX13" t="n">
         <v>8</v>
       </c>
-      <c r="AT13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AY13" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -3896,229 +3896,229 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="H14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
         <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>2.66</v>
+        <v>1.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.45</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
-        <v>1.52</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="X14" t="n">
-        <v>40</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="n">
         <v>75</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB14" t="n">
-        <v>18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>16.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE14" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AF14" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AJ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV14" t="n">
         <v>21</v>
       </c>
-      <c r="AK14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>7.8</v>
       </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.76</v>
-      </c>
       <c r="AX14" t="n">
-        <v>2.42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.56</v>
+        <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.76</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.64</v>
+        <v>7.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.86</v>
+        <v>7.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.9</v>
+        <v>8.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.86</v>
+        <v>7.8</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,229 +4150,229 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.24</v>
+        <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="H15" t="n">
-        <v>2.96</v>
+        <v>5.8</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X15" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AR15" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="BJ15" t="n">
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.65</v>
+        <v>6.2</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="BN15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BU15" t="n">
         <v>6.6</v>
       </c>
-      <c r="BO15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>25</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BV15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -4404,229 +4404,229 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.75</v>
+        <v>2.24</v>
       </c>
       <c r="G16" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>2.58</v>
       </c>
       <c r="O16" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.86</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW16" t="n">
         <v>1.81</v>
       </c>
-      <c r="U16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="X16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>9</v>
-      </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.84</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -4775,52 +4775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G18" t="n">
         <v>2.04</v>
@@ -4936,7 +4936,7 @@
         <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.3</v>
@@ -4963,10 +4963,10 @@
         <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
         <v>1.16</v>
@@ -4978,7 +4978,7 @@
         <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -4987,34 +4987,34 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -5029,40 +5029,40 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AZ18" t="n">
         <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
         <v>1.01</v>
@@ -5071,10 +5071,10 @@
         <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -5283,52 +5283,52 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
         <v>1.01</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,234 +5415,234 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="G20" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="H20" t="n">
-        <v>2.66</v>
+        <v>4.8</v>
       </c>
       <c r="I20" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.2</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="T20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.04</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.72</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="Z20" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AA20" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AB20" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
         <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AJ20" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="AK20" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="AL20" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.16</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.12</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP20" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP20" t="n">
+      <c r="BQ20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR20" t="n">
         <v>32</v>
       </c>
-      <c r="BQ20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>50</v>
-      </c>
       <c r="BS20" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="BT20" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV20" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.74</v>
+        <v>9</v>
       </c>
       <c r="BX20" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.78</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,117 +5669,117 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J21" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="P21" t="n">
-        <v>1.28</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.1</v>
+        <v>2.04</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>1.11</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
@@ -5791,112 +5791,112 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,22 +5961,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="P22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -6045,52 +6045,52 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,22 +6215,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="O23" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="P23" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6299,52 +6299,52 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -6457,7 +6457,7 @@
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -6469,22 +6469,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="P24" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="S24" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -6553,52 +6553,52 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
         <v>1.01</v>
@@ -6610,55 +6610,55 @@
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN24" t="n">
         <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT24" t="n">
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,28 +6690,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -6723,22 +6723,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="O25" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -6807,52 +6807,52 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -6915,14 +6915,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -6965,7 +6965,7 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
@@ -6977,22 +6977,22 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="O26" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="P26" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="R26" t="n">
         <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -7061,52 +7061,52 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
         <v>1.01</v>
@@ -7118,72 +7118,72 @@
         <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7198,28 +7198,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7231,22 +7231,22 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="P27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="R27" t="n">
         <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -7315,52 +7315,52 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF27" t="n">
         <v>1.01</v>
@@ -7372,65 +7372,65 @@
         <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27" t="n">
         <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN27" t="n">
         <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT27" t="n">
         <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -7485,19 +7485,19 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="P28" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="R28" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
         <v>1.05</v>
@@ -7569,52 +7569,52 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF28" t="n">
         <v>1.01</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,36 +7701,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="G29" t="n">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="K29" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,22 +7739,22 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="R29" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="S29" t="n">
-        <v>2.48</v>
+        <v>1.05</v>
       </c>
       <c r="T29" t="n">
         <v>1.11</v>
@@ -7763,10 +7763,10 @@
         <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7823,52 +7823,52 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
         <v>1.01</v>
@@ -7877,10 +7877,10 @@
         <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
         <v>1000</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,244 +7955,498 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="G30" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="J30" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K30" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="O30" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="P30" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="R30" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>3.9</v>
+        <v>2.48</v>
       </c>
       <c r="T30" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="U30" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="W30" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X30" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AC30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AE30" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
         <v>15</v>
       </c>
       <c r="AG30" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK30" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:34:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X31" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL31" t="n">
         <v>60</v>
       </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AQ30" t="n">
+      <c r="AM31" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX31" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BH30" t="n">
+      <c r="AY31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH31" t="n">
         <v>3.5</v>
       </c>
-      <c r="BI30" t="n">
+      <c r="BI31" t="n">
         <v>2.36</v>
       </c>
-      <c r="BJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB30" t="inlineStr">
-        <is>
-          <t>2026-06-24 20:24:08</t>
+      <c r="BJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -875,7 +875,7 @@
         <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
@@ -893,16 +893,16 @@
         <v>1.59</v>
       </c>
       <c r="R2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T2" t="n">
         <v>1.54</v>
       </c>
       <c r="U2" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="V2" t="n">
         <v>1.64</v>
@@ -926,10 +926,10 @@
         <v>19.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
         <v>27</v>
@@ -938,7 +938,7 @@
         <v>27</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>17</v>
@@ -962,22 +962,22 @@
         <v>19.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AU2" t="n">
         <v>8.4</v>
@@ -989,40 +989,40 @@
         <v>17.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH2" t="n">
         <v>4.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.800000000000001</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
         <v>3.35</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="AT4" t="n">
         <v>3</v>
@@ -1494,7 +1494,7 @@
         <v>3.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="AX4" t="n">
         <v>3.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -1643,16 +1643,16 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R5" t="n">
         <v>1.16</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G6" t="n">
         <v>1.76</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I6" t="n">
         <v>6.2</v>
@@ -1975,64 +1975,64 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
         <v>85</v>
       </c>
       <c r="AP6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR6" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AS6" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AU6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX6" t="n">
         <v>3.6</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AY6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA6" t="n">
         <v>4.4</v>
       </c>
-      <c r="AW6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BB6" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BD6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.5</v>
       </c>
-      <c r="BE6" t="n">
-        <v>5</v>
-      </c>
       <c r="BF6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="n">
         <v>4.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -2118,184 +2118,184 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hammarby TFF</t>
+          <t>AFC Eskilstuna</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.35</v>
+        <v>2.36</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="H7" t="n">
-        <v>1.95</v>
+        <v>2.58</v>
       </c>
       <c r="I7" t="n">
-        <v>2.24</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
         <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="U7" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="X7" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK7" t="n">
         <v>26</v>
       </c>
-      <c r="Y7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG7" t="n">
+      <c r="AL7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN7" t="n">
         <v>16.5</v>
       </c>
-      <c r="AH7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>32</v>
-      </c>
       <c r="AO7" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="AP7" t="n">
         <v>5.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AR7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT7" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.1</v>
       </c>
       <c r="AU7" t="n">
         <v>4.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BA7" t="n">
         <v>5.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH7" t="n">
         <v>4.5</v>
       </c>
-      <c r="BH7" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BI7" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BK7" t="n">
         <v>4.6</v>
@@ -2304,53 +2304,53 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BP7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BX7" t="n">
         <v>28</v>
       </c>
-      <c r="BQ7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>25</v>
-      </c>
       <c r="BY7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="CA7" t="n">
         <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -2372,184 +2372,184 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>FBK Karlstad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>Hammarby TFF</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.36</v>
+        <v>3.35</v>
       </c>
       <c r="G8" t="n">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>2.58</v>
+        <v>1.95</v>
       </c>
       <c r="I8" t="n">
-        <v>3.25</v>
+        <v>2.24</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
         <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="X8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL8" t="n">
         <v>48</v>
       </c>
-      <c r="AB8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AM8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN8" t="n">
         <v>32</v>
       </c>
-      <c r="AF8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AO8" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AP8" t="n">
         <v>5.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AU8" t="n">
         <v>4.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA8" t="n">
         <v>5.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BK8" t="n">
         <v>4.6</v>
@@ -2558,53 +2558,53 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR8" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY8" t="n">
         <v>6.6</v>
       </c>
-      <c r="BU8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>7</v>
-      </c>
       <c r="BZ8" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="CA8" t="n">
         <v>6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
         <v>4.8</v>
@@ -2665,7 +2665,7 @@
         <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q9" t="n">
         <v>1.67</v>
@@ -2683,7 +2683,7 @@
         <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="W9" t="n">
         <v>1.17</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -3134,239 +3134,239 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Hassleholms IF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.84</v>
+        <v>1.8</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>2.12</v>
       </c>
       <c r="H11" t="n">
-        <v>2.04</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
-        <v>2.48</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U11" t="n">
         <v>2.26</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.5</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="X11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL11" t="n">
         <v>32</v>
       </c>
-      <c r="Y11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>42</v>
-      </c>
       <c r="AM11" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="AP11" t="n">
         <v>4.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AR11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV11" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AW11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>4.3</v>
       </c>
-      <c r="AX11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4</v>
-      </c>
       <c r="BA11" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG11" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BH11" t="n">
         <v>4.6</v>
       </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BI11" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS11" t="n">
         <v>5.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -3388,239 +3388,239 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hassleholms IF</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>2.84</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="H12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J12" t="n">
         <v>3.4</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>4.8</v>
       </c>
-      <c r="J12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="T12" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="U12" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="W12" t="n">
-        <v>1.89</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN12" t="n">
         <v>25</v>
       </c>
-      <c r="Y12" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>11</v>
-      </c>
       <c r="AO12" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="AP12" t="n">
         <v>4.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK12" t="n">
         <v>3.95</v>
       </c>
-      <c r="AU12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BR12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
         <v>5.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="BV12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BX12" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BZ12" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -3932,13 +3932,13 @@
         <v>3.65</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
         <v>1.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R14" t="n">
         <v>1.33</v>
@@ -3956,7 +3956,7 @@
         <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X14" t="n">
         <v>15.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.13</v>
@@ -4213,10 +4213,10 @@
         <v>2.62</v>
       </c>
       <c r="X15" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Y15" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="Z15" t="n">
         <v>85</v>
@@ -4225,7 +4225,7 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC15" t="n">
         <v>17.5</v>
@@ -4267,58 +4267,58 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AQ15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB15" t="n">
         <v>2.92</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>2.74</v>
       </c>
       <c r="BC15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BF15" t="n">
         <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>2.24</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H16" t="n">
         <v>3.2</v>
@@ -4425,28 +4425,28 @@
         <v>3.75</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
         <v>3.75</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O16" t="n">
         <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R16" t="n">
         <v>1.22</v>
@@ -4455,19 +4455,19 @@
         <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V16" t="n">
         <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y16" t="n">
         <v>12</v>
@@ -4500,7 +4500,7 @@
         <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ16" t="n">
         <v>36</v>
@@ -4530,7 +4530,7 @@
         <v>19.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
         <v>7.4</v>
@@ -4542,7 +4542,7 @@
         <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
         <v>12</v>
@@ -4554,7 +4554,7 @@
         <v>16.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
         <v>1.01</v>
@@ -4563,10 +4563,10 @@
         <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>19</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
         <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J18" t="n">
         <v>3.35</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
         <v>1.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
         <v>2.66</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
         <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW20" t="n">
         <v>4</v>
@@ -5567,7 +5567,7 @@
         <v>7.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
         <v>4.1</v>
@@ -5585,7 +5585,7 @@
         <v>4.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG20" t="n">
         <v>4.1</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -5701,16 +5701,16 @@
         <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P21" t="n">
         <v>1.79</v>
@@ -5719,16 +5719,16 @@
         <v>2.04</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T21" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="V21" t="n">
         <v>1.49</v>
@@ -5737,37 +5737,37 @@
         <v>1.54</v>
       </c>
       <c r="X21" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Y21" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="AA21" t="n">
         <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE21" t="n">
         <v>50</v>
       </c>
       <c r="AF21" t="n">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>70</v>
@@ -5782,67 +5782,67 @@
         <v>70</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.16</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.12</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.36</v>
+        <v>29</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.12</v>
+        <v>9</v>
       </c>
       <c r="AU21" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.16</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.34</v>
+        <v>22</v>
       </c>
       <c r="AX21" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>2.16</v>
+        <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.24</v>
+        <v>15.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.36</v>
+        <v>32</v>
       </c>
       <c r="BB21" t="n">
-        <v>2.36</v>
+        <v>29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.34</v>
+        <v>23</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.36</v>
+        <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.44</v>
+        <v>7</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.44</v>
+        <v>7</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,22 +5961,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O22" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P22" t="n">
         <v>1.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J23" t="n">
-        <v>1.08</v>
+        <v>3.95</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6215,34 +6215,34 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.29</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>1.28</v>
+        <v>2.58</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.15</v>
+        <v>1.39</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="S23" t="n">
-        <v>1.15</v>
+        <v>2.14</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6251,37 +6251,37 @@
         <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD23" t="n">
         <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF23" t="n">
         <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK23" t="n">
         <v>1000</v>
@@ -6305,37 +6305,37 @@
         <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
         <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
         <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
         <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
         <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
         <v>1.03</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="J24" t="n">
-        <v>1.08</v>
+        <v>3.85</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6469,22 +6469,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="O24" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="P24" t="n">
-        <v>1.08</v>
+        <v>2.62</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.08</v>
+        <v>1.49</v>
       </c>
       <c r="R24" t="n">
-        <v>1.07</v>
+        <v>1.69</v>
       </c>
       <c r="S24" t="n">
-        <v>1.05</v>
+        <v>2.18</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -6493,10 +6493,10 @@
         <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6723,22 +6723,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="P25" t="n">
-        <v>1.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="S25" t="n">
-        <v>1.12</v>
+        <v>1.92</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -6747,10 +6747,10 @@
         <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -7231,13 +7231,13 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O27" t="n">
         <v>1.12</v>
       </c>
       <c r="P27" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q27" t="n">
         <v>1.12</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="G30" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H30" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="I30" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -7993,19 +7993,19 @@
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P30" t="n">
         <v>1.79</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
         <v>2.48</v>
@@ -8017,10 +8017,10 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="W30" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -8223,19 +8223,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G31" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H31" t="n">
         <v>4.8</v>
       </c>
       <c r="I31" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J31" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K31" t="n">
         <v>3.65</v>
@@ -8313,7 +8313,7 @@
         <v>110</v>
       </c>
       <c r="AJ31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK31" t="n">
         <v>24</v>
@@ -8340,7 +8340,7 @@
         <v>24</v>
       </c>
       <c r="AS31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
@@ -8352,7 +8352,7 @@
         <v>17.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>9.800000000000001</v>
@@ -8364,7 +8364,7 @@
         <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB31" t="n">
         <v>20</v>
@@ -8376,7 +8376,7 @@
         <v>40</v>
       </c>
       <c r="BE31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF31" t="n">
         <v>15</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -896,7 +896,7 @@
         <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
         <v>1.54</v>
@@ -959,13 +959,13 @@
         <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.9</v>
@@ -974,7 +974,7 @@
         <v>5.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT2" t="n">
         <v>5</v>
@@ -1001,19 +1001,19 @@
         <v>5.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE2" t="n">
         <v>6</v>
       </c>
       <c r="BF2" t="n">
-        <v>14</v>
+        <v>4.9</v>
       </c>
       <c r="BG2" t="n">
         <v>11.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="I3" t="n">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>1.73</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>1.37</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="U3" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="W3" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -1365,94 +1365,94 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="I4" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>1.88</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.24</v>
+        <v>1.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.66</v>
+        <v>1.31</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.37</v>
       </c>
       <c r="U4" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1461,7 +1461,7 @@
         <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1470,70 +1470,70 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.98</v>
+        <v>1.12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.45</v>
+        <v>1.12</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.35</v>
+        <v>1.12</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.8</v>
+        <v>1.12</v>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>1.12</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.5</v>
+        <v>1.12</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.85</v>
+        <v>1.12</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.2</v>
+        <v>1.12</v>
       </c>
       <c r="AY4" t="n">
-        <v>3</v>
+        <v>1.12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.96</v>
+        <v>1.12</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.1</v>
+        <v>1.12</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.3</v>
+        <v>1.12</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.25</v>
+        <v>1.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.25</v>
+        <v>1.12</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.25</v>
+        <v>1.12</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.25</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.4</v>
+        <v>1.12</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
@@ -1545,37 +1545,37 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
         <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1658,7 +1658,7 @@
         <v>1.16</v>
       </c>
       <c r="S5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G6" t="n">
         <v>1.76</v>
@@ -1882,55 +1882,55 @@
         <v>4.8</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
         <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
         <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
         <v>2.3</v>
       </c>
       <c r="X6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z6" t="n">
         <v>55</v>
@@ -1942,7 +1942,7 @@
         <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
         <v>26</v>
@@ -1951,19 +1951,19 @@
         <v>75</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
         <v>18</v>
@@ -1972,67 +1972,67 @@
         <v>34</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD6" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU6" t="n">
+      <c r="BE6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF6" t="n">
         <v>3.35</v>
       </c>
-      <c r="AV6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BH6" t="n">
         <v>4.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.36</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>2.58</v>
+        <v>1.53</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.26</v>
       </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.52</v>
-      </c>
       <c r="X7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.35</v>
+        <v>2.74</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="I8" t="n">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>1.97</v>
       </c>
       <c r="O8" t="n">
         <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="T8" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.3</v>
+        <v>1.09</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>1.78</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>2.68</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G10" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H10" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I10" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.32</v>
@@ -2919,13 +2919,13 @@
         <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
         <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
         <v>2.58</v>
@@ -2937,10 +2937,10 @@
         <v>2.66</v>
       </c>
       <c r="V10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
         <v>24</v>
@@ -2949,10 +2949,10 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB10" t="n">
         <v>970</v>
@@ -2967,7 +2967,7 @@
         <v>28</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
         <v>970</v>
@@ -2994,64 +2994,64 @@
         <v>970</v>
       </c>
       <c r="AO10" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AP10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT10" t="n">
         <v>5</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR10" t="n">
+      <c r="AU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>5</v>
       </c>
-      <c r="AS10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI10" t="n">
         <v>3.3</v>
@@ -3060,16 +3060,16 @@
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO10" t="n">
         <v>4.6</v>
@@ -3078,19 +3078,19 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT10" t="n">
         <v>6.4</v>
       </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BU10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3102,7 +3102,7 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.12</v>
+        <v>2.88</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.27</v>
       </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.6</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="T11" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="U11" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -3397,230 +3397,230 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>2.48</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>1.05</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>2.06</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="R12" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="T12" t="n">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="V12" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H13" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
@@ -3669,7 +3669,7 @@
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -3678,7 +3678,7 @@
         <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P13" t="n">
         <v>2.16</v>
@@ -3690,19 +3690,19 @@
         <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="U13" t="n">
         <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W13" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -3711,22 +3711,22 @@
         <v>32</v>
       </c>
       <c r="Z13" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AA13" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AB13" t="n">
         <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD13" t="n">
         <v>36</v>
       </c>
       <c r="AE13" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF13" t="n">
         <v>10.5</v>
@@ -3735,10 +3735,10 @@
         <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ13" t="n">
         <v>15.5</v>
@@ -3750,37 +3750,37 @@
         <v>42</v>
       </c>
       <c r="AM13" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN13" t="n">
         <v>8</v>
       </c>
       <c r="AO13" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP13" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT13" t="n">
         <v>7.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>22</v>
+        <v>4.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX13" t="n">
         <v>8</v>
@@ -3792,7 +3792,7 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB13" t="n">
         <v>11.5</v>
@@ -3804,67 +3804,67 @@
         <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BL13" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H14" t="n">
         <v>6</v>
@@ -3923,28 +3923,28 @@
         <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
         <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
         <v>1.93</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T14" t="n">
         <v>1.94</v>
@@ -3959,7 +3959,7 @@
         <v>2.4</v>
       </c>
       <c r="X14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="n">
         <v>21</v>
@@ -3971,7 +3971,7 @@
         <v>240</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
         <v>9.800000000000001</v>
@@ -3983,10 +3983,10 @@
         <v>130</v>
       </c>
       <c r="AF14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -4019,10 +4019,10 @@
         <v>17</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
         <v>6.6</v>
@@ -4034,7 +4034,7 @@
         <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX14" t="n">
         <v>8.199999999999999</v>
@@ -4046,7 +4046,7 @@
         <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB14" t="n">
         <v>13.5</v>
@@ -4055,16 +4055,16 @@
         <v>15.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
         <v>8.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -4162,217 +4162,217 @@
         <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H15" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I15" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K15" t="n">
         <v>5.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="P15" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="Q15" t="n">
         <v>1.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="T15" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="U15" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="V15" t="n">
         <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="X15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Y15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z15" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB15" t="n">
         <v>970</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>100</v>
       </c>
       <c r="AF15" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>970</v>
       </c>
-      <c r="AH15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI15" t="n">
+      <c r="AK15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM15" t="n">
         <v>90</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN15" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.05</v>
+        <v>6.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.76</v>
+        <v>5.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.82</v>
+        <v>5.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>2.82</v>
+        <v>5.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>2.48</v>
+        <v>4.9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.96</v>
+        <v>6.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.92</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.05</v>
+        <v>6.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.1</v>
+        <v>3.55</v>
       </c>
       <c r="BJ15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="BP15" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BR15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.96</v>
+        <v>14</v>
       </c>
       <c r="BT15" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>2.02</v>
+        <v>8</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.02</v>
+        <v>8</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -4437,22 +4437,22 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="T16" t="n">
         <v>1.87</v>
@@ -4488,7 +4488,7 @@
         <v>15.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF16" t="n">
         <v>15.5</v>
@@ -4512,10 +4512,10 @@
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO16" t="n">
         <v>60</v>
@@ -4524,55 +4524,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR16" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU16" t="n">
         <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF16" t="n">
         <v>19</v>
       </c>
       <c r="BG16" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -4670,160 +4670,160 @@
         <v>1.92</v>
       </c>
       <c r="G17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J17" t="n">
         <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q17" t="n">
         <v>1.88</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="U17" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W17" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
         <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG17" t="n">
         <v>1.01</v>
@@ -4832,55 +4832,55 @@
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BJ17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BN17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BP17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="BR17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW17" t="n">
         <v>1.9</v>
       </c>
-      <c r="BT17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -4921,85 +4921,85 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="G18" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="H18" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I18" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="n">
         <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O18" t="n">
         <v>1.3</v>
       </c>
-      <c r="M18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>1.99</v>
       </c>
       <c r="V18" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y18" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD18" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF18" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AG18" t="n">
         <v>970</v>
@@ -5008,7 +5008,7 @@
         <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ18" t="n">
         <v>28</v>
@@ -5017,28 +5017,28 @@
         <v>28</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
         <v>5.6</v>
@@ -5047,10 +5047,10 @@
         <v>5.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
         <v>7.2</v>
@@ -5059,79 +5059,79 @@
         <v>6.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG18" t="n">
         <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK18" t="n">
         <v>1.01</v>
       </c>
       <c r="BL18" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM18" t="n">
         <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ18" t="n">
         <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS18" t="n">
         <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU18" t="n">
         <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW18" t="n">
         <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY18" t="n">
         <v>1.01</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.57</v>
       </c>
       <c r="G19" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="H19" t="n">
         <v>5.3</v>
@@ -5199,7 +5199,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="O19" t="n">
         <v>1.23</v>
@@ -5208,7 +5208,7 @@
         <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R19" t="n">
         <v>1.41</v>
@@ -5226,7 +5226,7 @@
         <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G20" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H20" t="n">
         <v>4.8</v>
@@ -5453,19 +5453,19 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P20" t="n">
         <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
         <v>3.2</v>
@@ -5480,10 +5480,10 @@
         <v>1.22</v>
       </c>
       <c r="W20" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
         <v>22</v>
@@ -5492,13 +5492,13 @@
         <v>48</v>
       </c>
       <c r="AA20" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB20" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
         <v>24</v>
@@ -5519,7 +5519,7 @@
         <v>85</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK20" t="n">
         <v>23</v>
@@ -5531,34 +5531,34 @@
         <v>130</v>
       </c>
       <c r="AN20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO20" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP20" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT20" t="n">
         <v>6.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW20" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AX20" t="n">
         <v>8.199999999999999</v>
@@ -5567,46 +5567,46 @@
         <v>7.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BH20" t="n">
         <v>3.6</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="BJ20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN20" t="n">
         <v>4.5</v>
@@ -5618,7 +5618,7 @@
         <v>12.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR20" t="n">
         <v>32</v>
@@ -5630,7 +5630,7 @@
         <v>8.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV20" t="n">
         <v>55</v>
@@ -5639,10 +5639,10 @@
         <v>9</v>
       </c>
       <c r="BX20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H21" t="n">
         <v>2.8</v>
@@ -5695,7 +5695,7 @@
         <v>3.05</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
         <v>3.65</v>
@@ -5707,10 +5707,10 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P21" t="n">
         <v>1.79</v>
@@ -5731,7 +5731,7 @@
         <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
         <v>1.54</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -5961,22 +5961,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.29</v>
+        <v>2.44</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P22" t="n">
-        <v>1.28</v>
+        <v>2.44</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1</v>
+        <v>1.89</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -5985,10 +5985,10 @@
         <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -6194,217 +6194,217 @@
         <v>2.16</v>
       </c>
       <c r="G23" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H23" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="I23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K23" t="n">
         <v>4.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="R23" t="n">
         <v>1.67</v>
       </c>
       <c r="S23" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="U23" t="n">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="V23" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI23" t="n">
         <v>38</v>
       </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AJ23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR23" t="n">
         <v>23</v>
       </c>
-      <c r="AC23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH23" t="n">
+      <c r="BS23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV23" t="n">
         <v>21</v>
       </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="G24" t="n">
         <v>2.9</v>
@@ -6454,13 +6454,13 @@
         <v>2.36</v>
       </c>
       <c r="I24" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="J24" t="n">
         <v>3.85</v>
       </c>
       <c r="K24" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6469,22 +6469,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="O24" t="n">
         <v>1.12</v>
       </c>
       <c r="P24" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R24" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="S24" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -6493,7 +6493,7 @@
         <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W24" t="n">
         <v>1.53</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -6708,13 +6708,13 @@
         <v>3.4</v>
       </c>
       <c r="I25" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
         <v>3.55</v>
       </c>
       <c r="K25" t="n">
-        <v>19.5</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6723,10 +6723,10 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>5.1</v>
+        <v>2.36</v>
       </c>
       <c r="O25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P25" t="n">
         <v>2.36</v>
@@ -6747,7 +6747,7 @@
         <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="W25" t="n">
         <v>1.96</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
         <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -7231,22 +7231,22 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="O27" t="n">
         <v>1.12</v>
       </c>
       <c r="P27" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="R27" t="n">
         <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="G30" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H30" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I30" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K30" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -8005,7 +8005,7 @@
         <v>1.73</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
         <v>2.48</v>
@@ -8017,10 +8017,10 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -8226,28 +8226,28 @@
         <v>1.9</v>
       </c>
       <c r="G31" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H31" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I31" t="n">
         <v>5.3</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K31" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="O31" t="n">
         <v>1.44</v>
@@ -8259,7 +8259,7 @@
         <v>2.28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S31" t="n">
         <v>4.5</v>
@@ -8268,13 +8268,13 @@
         <v>2.04</v>
       </c>
       <c r="U31" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V31" t="n">
         <v>1.23</v>
       </c>
       <c r="W31" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X31" t="n">
         <v>11</v>
@@ -8292,7 +8292,7 @@
         <v>7</v>
       </c>
       <c r="AC31" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD31" t="n">
         <v>21</v>
@@ -8307,16 +8307,16 @@
         <v>10.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI31" t="n">
         <v>110</v>
       </c>
       <c r="AJ31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL31" t="n">
         <v>60</v>
@@ -8325,7 +8325,7 @@
         <v>190</v>
       </c>
       <c r="AN31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="n">
         <v>140</v>
@@ -8340,7 +8340,7 @@
         <v>24</v>
       </c>
       <c r="AS31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
@@ -8352,10 +8352,10 @@
         <v>17.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY31" t="n">
         <v>9</v>
@@ -8364,7 +8364,7 @@
         <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB31" t="n">
         <v>20</v>
@@ -8376,13 +8376,13 @@
         <v>40</v>
       </c>
       <c r="BE31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BF31" t="n">
         <v>15</v>
       </c>
       <c r="BG31" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BH31" t="n">
         <v>3.5</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -866,7 +866,7 @@
         <v>2.42</v>
       </c>
       <c r="I2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J2" t="n">
         <v>3.85</v>
@@ -896,13 +896,13 @@
         <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T2" t="n">
         <v>1.54</v>
       </c>
       <c r="U2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V2" t="n">
         <v>1.64</v>
@@ -926,7 +926,7 @@
         <v>19.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>12.5</v>
@@ -965,19 +965,19 @@
         <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU2" t="n">
         <v>8.4</v>
@@ -989,7 +989,7 @@
         <v>17.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY2" t="n">
         <v>11.5</v>
@@ -998,28 +998,28 @@
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="BG2" t="n">
         <v>11.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI2" t="n">
         <v>3.8</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
@@ -1043,28 +1043,28 @@
         <v>5.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
         <v>17</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="J3" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.73</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>1.37</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="V3" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -1365,94 +1365,94 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="I4" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>1.88</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>1.88</v>
+        <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>1.31</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.37</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1470,70 +1470,70 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.12</v>
+        <v>3.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.12</v>
+        <v>3.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.12</v>
+        <v>4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.12</v>
+        <v>3.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.12</v>
+        <v>4</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.12</v>
+        <v>3.1</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.12</v>
+        <v>3.15</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.12</v>
+        <v>3.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.12</v>
+        <v>3.15</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.12</v>
+        <v>3.15</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.12</v>
+        <v>3.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>3.15</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.12</v>
+        <v>3.15</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI4" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
@@ -1545,37 +1545,37 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO4" t="n">
         <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU4" t="n">
         <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -1640,16 +1640,16 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q5" t="n">
         <v>1.22</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>1.67</v>
       </c>
       <c r="G6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
@@ -1891,7 +1891,7 @@
         <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1906,37 +1906,37 @@
         <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
         <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T6" t="n">
         <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
         <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="X6" t="n">
         <v>20</v>
       </c>
       <c r="Y6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z6" t="n">
         <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB6" t="n">
         <v>12</v>
@@ -1945,7 +1945,7 @@
         <v>12</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
         <v>75</v>
@@ -1957,7 +1957,7 @@
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
         <v>70</v>
@@ -1972,67 +1972,67 @@
         <v>34</v>
       </c>
       <c r="AM6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
         <v>9</v>
       </c>
       <c r="AO6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB6" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG6" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5</v>
       </c>
       <c r="BH6" t="n">
         <v>4.6</v>
@@ -2059,13 +2059,13 @@
         <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>2.36</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="H7" t="n">
-        <v>1.53</v>
+        <v>2.58</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N7" t="n">
         <v>1.1</v>
       </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.98</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="U7" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>1.97</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="R8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.33</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.1</v>
-      </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.09</v>
+        <v>4.8</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="I9" t="n">
-        <v>2.22</v>
+        <v>1.81</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>2.68</v>
       </c>
       <c r="T9" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.82</v>
+        <v>2.24</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H10" t="n">
         <v>2.74</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.7</v>
       </c>
       <c r="I10" t="n">
         <v>2.94</v>
@@ -2904,31 +2904,31 @@
         <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
         <v>4.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
         <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="T10" t="n">
         <v>1.56</v>
@@ -2940,10 +2940,10 @@
         <v>1.52</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
@@ -2973,7 +2973,7 @@
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>34</v>
@@ -2997,58 +2997,58 @@
         <v>970</v>
       </c>
       <c r="AP10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW10" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="AX10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY10" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AZ10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE10" t="n">
         <v>5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH10" t="n">
         <v>4.2</v>
@@ -3057,16 +3057,16 @@
         <v>3.3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
         <v>6.2</v>
@@ -3078,31 +3078,31 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT10" t="n">
         <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.5</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.26</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -3397,230 +3397,230 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="J12" t="n">
-        <v>1.05</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>2.06</v>
+        <v>1.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P12" t="n">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="T12" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="U12" t="n">
-        <v>1.97</v>
+        <v>2.46</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3651,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G13" t="n">
         <v>1.54</v>
       </c>
       <c r="H13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -3681,13 +3681,13 @@
         <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
         <v>1.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
         <v>2.92</v>
@@ -3699,10 +3699,10 @@
         <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -3720,7 +3720,7 @@
         <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
         <v>36</v>
@@ -3762,13 +3762,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT13" t="n">
         <v>7.8</v>
@@ -3777,10 +3777,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX13" t="n">
         <v>8</v>
@@ -3792,7 +3792,7 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB13" t="n">
         <v>11.5</v>
@@ -3804,31 +3804,31 @@
         <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF13" t="n">
         <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BJ13" t="n">
         <v>12.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>160</v>
       </c>
       <c r="BM13" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
         <v>4.5</v>
@@ -3840,31 +3840,31 @@
         <v>10.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
         <v>27</v>
       </c>
       <c r="BS13" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
         <v>13</v>
       </c>
       <c r="BU13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW13" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
         <v>75</v>
       </c>
       <c r="BY13" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.32</v>
@@ -3986,7 +3986,7 @@
         <v>10</v>
       </c>
       <c r="AG14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -4019,10 +4019,10 @@
         <v>17</v>
       </c>
       <c r="AR14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>6.6</v>
@@ -4034,7 +4034,7 @@
         <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX14" t="n">
         <v>8.199999999999999</v>
@@ -4046,7 +4046,7 @@
         <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB14" t="n">
         <v>13.5</v>
@@ -4058,13 +4058,13 @@
         <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF14" t="n">
         <v>8.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -4165,10 +4165,10 @@
         <v>1.62</v>
       </c>
       <c r="H15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J15" t="n">
         <v>4.6</v>
@@ -4177,19 +4177,19 @@
         <v>5.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
         <v>1.17</v>
       </c>
       <c r="P15" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q15" t="n">
         <v>1.45</v>
@@ -4210,13 +4210,13 @@
         <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X15" t="n">
         <v>30</v>
       </c>
       <c r="Y15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z15" t="n">
         <v>60</v>
@@ -4240,7 +4240,7 @@
         <v>970</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
         <v>20</v>
@@ -4267,16 +4267,16 @@
         <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AT15" t="n">
         <v>5.7</v>
@@ -4285,10 +4285,10 @@
         <v>5.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AX15" t="n">
         <v>5.6</v>
@@ -4300,7 +4300,7 @@
         <v>6.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BB15" t="n">
         <v>6.2</v>
@@ -4309,16 +4309,16 @@
         <v>6</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BF15" t="n">
         <v>5</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH15" t="n">
         <v>4.8</v>
@@ -4330,7 +4330,7 @@
         <v>10</v>
       </c>
       <c r="BK15" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4342,25 +4342,25 @@
         <v>4.7</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="BT15" t="n">
         <v>10.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -4416,37 +4416,37 @@
         <v>2.24</v>
       </c>
       <c r="G16" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I16" t="n">
         <v>3.75</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
         <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P16" t="n">
         <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
         <v>1.26</v>
@@ -4455,7 +4455,7 @@
         <v>3.95</v>
       </c>
       <c r="T16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U16" t="n">
         <v>1.94</v>
@@ -4464,7 +4464,7 @@
         <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X16" t="n">
         <v>13.5</v>
@@ -4479,7 +4479,7 @@
         <v>70</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
         <v>8.199999999999999</v>
@@ -4524,43 +4524,43 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR16" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS16" t="n">
         <v>7.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU16" t="n">
         <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC16" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>21</v>
       </c>
       <c r="BD16" t="n">
         <v>7</v>
@@ -4569,28 +4569,28 @@
         <v>7.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BJ16" t="n">
         <v>13</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BN16" t="n">
         <v>6.6</v>
@@ -4599,7 +4599,7 @@
         <v>3.65</v>
       </c>
       <c r="BP16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ16" t="n">
         <v>1.76</v>
@@ -4608,7 +4608,7 @@
         <v>48</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BT16" t="n">
         <v>8.4</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -4670,82 +4670,82 @@
         <v>1.92</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J17" t="n">
         <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O17" t="n">
         <v>1.3</v>
       </c>
       <c r="P17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.88</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
         <v>1.27</v>
       </c>
       <c r="W17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="X17" t="n">
         <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA17" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB17" t="n">
         <v>11</v>
       </c>
       <c r="AC17" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG17" t="n">
         <v>12.5</v>
@@ -4772,22 +4772,22 @@
         <v>16.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP17" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AU17" t="n">
         <v>7.2</v>
@@ -4796,10 +4796,10 @@
         <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY17" t="n">
         <v>8.199999999999999</v>
@@ -4808,7 +4808,7 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB17" t="n">
         <v>17.5</v>
@@ -4817,70 +4817,70 @@
         <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF17" t="n">
         <v>11</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BN17" t="n">
         <v>6</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP17" t="n">
         <v>19</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BR17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BT17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -4921,28 +4921,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
         <v>3.3</v>
@@ -4951,28 +4951,28 @@
         <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
         <v>1.89</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
         <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X18" t="n">
         <v>970</v>
@@ -4984,7 +4984,7 @@
         <v>50</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB18" t="n">
         <v>12</v>
@@ -4996,10 +4996,10 @@
         <v>25</v>
       </c>
       <c r="AE18" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF18" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG18" t="n">
         <v>970</v>
@@ -5023,10 +5023,10 @@
         <v>140</v>
       </c>
       <c r="AN18" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AO18" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP18" t="n">
         <v>10.5</v>
@@ -5077,16 +5077,16 @@
         <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG18" t="n">
         <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ18" t="n">
         <v>12.5</v>
@@ -5104,13 +5104,13 @@
         <v>5.2</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BR18" t="n">
         <v>34</v>
@@ -5122,7 +5122,7 @@
         <v>10.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV18" t="n">
         <v>55</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -5175,220 +5175,220 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J19" t="n">
         <v>4.1</v>
       </c>
       <c r="K19" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="T19" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD19" t="n">
         <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG19" t="n">
         <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G20" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
         <v>3.9</v>
@@ -5459,31 +5459,31 @@
         <v>1.3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R20" t="n">
         <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
         <v>1.22</v>
       </c>
       <c r="W20" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y20" t="n">
         <v>22</v>
@@ -5495,7 +5495,7 @@
         <v>140</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC20" t="n">
         <v>9.199999999999999</v>
@@ -5507,7 +5507,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
@@ -5531,7 +5531,7 @@
         <v>130</v>
       </c>
       <c r="AN20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO20" t="n">
         <v>95</v>
@@ -5540,109 +5540,109 @@
         <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT20" t="n">
         <v>6.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB20" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ20" t="n">
         <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR20" t="n">
         <v>32</v>
       </c>
       <c r="BS20" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV20" t="n">
         <v>55</v>
       </c>
       <c r="BW20" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H21" t="n">
         <v>2.8</v>
@@ -5695,7 +5695,7 @@
         <v>3.05</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
         <v>3.65</v>
@@ -5707,7 +5707,7 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
         <v>1.36</v>
@@ -5731,7 +5731,7 @@
         <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W21" t="n">
         <v>1.54</v>
@@ -5845,58 +5845,58 @@
         <v>7</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="BJ21" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.84</v>
+        <v>9.4</v>
       </c>
       <c r="BN21" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BP21" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.74</v>
+        <v>7.2</v>
       </c>
       <c r="BR21" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="BT21" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="BV21" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.74</v>
+        <v>7.2</v>
       </c>
       <c r="BX21" t="n">
         <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -5937,40 +5937,40 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="G22" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I22" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
         <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>2.44</v>
+        <v>1.1</v>
       </c>
       <c r="O22" t="n">
         <v>1.11</v>
       </c>
       <c r="P22" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="R22" t="n">
         <v>1.61</v>
@@ -5979,124 +5979,124 @@
         <v>1.89</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AY22" t="n">
         <v>1.86</v>
       </c>
-      <c r="X22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G23" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
         <v>4.6</v>
@@ -6212,7 +6212,7 @@
         <v>1.22</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
         <v>1.1</v>
@@ -6221,37 +6221,37 @@
         <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="Q23" t="n">
         <v>1.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="S23" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="T23" t="n">
         <v>1.49</v>
       </c>
       <c r="U23" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="V23" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="X23" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Y23" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA23" t="n">
         <v>50</v>
@@ -6263,121 +6263,121 @@
         <v>11</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF23" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
         <v>15.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM23" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO23" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AP23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC23" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV23" t="n">
+      <c r="BD23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF23" t="n">
         <v>5.1</v>
       </c>
-      <c r="AW23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG23" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH23" t="n">
         <v>4.8</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ23" t="n">
         <v>8.6</v>
       </c>
       <c r="BK23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO23" t="n">
         <v>3.85</v>
       </c>
       <c r="BP23" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ23" t="n">
         <v>6.4</v>
@@ -6386,25 +6386,25 @@
         <v>23</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT23" t="n">
         <v>7</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV23" t="n">
         <v>21</v>
       </c>
       <c r="BW23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX23" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="G24" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="H24" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="I24" t="n">
         <v>2.94</v>
@@ -6460,205 +6460,205 @@
         <v>3.85</v>
       </c>
       <c r="K24" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S24" t="n">
         <v>2.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>2.64</v>
       </c>
       <c r="V24" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W24" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>1.57</v>
       </c>
       <c r="G25" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H25" t="n">
         <v>3.4</v>
@@ -6720,7 +6720,7 @@
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N25" t="n">
         <v>2.36</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
         <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7228,7 @@
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N27" t="n">
         <v>1.26</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O28" t="n">
         <v>1.03</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="G30" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J30" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K30" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -7993,22 +7993,22 @@
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O30" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="P30" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="Q30" t="n">
         <v>1.73</v>
       </c>
       <c r="R30" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="S30" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8020,52 +8020,52 @@
         <v>1.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="Z30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL30" t="n">
         <v>46</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -8226,37 +8226,37 @@
         <v>1.9</v>
       </c>
       <c r="G31" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I31" t="n">
         <v>5.3</v>
       </c>
       <c r="J31" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K31" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N31" t="n">
         <v>2.86</v>
       </c>
       <c r="O31" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P31" t="n">
         <v>1.69</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R31" t="n">
         <v>1.24</v>
@@ -8265,10 +8265,10 @@
         <v>4.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U31" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V31" t="n">
         <v>1.23</v>
@@ -8277,10 +8277,10 @@
         <v>2</v>
       </c>
       <c r="X31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z31" t="n">
         <v>38</v>
@@ -8292,7 +8292,7 @@
         <v>7</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD31" t="n">
         <v>21</v>
@@ -8331,7 +8331,7 @@
         <v>140</v>
       </c>
       <c r="AP31" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ31" t="n">
         <v>12</v>
@@ -8340,7 +8340,7 @@
         <v>24</v>
       </c>
       <c r="AS31" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
@@ -8352,7 +8352,7 @@
         <v>17.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>9.6</v>
@@ -8364,7 +8364,7 @@
         <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BB31" t="n">
         <v>20</v>
@@ -8376,77 +8376,77 @@
         <v>40</v>
       </c>
       <c r="BE31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BF31" t="n">
         <v>15</v>
       </c>
       <c r="BG31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ31" t="n">
         <v>11</v>
       </c>
-      <c r="BH31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>1000</v>
-      </c>
       <c r="BK31" t="n">
-        <v>1.41</v>
+        <v>6.6</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.41</v>
+        <v>8.4</v>
       </c>
       <c r="BN31" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.41</v>
+        <v>3.55</v>
       </c>
       <c r="BP31" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.41</v>
+        <v>8</v>
       </c>
       <c r="BR31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.41</v>
+        <v>11.5</v>
       </c>
       <c r="BT31" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.41</v>
+        <v>5.4</v>
       </c>
       <c r="BV31" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.41</v>
+        <v>12.5</v>
       </c>
       <c r="BX31" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.41</v>
+        <v>13.5</v>
       </c>
       <c r="BZ31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.41</v>
+        <v>11.5</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -857,127 +857,127 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G2" t="n">
         <v>2.96</v>
       </c>
       <c r="H2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I2" t="n">
         <v>2.54</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R2" t="n">
         <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U2" t="n">
         <v>2.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W2" t="n">
         <v>1.51</v>
       </c>
       <c r="X2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
         <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AJ2" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="AK2" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AL2" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="AN2" t="n">
         <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.9</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.1</v>
+        <v>15</v>
       </c>
       <c r="AU2" t="n">
         <v>8.4</v>
@@ -986,34 +986,34 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY2" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.8</v>
+        <v>19</v>
       </c>
       <c r="BB2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="BC2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD2" t="n">
         <v>20</v>
       </c>
-      <c r="BD2" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
         <v>11.5</v>
@@ -1022,7 +1022,7 @@
         <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.800000000000001</v>
@@ -1076,11 +1076,11 @@
         <v>17</v>
       </c>
       <c r="CA2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
         <v>4.1</v>
@@ -1120,22 +1120,22 @@
         <v>1.97</v>
       </c>
       <c r="I3" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.23</v>
@@ -1150,7 +1150,7 @@
         <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="T3" t="n">
         <v>1.61</v>
@@ -1159,7 +1159,7 @@
         <v>2.26</v>
       </c>
       <c r="V3" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="W3" t="n">
         <v>1.32</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="G4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I4" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.27</v>
@@ -1389,7 +1389,7 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.22</v>
@@ -1404,7 +1404,7 @@
         <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="T4" t="n">
         <v>1.76</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1643,22 +1643,22 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
         <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R5" t="n">
         <v>1.16</v>
       </c>
       <c r="S5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1873,31 +1873,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G6" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K6" t="n">
         <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
@@ -1912,19 +1912,19 @@
         <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X6" t="n">
         <v>20</v>
@@ -1942,10 +1942,10 @@
         <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>75</v>
@@ -1975,64 +1975,64 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AU6" t="n">
         <v>3.8</v>
       </c>
       <c r="AV6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB6" t="n">
         <v>4.5</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="BC6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD6" t="n">
         <v>5.2</v>
       </c>
-      <c r="AX6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE6" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BH6" t="n">
         <v>4.6</v>
@@ -2047,31 +2047,31 @@
         <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BM6" t="n">
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS6" t="n">
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>2.58</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
         <v>3.1</v>
@@ -2175,7 +2175,7 @@
         <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
         <v>1.52</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.21</v>
@@ -2420,7 +2420,7 @@
         <v>1.51</v>
       </c>
       <c r="S8" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
         <v>1.57</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1.81</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
         <v>4.8</v>
@@ -2665,7 +2665,7 @@
         <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
         <v>1.59</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>2.74</v>
       </c>
       <c r="I10" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J10" t="n">
         <v>3.6</v>
@@ -2997,52 +2997,52 @@
         <v>970</v>
       </c>
       <c r="AP10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE10" t="n">
         <v>5.2</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
@@ -3054,7 +3054,7 @@
         <v>4.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ10" t="n">
         <v>9</v>
@@ -3078,7 +3078,7 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
@@ -3090,7 +3090,7 @@
         <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.19</v>
@@ -3176,7 +3176,7 @@
         <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="R11" t="n">
         <v>1.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G13" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="H13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
@@ -3669,13 +3669,13 @@
         <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.26</v>
@@ -3693,7 +3693,7 @@
         <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
         <v>1.96</v>
@@ -3702,7 +3702,7 @@
         <v>1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -3762,7 +3762,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.7</v>
+        <v>22</v>
       </c>
       <c r="AR13" t="n">
         <v>5.1</v>
@@ -3816,7 +3816,7 @@
         <v>4.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ13" t="n">
         <v>12.5</v>
@@ -3852,7 +3852,7 @@
         <v>13</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV13" t="n">
         <v>70</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.39</v>
@@ -3932,31 +3932,31 @@
         <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="R14" t="n">
         <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V14" t="n">
         <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="X14" t="n">
         <v>15</v>
@@ -4019,7 +4019,7 @@
         <v>17</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS14" t="n">
         <v>9.199999999999999</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="G15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H15" t="n">
         <v>5.8</v>
@@ -4174,7 +4174,7 @@
         <v>4.6</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.23</v>
@@ -4204,13 +4204,13 @@
         <v>1.64</v>
       </c>
       <c r="U15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X15" t="n">
         <v>30</v>
@@ -4342,7 +4342,7 @@
         <v>4.7</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BP15" t="n">
         <v>9.800000000000001</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G16" t="n">
         <v>2.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4694,10 +4694,10 @@
         <v>3.65</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
         <v>1.89</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4921,58 +4921,58 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="G18" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="H18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" t="n">
         <v>4.5</v>
       </c>
-      <c r="I18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
         <v>1.89</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
         <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="X18" t="n">
         <v>970</v>
@@ -4981,7 +4981,7 @@
         <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA18" t="n">
         <v>160</v>
@@ -4993,13 +4993,13 @@
         <v>12</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
         <v>85</v>
       </c>
       <c r="AF18" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AG18" t="n">
         <v>970</v>
@@ -5011,10 +5011,10 @@
         <v>90</v>
       </c>
       <c r="AJ18" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AL18" t="n">
         <v>46</v>
@@ -5023,13 +5023,13 @@
         <v>140</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AO18" t="n">
         <v>100</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
         <v>11</v>
@@ -5077,7 +5077,7 @@
         <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BG18" t="n">
         <v>1.01</v>
@@ -5086,7 +5086,7 @@
         <v>4.1</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ18" t="n">
         <v>12.5</v>
@@ -5101,13 +5101,13 @@
         <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP18" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ18" t="n">
         <v>9</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.58</v>
       </c>
       <c r="G19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H19" t="n">
         <v>5.4</v>
@@ -5205,10 +5205,10 @@
         <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
         <v>1.44</v>
@@ -5226,7 +5226,7 @@
         <v>1.15</v>
       </c>
       <c r="W19" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X19" t="n">
         <v>24</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G20" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H20" t="n">
         <v>4.9</v>
@@ -5459,7 +5459,7 @@
         <v>1.3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
         <v>1.88</v>
@@ -5468,7 +5468,7 @@
         <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
         <v>1.85</v>
@@ -5480,7 +5480,7 @@
         <v>1.22</v>
       </c>
       <c r="W20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X20" t="n">
         <v>18.5</v>
@@ -5564,7 +5564,7 @@
         <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
         <v>17</v>
@@ -5594,7 +5594,7 @@
         <v>3.55</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ20" t="n">
         <v>10.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G21" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="I21" t="n">
         <v>3.05</v>
@@ -5698,7 +5698,7 @@
         <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L21" t="n">
         <v>1.41</v>
@@ -5716,7 +5716,7 @@
         <v>1.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R21" t="n">
         <v>1.29</v>
@@ -5734,7 +5734,7 @@
         <v>1.49</v>
       </c>
       <c r="W21" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
         <v>13</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -5940,16 +5940,16 @@
         <v>1.77</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="H22" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="n">
         <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K22" t="n">
         <v>4.9</v>
@@ -5961,7 +5961,7 @@
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>1.1</v>
+        <v>2.88</v>
       </c>
       <c r="O22" t="n">
         <v>1.11</v>
@@ -5988,7 +5988,7 @@
         <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6194,16 +6194,16 @@
         <v>2.22</v>
       </c>
       <c r="G23" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H23" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I23" t="n">
         <v>3.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="K23" t="n">
         <v>4.6</v>
@@ -6215,19 +6215,19 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" t="n">
         <v>1.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S23" t="n">
         <v>2.06</v>
@@ -6242,13 +6242,13 @@
         <v>1.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X23" t="n">
         <v>29</v>
       </c>
       <c r="Y23" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z23" t="n">
         <v>26</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
         <v>2.58</v>
       </c>
       <c r="I24" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="J24" t="n">
         <v>3.85</v>
@@ -6469,22 +6469,22 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
         <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="R24" t="n">
         <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T24" t="n">
         <v>1.5</v>
@@ -6493,7 +6493,7 @@
         <v>2.64</v>
       </c>
       <c r="V24" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.58</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="O25" t="n">
         <v>1.12</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
         <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>1.08</v>
+        <v>2.04</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -7240,13 +7240,13 @@
         <v>1.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="R27" t="n">
         <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G28" t="n">
         <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G29" t="n">
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -7969,23 +7969,23 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="H30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K30" t="n">
         <v>4</v>
       </c>
-      <c r="I30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L30" t="n">
         <v>1.01</v>
       </c>
@@ -7993,22 +7993,22 @@
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="O30" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P30" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8017,31 +8017,31 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
@@ -8053,19 +8053,19 @@
         <v>14.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL30" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H31" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I31" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>3.3</v>
       </c>
       <c r="K31" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L31" t="n">
         <v>1.44</v>
@@ -8250,10 +8250,10 @@
         <v>2.86</v>
       </c>
       <c r="O31" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P31" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q31" t="n">
         <v>2.32</v>
@@ -8271,10 +8271,10 @@
         <v>1.82</v>
       </c>
       <c r="V31" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W31" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="X31" t="n">
         <v>10.5</v>
@@ -8283,7 +8283,7 @@
         <v>14</v>
       </c>
       <c r="Z31" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AA31" t="n">
         <v>150</v>
@@ -8340,7 +8340,7 @@
         <v>24</v>
       </c>
       <c r="AS31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
@@ -8364,7 +8364,7 @@
         <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB31" t="n">
         <v>20</v>
@@ -8382,7 +8382,7 @@
         <v>15</v>
       </c>
       <c r="BG31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH31" t="n">
         <v>2.94</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB31"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G2" t="n">
         <v>2.96</v>
       </c>
       <c r="H2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I2" t="n">
         <v>2.54</v>
@@ -875,34 +875,34 @@
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
         <v>1.61</v>
       </c>
       <c r="R2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
         <v>1.53</v>
       </c>
       <c r="U2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V2" t="n">
         <v>1.65</v>
@@ -914,7 +914,7 @@
         <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Z2" t="n">
         <v>21</v>
@@ -923,7 +923,7 @@
         <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC2" t="n">
         <v>9.4</v>
@@ -938,7 +938,7 @@
         <v>32</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
         <v>15</v>
@@ -956,13 +956,13 @@
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN2" t="n">
         <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AP2" t="n">
         <v>17.5</v>
@@ -971,7 +971,7 @@
         <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
         <v>22</v>
@@ -980,7 +980,7 @@
         <v>15</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
@@ -989,25 +989,25 @@
         <v>16</v>
       </c>
       <c r="AX2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
         <v>19</v>
       </c>
       <c r="BB2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
         <v>28</v>
@@ -1019,22 +1019,22 @@
         <v>11.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
@@ -1043,28 +1043,28 @@
         <v>5.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
         <v>17</v>
       </c>
       <c r="BW2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1076,11 +1076,11 @@
         <v>17</v>
       </c>
       <c r="CA2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1.29</v>
@@ -1141,7 +1141,7 @@
         <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
         <v>1.67</v>
@@ -1177,7 +1177,7 @@
         <v>28</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC3" t="n">
         <v>9.800000000000001</v>
@@ -1189,7 +1189,7 @@
         <v>22</v>
       </c>
       <c r="AF3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG3" t="n">
         <v>16.5</v>
@@ -1204,10 +1204,10 @@
         <v>75</v>
       </c>
       <c r="AK3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
         <v>85</v>
@@ -1219,58 +1219,58 @@
         <v>13.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT3" t="n">
         <v>5.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC3" t="n">
         <v>6.2</v>
       </c>
       <c r="BD3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF3" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>6</v>
-      </c>
       <c r="BG3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="n">
         <v>4.1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="G4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="I4" t="n">
         <v>1.6</v>
@@ -1380,7 +1380,7 @@
         <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.27</v>
@@ -1398,16 +1398,16 @@
         <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R4" t="n">
         <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U4" t="n">
         <v>2.06</v>
@@ -1419,7 +1419,7 @@
         <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1431,7 +1431,7 @@
         <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1470,58 +1470,58 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AS4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT4" t="n">
         <v>4</v>
       </c>
-      <c r="AT4" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AU4" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AW4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BB4" t="n">
         <v>3.1</v>
       </c>
-      <c r="AY4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BC4" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BG4" t="n">
         <v>3.15</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chilean Segunda Division</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,60 +1605,60 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Santiago City</t>
+          <t>Eidsvold Turn</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Provincial Ovalle FC</t>
+          <t>Tromsdalen</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="P5" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1835,21 +1835,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,226 +1864,226 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>Santiago City</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Provincial Ovalle FC</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>1.33</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>1.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.72</v>
+        <v>1.23</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>2.54</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
         <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
         <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
         <v>1.01</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,239 +2118,239 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.36</v>
+        <v>1.62</v>
       </c>
       <c r="G7" t="n">
-        <v>2.92</v>
+        <v>1.68</v>
       </c>
       <c r="H7" t="n">
-        <v>2.58</v>
+        <v>5.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.52</v>
+        <v>2.46</v>
       </c>
       <c r="X7" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.5</v>
+        <v>26</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AC7" t="n">
         <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>17.5</v>
       </c>
-      <c r="AI7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>50</v>
-      </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO7" t="n">
-        <v>19.5</v>
+        <v>90</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AY7" t="n">
         <v>4.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BC7" t="n">
         <v>5.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BG7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH7" t="n">
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>140</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
         <v>4.5</v>
       </c>
-      <c r="BI7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BO7" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -2372,28 +2372,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FBK Karlstad</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hammarby TFF</t>
+          <t>AFC Eskilstuna</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="H8" t="n">
-        <v>1.95</v>
+        <v>2.58</v>
       </c>
       <c r="I8" t="n">
-        <v>2.24</v>
+        <v>3.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
         <v>4.5</v>
@@ -2402,209 +2402,209 @@
         <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.57</v>
       </c>
-      <c r="U8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X8" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z8" t="n">
         <v>24</v>
       </c>
-      <c r="Y8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB8" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>19.5</v>
       </c>
       <c r="AC8" t="n">
         <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF8" t="n">
         <v>21</v>
       </c>
-      <c r="AF8" t="n">
-        <v>32</v>
-      </c>
       <c r="AG8" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AJ8" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AK8" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AN8" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="AO8" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT8" t="n">
         <v>5.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH8" t="n">
         <v>4.5</v>
       </c>
-      <c r="AW8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD8" t="n">
+      <c r="BI8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN8" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BO8" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BP8" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS8" t="n">
         <v>6.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BZ8" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>FBK Karlstad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trelleborgs</t>
+          <t>Hammarby TFF</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="I9" t="n">
-        <v>1.81</v>
+        <v>2.24</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="S9" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="V9" t="n">
-        <v>2.24</v>
+        <v>1.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AB9" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AC9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD9" t="n">
         <v>12</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>12.5</v>
       </c>
       <c r="AE9" t="n">
         <v>21</v>
       </c>
       <c r="AF9" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AG9" t="n">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ9" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AK9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM9" t="n">
         <v>80</v>
       </c>
-      <c r="AL9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>110</v>
-      </c>
       <c r="AN9" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO9" t="n">
         <v>4</v>
       </c>
-      <c r="BD9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BP9" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BX9" t="n">
         <v>25</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IK Brage</t>
+          <t>Kristianstads</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Trelleborgs</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.54</v>
+        <v>4.8</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.74</v>
+        <v>1.62</v>
       </c>
       <c r="I10" t="n">
-        <v>2.92</v>
+        <v>1.81</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T10" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>2.66</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.52</v>
+        <v>2.22</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH10" t="n">
         <v>23</v>
       </c>
-      <c r="Y10" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>17</v>
-      </c>
       <c r="AI10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="AK10" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AL10" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>970</v>
+        <v>80</v>
       </c>
       <c r="AO10" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="AQ10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK10" t="n">
         <v>4.9</v>
       </c>
-      <c r="AR10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BO10" t="n">
         <v>4.6</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,244 +3129,244 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hassleholms IF</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.79</v>
+        <v>2.54</v>
       </c>
       <c r="G11" t="n">
-        <v>2.12</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="I11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
         <v>4.8</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O11" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
         <v>1.56</v>
       </c>
       <c r="U11" t="n">
-        <v>2.28</v>
+        <v>2.72</v>
       </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="W11" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>38</v>
       </c>
-      <c r="AA11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AK11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG11" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP11" t="n">
+      <c r="BH11" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS11" t="n">
+      <c r="BI11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK11" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>4</v>
-      </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>6.4</v>
       </c>
-      <c r="BN11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BR11" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT11" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -3388,246 +3388,246 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Hassleholms IF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vasalunds IF</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.84</v>
+        <v>1.79</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="H12" t="n">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="I12" t="n">
-        <v>2.48</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
         <v>4.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="T12" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="U12" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="X12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="Z12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AA12" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AB12" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AC12" t="n">
         <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AF12" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO12" t="n">
         <v>38</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>4.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BA12" t="n">
         <v>4.9</v>
       </c>
       <c r="BB12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS12" t="n">
         <v>5.4</v>
       </c>
-      <c r="BC12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BT12" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BZ12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,244 +3637,244 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Vasalunds IF</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.48</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="U13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X13" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT13" t="n">
         <v>4.5</v>
       </c>
-      <c r="K13" t="n">
+      <c r="AU13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC13" t="n">
         <v>4.9</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="X13" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>12</v>
-      </c>
       <c r="BD13" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="BE13" t="n">
         <v>5.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="BJ13" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BL13" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BO13" t="n">
         <v>3.6</v>
       </c>
       <c r="BP13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR13" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>8.800000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="BV13" t="n">
-        <v>70</v>
+        <v>16.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BX13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -3891,102 +3891,102 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="H14" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="U14" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Y14" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Z14" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA14" t="n">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="AB14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE14" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG14" t="n">
         <v>10</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -3995,127 +3995,127 @@
         <v>120</v>
       </c>
       <c r="AJ14" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AM14" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AO14" t="n">
         <v>170</v>
       </c>
       <c r="AP14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AT14" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AU14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX14" t="n">
         <v>8</v>
       </c>
-      <c r="AV14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AY14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BA14" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BB14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC14" t="n">
         <v>13.5</v>
       </c>
-      <c r="BC14" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BD14" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK14" t="n">
         <v>1.01</v>
       </c>
       <c r="BL14" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM14" t="n">
         <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ14" t="n">
         <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS14" t="n">
         <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU14" t="n">
         <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW14" t="n">
         <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -4150,229 +4150,229 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="G15" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="H15" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.45</v>
+        <v>1.97</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.28</v>
+        <v>3.55</v>
       </c>
       <c r="T15" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="V15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="X15" t="n">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="Z15" t="n">
         <v>60</v>
       </c>
       <c r="AA15" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
         <v>180</v>
       </c>
-      <c r="AB15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>90</v>
-      </c>
       <c r="AN15" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AO15" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="AP15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="AS15" t="n">
-        <v>3</v>
+        <v>8.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.96</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.92</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.96</v>
+        <v>8.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.05</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>190</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN15" t="n">
         <v>4.8</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BO15" t="n">
         <v>3.55</v>
       </c>
-      <c r="BJ15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BP15" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS15" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BU15" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW15" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY15" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,229 +4404,229 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.26</v>
+        <v>1.53</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>7.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.14</v>
+        <v>1.51</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="S16" t="n">
-        <v>3.95</v>
+        <v>2.28</v>
       </c>
       <c r="T16" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="U16" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.66</v>
+        <v>2.74</v>
       </c>
       <c r="X16" t="n">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="Z16" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AA16" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI16" t="n">
         <v>70</v>
       </c>
-      <c r="AB16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI16" t="n">
+      <c r="AJ16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO16" t="n">
         <v>65</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>60</v>
-      </c>
       <c r="AP16" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW16" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>7</v>
-      </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>21</v>
+        <v>5.1</v>
       </c>
       <c r="BG16" t="n">
         <v>7.2</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.9</v>
+        <v>3.55</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.66</v>
+        <v>4.9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
         <v>6.6</v>
       </c>
-      <c r="BO16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BT16" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BV16" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.81</v>
+        <v>8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.84</v>
+        <v>8</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -4658,229 +4658,229 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="G17" t="n">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH17" t="n">
         <v>3.2</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT17" t="n">
+      <c r="BI17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW17" t="n">
         <v>8</v>
       </c>
-      <c r="AU17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.93</v>
+        <v>8.6</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -4912,229 +4912,229 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="H18" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
         <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="X18" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AA18" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AB18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>12</v>
       </c>
-      <c r="AC18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH18" t="n">
+      <c r="AR18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR18" t="n">
         <v>29</v>
       </c>
-      <c r="AI18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL18" t="n">
+      <c r="BS18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX18" t="n">
         <v>46</v>
       </c>
-      <c r="AM18" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>160</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>65</v>
-      </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -5166,127 +5166,127 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="G19" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="H19" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I19" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="V19" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Y19" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA19" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE19" t="n">
         <v>95</v>
       </c>
       <c r="AF19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AK19" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AL19" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AO19" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP19" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
         <v>1.01</v>
@@ -5295,100 +5295,100 @@
         <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
         <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY19" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>160</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP19" t="n">
         <v>14.5</v>
       </c>
-      <c r="BA19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ19" t="n">
+      <c r="BQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT19" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BU19" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -5420,88 +5420,88 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="G20" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="H20" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="X20" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="Y20" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Z20" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AA20" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AB20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AE20" t="n">
         <v>80</v>
@@ -5516,133 +5516,133 @@
         <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AK20" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AL20" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO20" t="n">
         <v>95</v>
       </c>
       <c r="AP20" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
         <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BJ20" t="n">
         <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BR20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BT20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU20" t="n">
         <v>5</v>
       </c>
       <c r="BV20" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BX20" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,234 +5669,234 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.74</v>
+        <v>1.73</v>
       </c>
       <c r="G21" t="n">
-        <v>2.82</v>
+        <v>1.81</v>
       </c>
       <c r="H21" t="n">
-        <v>2.88</v>
+        <v>4.9</v>
       </c>
       <c r="I21" t="n">
-        <v>3.05</v>
+        <v>5.6</v>
       </c>
       <c r="J21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.25</v>
       </c>
-      <c r="K21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.7</v>
-      </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>2.22</v>
       </c>
       <c r="X21" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>13</v>
       </c>
-      <c r="Y21" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC21" t="n">
+      <c r="AR21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX21" t="n">
         <v>8</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AY21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB21" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG21" t="n">
+      <c r="BC21" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>23</v>
-      </c>
       <c r="BD21" t="n">
-        <v>32</v>
+        <v>4.8</v>
       </c>
       <c r="BE21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF21" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF21" t="n">
-        <v>7</v>
-      </c>
       <c r="BG21" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="BJ21" t="n">
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS21" t="n">
         <v>9.4</v>
       </c>
-      <c r="BN21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>8</v>
-      </c>
       <c r="BT21" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV21" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY21" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,234 +5923,234 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.77</v>
+        <v>2.74</v>
       </c>
       <c r="G22" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="H22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.7</v>
       </c>
-      <c r="I22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.89</v>
-      </c>
       <c r="T22" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="U22" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX22" t="n">
         <v>38</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -6182,229 +6182,229 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.22</v>
+        <v>1.77</v>
       </c>
       <c r="G23" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R23" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="S23" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="T23" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="U23" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="V23" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="X23" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="Y23" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Z23" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AA23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE23" t="n">
         <v>50</v>
       </c>
-      <c r="AB23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>29</v>
-      </c>
       <c r="AF23" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG23" t="n">
         <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AJ23" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM23" t="n">
         <v>65</v>
       </c>
       <c r="AN23" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="AO23" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AP23" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="AX23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ23" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
+      <c r="BR23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW23" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BN23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>23</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>7</v>
-      </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -6436,181 +6436,181 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="G24" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="H24" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="S24" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U24" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V24" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W24" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="X24" t="n">
         <v>34</v>
       </c>
       <c r="Y24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA24" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB24" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AC24" t="n">
         <v>12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI24" t="n">
         <v>32</v>
       </c>
-      <c r="AF24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>36</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AK24" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AM24" t="n">
         <v>65</v>
       </c>
       <c r="AN24" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AO24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AR24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI24" t="n">
         <v>3.6</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>3.25</v>
       </c>
       <c r="BJ24" t="n">
         <v>8.6</v>
@@ -6625,40 +6625,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ24" t="n">
         <v>6.4</v>
       </c>
-      <c r="BO24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BR24" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BU24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BV24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BW24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX24" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -6690,229 +6690,229 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="G25" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="H25" t="n">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>2.98</v>
       </c>
       <c r="J25" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M25" t="n">
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="R25" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S25" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="V25" t="n">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="W25" t="n">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BH25" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ25" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP25" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX25" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6944,55 +6944,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M26" t="n">
         <v>1.02</v>
       </c>
-      <c r="G26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N26" t="n">
-        <v>1.26</v>
+        <v>2.42</v>
       </c>
       <c r="O26" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="S26" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -7001,10 +7001,10 @@
         <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7169,14 +7169,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -7198,16 +7198,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haukar</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
@@ -7219,7 +7219,7 @@
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7228,25 +7228,25 @@
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
         <v>1.26</v>
       </c>
       <c r="O27" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="P27" t="n">
         <v>1.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="R27" t="n">
         <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>1.12</v>
+        <v>2.04</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7452,55 +7452,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>Haukar</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
         <v>1.02</v>
       </c>
-      <c r="G28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N28" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="O28" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -7626,65 +7626,65 @@
         <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN28" t="n">
         <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT28" t="n">
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -7706,12 +7706,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -7727,7 +7727,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7742,16 +7742,16 @@
         <v>1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="P29" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="R29" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
         <v>1.05</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,60 +7955,60 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1.02</v>
       </c>
       <c r="G30" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="K30" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.82</v>
+        <v>1.1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="P30" t="n">
-        <v>1.83</v>
+        <v>1.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="R30" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="S30" t="n">
-        <v>2.34</v>
+        <v>1.05</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8017,43 +8017,43 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
@@ -8062,7 +8062,7 @@
         <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
         <v>1000</v>
@@ -8131,10 +8131,10 @@
         <v>1.01</v>
       </c>
       <c r="BH30" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
@@ -8192,261 +8192,515 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HFX Wanderers</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X31" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:35:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Novorizontino</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F32" t="n">
         <v>1.93</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G32" t="n">
         <v>2.02</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H32" t="n">
         <v>4.7</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I32" t="n">
         <v>5.2</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>3.3</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>3.6</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L32" t="n">
         <v>1.44</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M32" t="n">
         <v>1.1</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N32" t="n">
         <v>2.86</v>
       </c>
-      <c r="O31" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="O32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P32" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q32" t="n">
         <v>2.32</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V32" t="n">
         <v>1.24</v>
       </c>
-      <c r="S31" t="n">
+      <c r="W32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN32" t="n">
         <v>4.5</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="X31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z31" t="n">
+      <c r="BO32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV32" t="n">
         <v>48</v>
       </c>
-      <c r="AA31" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA31" t="n">
+      <c r="BW32" t="n">
         <v>12.5</v>
       </c>
-      <c r="BB31" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>13</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BN31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP31" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ31" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR31" t="n">
+      <c r="BX32" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ32" t="n">
         <v>36</v>
       </c>
-      <c r="BS31" t="n">
+      <c r="CA32" t="n">
         <v>11.5</v>
       </c>
-      <c r="BT31" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV31" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW31" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX31" t="n">
-        <v>65</v>
-      </c>
-      <c r="BY31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BZ31" t="n">
-        <v>36</v>
-      </c>
-      <c r="CA31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="CB31" t="inlineStr">
-        <is>
-          <t>2026-06-25 07:19:53</t>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -887,7 +887,7 @@
         <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q2" t="n">
         <v>1.61</v>
@@ -896,7 +896,7 @@
         <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T2" t="n">
         <v>1.53</v>
@@ -914,7 +914,7 @@
         <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
         <v>21</v>
@@ -944,7 +944,7 @@
         <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AJ2" t="n">
         <v>140</v>
@@ -1040,7 +1040,7 @@
         <v>6.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BP2" t="n">
         <v>21</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.29</v>
@@ -1135,7 +1135,7 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.23</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
         <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
         <v>2.06</v>
@@ -1473,58 +1473,58 @@
         <v>9</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AR4" t="n">
         <v>3.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AT4" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AV4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BF4" t="n">
         <v>3.25</v>
       </c>
-      <c r="AW4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BG4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BH4" t="n">
         <v>4.7</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1655,7 +1655,7 @@
         <v>1.11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
         <v>1.11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,22 +1897,22 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>1.33</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.23</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I7" t="n">
         <v>6.4</v>
@@ -2142,7 +2142,7 @@
         <v>4.3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.32</v>
@@ -2151,58 +2151,58 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R7" t="n">
         <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T7" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA7" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AB7" t="n">
         <v>10</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE7" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF7" t="n">
         <v>11</v>
@@ -2211,82 +2211,82 @@
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
         <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK7" t="n">
         <v>20</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO7" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AQ7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW7" t="n">
         <v>5.5</v>
       </c>
-      <c r="AR7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV7" t="n">
+      <c r="AX7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA7" t="n">
         <v>5.5</v>
       </c>
-      <c r="AW7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="BB7" t="n">
         <v>4.5</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5</v>
-      </c>
       <c r="BC7" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH7" t="n">
         <v>4.6</v>
@@ -2307,25 +2307,25 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BO7" t="n">
         <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ7" t="n">
         <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BS7" t="n">
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU7" t="n">
         <v>1.01</v>
@@ -2337,7 +2337,7 @@
         <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BY7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I9" t="n">
         <v>2.24</v>
@@ -2650,7 +2650,7 @@
         <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
         <v>1.29</v>
@@ -2659,13 +2659,13 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
         <v>1.61</v>
@@ -2683,7 +2683,7 @@
         <v>2.34</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W9" t="n">
         <v>1.33</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -2898,10 +2898,10 @@
         <v>1.62</v>
       </c>
       <c r="I10" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
         <v>4.8</v>
@@ -2922,7 +2922,7 @@
         <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
         <v>1.45</v>
@@ -2937,7 +2937,7 @@
         <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="W10" t="n">
         <v>1.17</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.54</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
         <v>2.72</v>
@@ -3167,19 +3167,19 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
         <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
         <v>2.62</v>
@@ -3212,10 +3212,10 @@
         <v>17</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE11" t="n">
         <v>29</v>
@@ -3224,7 +3224,7 @@
         <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
@@ -3236,7 +3236,7 @@
         <v>38</v>
       </c>
       <c r="AK11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL11" t="n">
         <v>36</v>
@@ -3251,52 +3251,52 @@
         <v>970</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>4.5</v>
       </c>
-      <c r="AY11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BA11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF11" t="n">
         <v>12.5</v>
@@ -3314,7 +3314,7 @@
         <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3344,7 +3344,7 @@
         <v>6.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -3421,13 +3421,13 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
         <v>1.61</v>
@@ -3496,7 +3496,7 @@
         <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="n">
         <v>10.5</v>
@@ -3505,19 +3505,19 @@
         <v>38</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ12" t="n">
         <v>4.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AU12" t="n">
         <v>3.7</v>
@@ -3526,7 +3526,7 @@
         <v>4.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="n">
         <v>4.1</v>
@@ -3538,7 +3538,7 @@
         <v>4.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB12" t="n">
         <v>4.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -3654,16 +3654,16 @@
         <v>2.84</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="H13" t="n">
         <v>2.12</v>
       </c>
       <c r="I13" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
         <v>4.8</v>
@@ -3675,13 +3675,13 @@
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
         <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
         <v>1.5</v>
@@ -3699,25 +3699,25 @@
         <v>2.46</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
         <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y13" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
         <v>42</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AC13" t="n">
         <v>11.5</v>
@@ -3726,16 +3726,16 @@
         <v>14.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF13" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AI13" t="n">
         <v>38</v>
@@ -3753,7 +3753,7 @@
         <v>70</v>
       </c>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
         <v>12.5</v>
@@ -3762,55 +3762,55 @@
         <v>4.7</v>
       </c>
       <c r="AQ13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR13" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AS13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT13" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AU13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC13" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC13" t="n">
+      <c r="BD13" t="n">
         <v>4.9</v>
       </c>
-      <c r="BD13" t="n">
-        <v>5</v>
-      </c>
       <c r="BE13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BH13" t="n">
         <v>4.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H14" t="n">
         <v>7.8</v>
       </c>
       <c r="I14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.33</v>
@@ -3935,10 +3935,10 @@
         <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R14" t="n">
         <v>1.47</v>
@@ -3953,7 +3953,7 @@
         <v>1.96</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W14" t="n">
         <v>3</v>
@@ -3974,7 +3974,7 @@
         <v>9</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
         <v>30</v>
@@ -3989,7 +3989,7 @@
         <v>10</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
         <v>120</v>
@@ -3998,7 +3998,7 @@
         <v>13.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL14" t="n">
         <v>34</v>
@@ -4016,13 +4016,13 @@
         <v>15</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AR14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS14" t="n">
         <v>11</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>12.5</v>
       </c>
       <c r="AT14" t="n">
         <v>8</v>
@@ -4031,10 +4031,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="AW14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AX14" t="n">
         <v>8</v>
@@ -4043,10 +4043,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB14" t="n">
         <v>11.5</v>
@@ -4055,16 +4055,16 @@
         <v>13.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BF14" t="n">
         <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH14" t="n">
         <v>4.5</v>
@@ -4109,7 +4109,7 @@
         <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BW14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.59</v>
       </c>
       <c r="G15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H15" t="n">
         <v>6.6</v>
@@ -4174,7 +4174,7 @@
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.39</v>
@@ -4195,7 +4195,7 @@
         <v>1.97</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
         <v>3.55</v>
@@ -4210,7 +4210,7 @@
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X15" t="n">
         <v>15.5</v>
@@ -4219,7 +4219,7 @@
         <v>22</v>
       </c>
       <c r="Z15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA15" t="n">
         <v>260</v>
@@ -4279,13 +4279,13 @@
         <v>8.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU15" t="n">
         <v>8</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="AW15" t="n">
         <v>8.199999999999999</v>
@@ -4300,7 +4300,7 @@
         <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB15" t="n">
         <v>13</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -4422,13 +4422,13 @@
         <v>6.2</v>
       </c>
       <c r="I16" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J16" t="n">
         <v>4.6</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.23</v>
@@ -4452,7 +4452,7 @@
         <v>1.64</v>
       </c>
       <c r="S16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T16" t="n">
         <v>1.65</v>
@@ -4461,52 +4461,52 @@
         <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W16" t="n">
         <v>2.74</v>
       </c>
       <c r="X16" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Y16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Z16" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AA16" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE16" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG16" t="n">
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
@@ -4518,61 +4518,61 @@
         <v>6.2</v>
       </c>
       <c r="AO16" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AY16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>4.6</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BA16" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.2</v>
+        <v>46</v>
       </c>
       <c r="BH16" t="n">
         <v>4.8</v>
@@ -4596,7 +4596,7 @@
         <v>4.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BP16" t="n">
         <v>9.800000000000001</v>
@@ -4614,7 +4614,7 @@
         <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -4670,25 +4670,25 @@
         <v>2.24</v>
       </c>
       <c r="G17" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H17" t="n">
         <v>3.2</v>
       </c>
       <c r="I17" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J17" t="n">
         <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
         <v>1.46</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
         <v>3.05</v>
@@ -4724,46 +4724,46 @@
         <v>13.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA17" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF17" t="n">
         <v>17</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>150</v>
@@ -4772,46 +4772,46 @@
         <v>30</v>
       </c>
       <c r="AO17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP17" t="n">
         <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR17" t="n">
         <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV17" t="n">
         <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="AX17" t="n">
         <v>11</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
         <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC17" t="n">
         <v>21</v>
@@ -4820,13 +4820,13 @@
         <v>34</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
         <v>19.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>38</v>
+        <v>4.7</v>
       </c>
       <c r="BH17" t="n">
         <v>3.2</v>
@@ -4850,7 +4850,7 @@
         <v>5.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP17" t="n">
         <v>19.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -4924,19 +4924,19 @@
         <v>1.91</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.38</v>
@@ -4963,16 +4963,16 @@
         <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U18" t="n">
         <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X18" t="n">
         <v>18</v>
@@ -4987,13 +4987,13 @@
         <v>110</v>
       </c>
       <c r="AB18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>65</v>
@@ -5035,25 +5035,25 @@
         <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS18" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AT18" t="n">
         <v>7.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV18" t="n">
         <v>13</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
         <v>8.199999999999999</v>
@@ -5062,7 +5062,7 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BB18" t="n">
         <v>17.5</v>
@@ -5071,16 +5071,16 @@
         <v>15.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BF18" t="n">
         <v>10.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH18" t="n">
         <v>3.6</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G19" t="n">
         <v>1.77</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.38</v>
@@ -5199,7 +5199,7 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
         <v>1.3</v>
@@ -5220,13 +5220,13 @@
         <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -5235,13 +5235,13 @@
         <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
         <v>13.5</v>
@@ -5253,13 +5253,13 @@
         <v>95</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AG19" t="n">
         <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>95</v>
@@ -5274,7 +5274,7 @@
         <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN19" t="n">
         <v>970</v>
@@ -5295,10 +5295,10 @@
         <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
         <v>1.01</v>
@@ -5307,13 +5307,13 @@
         <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY19" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
         <v>1.01</v>
@@ -5322,7 +5322,7 @@
         <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD19" t="n">
         <v>1.01</v>
@@ -5364,7 +5364,7 @@
         <v>14.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR19" t="n">
         <v>34</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.62</v>
       </c>
       <c r="G20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H20" t="n">
         <v>5.2</v>
@@ -5459,10 +5459,10 @@
         <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
         <v>1.44</v>
@@ -5474,13 +5474,13 @@
         <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V20" t="n">
         <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X20" t="n">
         <v>23</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="AE20" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
@@ -5516,22 +5516,22 @@
         <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ20" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AK20" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
         <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO20" t="n">
         <v>95</v>
@@ -5540,7 +5540,7 @@
         <v>14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR20" t="n">
         <v>1.01</v>
@@ -5555,7 +5555,7 @@
         <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
         <v>1.01</v>
@@ -5573,7 +5573,7 @@
         <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC20" t="n">
         <v>12</v>
@@ -5585,7 +5585,7 @@
         <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -5695,13 +5695,13 @@
         <v>5.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K21" t="n">
         <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -5716,7 +5716,7 @@
         <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R21" t="n">
         <v>1.37</v>
@@ -5731,13 +5731,13 @@
         <v>2.02</v>
       </c>
       <c r="V21" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W21" t="n">
         <v>2.22</v>
       </c>
       <c r="X21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y21" t="n">
         <v>22</v>
@@ -5749,16 +5749,16 @@
         <v>160</v>
       </c>
       <c r="AB21" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
         <v>25</v>
       </c>
       <c r="AE21" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF21" t="n">
         <v>13.5</v>
@@ -5770,7 +5770,7 @@
         <v>25</v>
       </c>
       <c r="AI21" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ21" t="n">
         <v>23</v>
@@ -5797,34 +5797,34 @@
         <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AT21" t="n">
         <v>6.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AX21" t="n">
         <v>8</v>
       </c>
       <c r="AY21" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BB21" t="n">
         <v>13.5</v>
@@ -5833,28 +5833,28 @@
         <v>13.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BH21" t="n">
         <v>3.55</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BJ21" t="n">
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
@@ -5866,7 +5866,7 @@
         <v>4.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BP21" t="n">
         <v>12</v>
@@ -5884,7 +5884,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -5940,16 +5940,16 @@
         <v>2.74</v>
       </c>
       <c r="G22" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="H22" t="n">
         <v>2.88</v>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J22" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
         <v>3.5</v>
@@ -5964,34 +5964,34 @@
         <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U22" t="n">
         <v>2.08</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.06</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W22" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
         <v>11.5</v>
@@ -6003,7 +6003,7 @@
         <v>65</v>
       </c>
       <c r="AB22" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC22" t="n">
         <v>8</v>
@@ -6033,13 +6033,13 @@
         <v>50</v>
       </c>
       <c r="AL22" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AM22" t="n">
         <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AO22" t="n">
         <v>34</v>
@@ -6054,7 +6054,7 @@
         <v>15.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="AT22" t="n">
         <v>9</v>
@@ -6066,7 +6066,7 @@
         <v>10.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX22" t="n">
         <v>15.5</v>
@@ -6078,25 +6078,25 @@
         <v>15.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BC22" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.9</v>
+        <v>22</v>
       </c>
       <c r="BH22" t="n">
         <v>3.3</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K23" t="n">
         <v>4.9</v>
@@ -6215,7 +6215,7 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="O23" t="n">
         <v>1.15</v>
@@ -6230,7 +6230,7 @@
         <v>1.75</v>
       </c>
       <c r="S23" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T23" t="n">
         <v>1.51</v>
@@ -6245,112 +6245,112 @@
         <v>2.1</v>
       </c>
       <c r="X23" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z23" t="n">
         <v>40</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>46</v>
       </c>
       <c r="AA23" t="n">
         <v>95</v>
       </c>
       <c r="AB23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AC23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD23" t="n">
         <v>22</v>
       </c>
       <c r="AE23" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AF23" t="n">
         <v>19.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
         <v>46</v>
       </c>
       <c r="AJ23" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>29</v>
       </c>
       <c r="AM23" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN23" t="n">
         <v>6.8</v>
       </c>
       <c r="AO23" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH23" t="n">
         <v>5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -6505,10 +6505,10 @@
         <v>23</v>
       </c>
       <c r="Z24" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB24" t="n">
         <v>17</v>
@@ -6517,10 +6517,10 @@
         <v>12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AF24" t="n">
         <v>21</v>
@@ -6532,79 +6532,79 @@
         <v>15.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AJ24" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK24" t="n">
         <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AM24" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN24" t="n">
         <v>12</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AR24" t="n">
         <v>5.1</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG24" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>4.8</v>
       </c>
       <c r="BH24" t="n">
         <v>4.8</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -6699,16 +6699,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="G25" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="H25" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="I25" t="n">
-        <v>2.98</v>
+        <v>2.66</v>
       </c>
       <c r="J25" t="n">
         <v>3.85</v>
@@ -6729,106 +6729,106 @@
         <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="Q25" t="n">
         <v>1.51</v>
       </c>
       <c r="R25" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="S25" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T25" t="n">
         <v>1.5</v>
       </c>
       <c r="U25" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.51</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.58</v>
       </c>
       <c r="X25" t="n">
         <v>34</v>
       </c>
       <c r="Y25" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB25" t="n">
         <v>22</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>18.5</v>
       </c>
       <c r="AC25" t="n">
         <v>12.5</v>
       </c>
       <c r="AD25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG25" t="n">
         <v>16</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>15.5</v>
       </c>
       <c r="AH25" t="n">
         <v>18</v>
       </c>
       <c r="AI25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ25" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AK25" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL25" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM25" t="n">
         <v>65</v>
       </c>
       <c r="AN25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO25" t="n">
         <v>15.5</v>
       </c>
-      <c r="AO25" t="n">
-        <v>18</v>
-      </c>
       <c r="AP25" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AQ25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT25" t="n">
         <v>3.55</v>
       </c>
-      <c r="AR25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AU25" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AX25" t="n">
         <v>3.65</v>
@@ -6837,82 +6837,82 @@
         <v>3.35</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BB25" t="n">
         <v>3.9</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BD25" t="n">
         <v>3.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BH25" t="n">
         <v>4.7</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ25" t="n">
         <v>8.6</v>
       </c>
       <c r="BK25" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="BN25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO25" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP25" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS25" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT25" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BU25" t="n">
         <v>4</v>
       </c>
       <c r="BV25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BW25" t="n">
         <v>6.8</v>
       </c>
       <c r="BX25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY25" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -7213,13 +7213,13 @@
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7255,7 +7255,7 @@
         <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -7461,19 +7461,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="G28" t="n">
         <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7485,13 +7485,13 @@
         <v>1.02</v>
       </c>
       <c r="N28" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="O28" t="n">
         <v>1.12</v>
       </c>
       <c r="P28" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q28" t="n">
         <v>1.11</v>
@@ -7500,7 +7500,7 @@
         <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -7721,13 +7721,13 @@
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7766,7 +7766,7 @@
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -7969,19 +7969,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G30" t="n">
         <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G31" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="H31" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I31" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -8247,94 +8247,94 @@
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="O31" t="n">
         <v>1.25</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="T31" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U31" t="n">
         <v>2.24</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="X31" t="n">
         <v>21</v>
       </c>
       <c r="Y31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z31" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA31" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB31" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF31" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AG31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH31" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI31" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AJ31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK31" t="n">
         <v>27</v>
       </c>
-      <c r="AK31" t="n">
-        <v>23</v>
-      </c>
       <c r="AL31" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM31" t="n">
         <v>90</v>
       </c>
       <c r="AN31" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP31" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR31" t="n">
         <v>1.03</v>
@@ -8343,7 +8343,7 @@
         <v>1.03</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AU31" t="n">
         <v>1.03</v>
@@ -8367,7 +8367,7 @@
         <v>1.03</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BC31" t="n">
         <v>1.03</v>
@@ -8379,7 +8379,7 @@
         <v>1.03</v>
       </c>
       <c r="BF31" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG31" t="n">
         <v>9.199999999999999</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -8624,10 +8624,10 @@
         <v>21</v>
       </c>
       <c r="BC32" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="BD32" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BE32" t="n">
         <v>12</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G2" t="n">
         <v>2.96</v>
@@ -887,10 +887,10 @@
         <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R2" t="n">
         <v>1.64</v>
@@ -914,7 +914,7 @@
         <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z2" t="n">
         <v>21</v>
@@ -944,7 +944,7 @@
         <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AJ2" t="n">
         <v>140</v>
@@ -959,7 +959,7 @@
         <v>250</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
         <v>13.5</v>
@@ -1019,10 +1019,10 @@
         <v>11.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.800000000000001</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
@@ -1043,7 +1043,7 @@
         <v>5</v>
       </c>
       <c r="BP2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ2" t="n">
         <v>6.6</v>
@@ -1073,14 +1073,14 @@
         <v>7</v>
       </c>
       <c r="BZ2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="I3" t="n">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AB3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AF3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD3" t="n">
         <v>40</v>
       </c>
-      <c r="AG3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BH3" t="n">
         <v>4.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>8</v>
       </c>
-      <c r="BN3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
+      <c r="BT3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY3" t="n">
         <v>7</v>
       </c>
-      <c r="BT3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>27</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BZ3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="CA3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -1365,73 +1365,73 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="G4" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>1.27</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V4" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AA4" t="n">
         <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1443,16 +1443,16 @@
         <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AG4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AH4" t="n">
         <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1461,7 +1461,7 @@
         <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1470,76 +1470,76 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT4" t="n">
         <v>4</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AU4" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AY4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.52</v>
+        <v>3.55</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="BF4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI4" t="n">
         <v>3.25</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
         <v>970</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM4" t="n">
         <v>1.01</v>
@@ -1548,34 +1548,34 @@
         <v>970</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BP4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -1619,106 +1619,106 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>2.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="S5" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN5" t="n">
         <v>1000</v>
@@ -1727,61 +1727,61 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2130,22 @@
         <v>1.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J7" t="n">
         <v>4.3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
@@ -2160,7 +2160,7 @@
         <v>2.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R7" t="n">
         <v>1.46</v>
@@ -2175,10 +2175,10 @@
         <v>2.06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X7" t="n">
         <v>24</v>
@@ -2202,13 +2202,13 @@
         <v>28</v>
       </c>
       <c r="AE7" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="n">
         <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>25</v>
@@ -2220,7 +2220,7 @@
         <v>18.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AL7" t="n">
         <v>40</v>
@@ -2235,67 +2235,67 @@
         <v>100</v>
       </c>
       <c r="AP7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH7" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BI7" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK7" t="n">
         <v>1.01</v>
@@ -2310,10 +2310,10 @@
         <v>5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ7" t="n">
         <v>1.01</v>
@@ -2325,13 +2325,13 @@
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU7" t="n">
         <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BW7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>3.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
         <v>4.5</v>
@@ -2411,7 +2411,7 @@
         <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q8" t="n">
         <v>1.56</v>
@@ -2492,55 +2492,55 @@
         <v>6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS8" t="n">
         <v>6.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU8" t="n">
         <v>4.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW8" t="n">
         <v>6</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA8" t="n">
         <v>6.2</v>
       </c>
       <c r="BB8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD8" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>6</v>
       </c>
       <c r="BE8" t="n">
         <v>6.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH8" t="n">
         <v>4.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O9" t="n">
         <v>1.21</v>
@@ -2680,7 +2680,7 @@
         <v>1.57</v>
       </c>
       <c r="U9" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V9" t="n">
         <v>1.81</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="H10" t="n">
         <v>1.62</v>
@@ -2901,7 +2901,7 @@
         <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
         <v>4.8</v>
@@ -2913,13 +2913,13 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
         <v>1.67</v>
@@ -2931,7 +2931,7 @@
         <v>2.68</v>
       </c>
       <c r="T10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U10" t="n">
         <v>2.08</v>
@@ -2940,7 +2940,7 @@
         <v>2.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X10" t="n">
         <v>24</v>
@@ -2949,7 +2949,7 @@
         <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA10" t="n">
         <v>21</v>
@@ -3006,31 +3006,31 @@
         <v>3.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AT10" t="n">
         <v>3.65</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AV10" t="n">
         <v>3.15</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AY10" t="n">
         <v>3.65</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB10" t="n">
         <v>4.1</v>
@@ -3042,7 +3042,7 @@
         <v>4</v>
       </c>
       <c r="BE10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF10" t="n">
         <v>4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -3149,55 +3149,55 @@
         <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I11" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.28</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="U11" t="n">
         <v>2.72</v>
       </c>
       <c r="V11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X11" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Y11" t="n">
         <v>970</v>
@@ -3212,10 +3212,10 @@
         <v>17</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
         <v>29</v>
@@ -3224,25 +3224,25 @@
         <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>36</v>
       </c>
       <c r="AJ11" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AK11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN11" t="n">
         <v>970</v>
@@ -3251,52 +3251,52 @@
         <v>970</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY11" t="n">
         <v>4.9</v>
       </c>
-      <c r="AY11" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF11" t="n">
         <v>12.5</v>
@@ -3305,58 +3305,58 @@
         <v>14.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ11" t="n">
         <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN11" t="n">
         <v>6.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
         <v>6.4</v>
       </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.19</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>2.12</v>
       </c>
       <c r="I13" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="H14" t="n">
         <v>7.8</v>
       </c>
       <c r="I14" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K14" t="n">
         <v>5.3</v>
@@ -3929,40 +3929,40 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S14" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="U14" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="X14" t="n">
         <v>23</v>
       </c>
       <c r="Y14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Z14" t="n">
         <v>85</v>
@@ -3980,7 +3980,7 @@
         <v>30</v>
       </c>
       <c r="AE14" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AF14" t="n">
         <v>9.199999999999999</v>
@@ -3992,7 +3992,7 @@
         <v>29</v>
       </c>
       <c r="AI14" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ14" t="n">
         <v>13.5</v>
@@ -4040,7 +4040,7 @@
         <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
         <v>8.199999999999999</v>
@@ -4052,7 +4052,7 @@
         <v>11.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD14" t="n">
         <v>8.6</v>
@@ -4064,25 +4064,25 @@
         <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="n">
         <v>4.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BJ14" t="n">
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BL14" t="n">
         <v>160</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BN14" t="n">
         <v>4.5</v>
@@ -4094,31 +4094,31 @@
         <v>10.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BR14" t="n">
         <v>27</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BT14" t="n">
         <v>13</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV14" t="n">
         <v>70</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BX14" t="n">
         <v>75</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.39</v>
@@ -4183,19 +4183,19 @@
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
         <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q15" t="n">
         <v>1.97</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
         <v>3.55</v>
@@ -4210,13 +4210,13 @@
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="X15" t="n">
         <v>15.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Z15" t="n">
         <v>65</v>
@@ -4231,13 +4231,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AE15" t="n">
         <v>130</v>
       </c>
       <c r="AF15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG15" t="n">
         <v>9.800000000000001</v>
@@ -4252,7 +4252,7 @@
         <v>16.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL15" t="n">
         <v>55</v>
@@ -4273,10 +4273,10 @@
         <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
         <v>6.8</v>
@@ -4288,7 +4288,7 @@
         <v>19</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX15" t="n">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB15" t="n">
         <v>13</v>
@@ -4312,13 +4312,13 @@
         <v>27</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH15" t="n">
         <v>3.95</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -4455,10 +4455,10 @@
         <v>2.26</v>
       </c>
       <c r="T16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
         <v>1.16</v>
@@ -4467,13 +4467,13 @@
         <v>2.74</v>
       </c>
       <c r="X16" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Y16" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Z16" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA16" t="n">
         <v>190</v>
@@ -4482,7 +4482,7 @@
         <v>14.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD16" t="n">
         <v>32</v>
@@ -4503,13 +4503,13 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AK16" t="n">
         <v>18</v>
       </c>
       <c r="AL16" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AM16" t="n">
         <v>100</v>
@@ -4521,58 +4521,58 @@
         <v>80</v>
       </c>
       <c r="AP16" t="n">
-        <v>19.5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AY16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>19</v>
       </c>
       <c r="BE16" t="n">
         <v>5.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>46</v>
+        <v>5.7</v>
       </c>
       <c r="BH16" t="n">
         <v>4.8</v>
@@ -4596,13 +4596,13 @@
         <v>4.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BP16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4614,7 +4614,7 @@
         <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -4778,19 +4778,19 @@
         <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR17" t="n">
         <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
         <v>11</v>
@@ -4802,7 +4802,7 @@
         <v>11</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
         <v>15</v>
@@ -4826,7 +4826,7 @@
         <v>19.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.7</v>
+        <v>38</v>
       </c>
       <c r="BH17" t="n">
         <v>3.2</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5017,7 @@
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM18" t="n">
         <v>120</v>
@@ -5062,7 +5062,7 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB18" t="n">
         <v>17.5</v>
@@ -5074,7 +5074,7 @@
         <v>5.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF18" t="n">
         <v>10.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G19" t="n">
         <v>1.77</v>
       </c>
       <c r="H19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
         <v>6.2</v>
@@ -5208,13 +5208,13 @@
         <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R19" t="n">
         <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
         <v>1.86</v>
@@ -5226,7 +5226,7 @@
         <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -5262,7 +5262,7 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ19" t="n">
         <v>970</v>
@@ -5340,7 +5340,7 @@
         <v>4.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ19" t="n">
         <v>12.5</v>
@@ -5379,7 +5379,7 @@
         <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G20" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="H20" t="n">
         <v>5.2</v>
@@ -5453,34 +5453,34 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
         <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V20" t="n">
         <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="X20" t="n">
         <v>23</v>
@@ -5501,40 +5501,40 @@
         <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE20" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
         <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK20" t="n">
         <v>20</v>
       </c>
-      <c r="AK20" t="n">
-        <v>21</v>
-      </c>
       <c r="AL20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM20" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO20" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP20" t="n">
         <v>14</v>
@@ -5549,10 +5549,10 @@
         <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV20" t="n">
         <v>1.01</v>
@@ -5561,7 +5561,7 @@
         <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY20" t="n">
         <v>7.6</v>
@@ -5585,7 +5585,7 @@
         <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BG20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G21" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H21" t="n">
         <v>4.9</v>
@@ -5695,7 +5695,7 @@
         <v>5.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K21" t="n">
         <v>4.3</v>
@@ -5707,19 +5707,19 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O21" t="n">
         <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
         <v>3.25</v>
@@ -5728,13 +5728,13 @@
         <v>1.84</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V21" t="n">
         <v>1.22</v>
       </c>
       <c r="W21" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X21" t="n">
         <v>19</v>
@@ -5749,7 +5749,7 @@
         <v>160</v>
       </c>
       <c r="AB21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC21" t="n">
         <v>11</v>
@@ -5767,10 +5767,10 @@
         <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ21" t="n">
         <v>23</v>
@@ -5779,10 +5779,10 @@
         <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM21" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN21" t="n">
         <v>13.5</v>
@@ -5800,28 +5800,28 @@
         <v>3.95</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT21" t="n">
         <v>6.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV21" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AW21" t="n">
         <v>4.1</v>
       </c>
       <c r="AX21" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA21" t="n">
         <v>4.1</v>
@@ -5839,7 +5839,7 @@
         <v>4.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG21" t="n">
         <v>4.1</v>
@@ -5848,13 +5848,13 @@
         <v>3.55</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ21" t="n">
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
@@ -5866,7 +5866,7 @@
         <v>4.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="BP21" t="n">
         <v>12</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G22" t="n">
         <v>2.82</v>
       </c>
       <c r="H22" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I22" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J22" t="n">
         <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L22" t="n">
         <v>1.43</v>
@@ -5973,10 +5973,10 @@
         <v>2.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T22" t="n">
         <v>1.83</v>
@@ -5985,7 +5985,7 @@
         <v>2.08</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
         <v>1.55</v>
@@ -6003,10 +6003,10 @@
         <v>65</v>
       </c>
       <c r="AB22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD22" t="n">
         <v>13.5</v>
@@ -6066,7 +6066,7 @@
         <v>10.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX22" t="n">
         <v>15.5</v>
@@ -6081,19 +6081,19 @@
         <v>38</v>
       </c>
       <c r="BB22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC22" t="n">
         <v>7</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>6.6</v>
       </c>
       <c r="BD22" t="n">
         <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG22" t="n">
         <v>22</v>
@@ -6102,19 +6102,19 @@
         <v>3.3</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ22" t="n">
         <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN22" t="n">
         <v>6</v>
@@ -6129,7 +6129,7 @@
         <v>7.2</v>
       </c>
       <c r="BR22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS22" t="n">
         <v>8</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
         <v>4.9</v>
@@ -6224,13 +6224,13 @@
         <v>2.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R23" t="n">
         <v>1.75</v>
       </c>
       <c r="S23" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="T23" t="n">
         <v>1.51</v>
@@ -6257,7 +6257,7 @@
         <v>95</v>
       </c>
       <c r="AB23" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AC23" t="n">
         <v>12</v>
@@ -6275,7 +6275,7 @@
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI23" t="n">
         <v>46</v>
@@ -6299,58 +6299,58 @@
         <v>26</v>
       </c>
       <c r="AP23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS23" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AT23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE23" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC23" t="n">
+      <c r="BF23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG23" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>6.4</v>
       </c>
       <c r="BH23" t="n">
         <v>5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -6445,79 +6445,79 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="G24" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="H24" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
         <v>4.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
         <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
         <v>1.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="S24" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T24" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="U24" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="V24" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="X24" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z24" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA24" t="n">
         <v>50</v>
       </c>
       <c r="AB24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>34</v>
@@ -6529,136 +6529,136 @@
         <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ24" t="n">
         <v>38</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL24" t="n">
         <v>34</v>
       </c>
       <c r="AM24" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN24" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AQ24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE24" t="n">
         <v>4.8</v>
       </c>
-      <c r="AR24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT24" t="n">
+      <c r="BF24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS24" t="n">
         <v>4.5</v>
       </c>
-      <c r="AU24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV24" t="n">
+      <c r="BT24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW24" t="n">
         <v>4.4</v>
       </c>
-      <c r="AW24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG24" t="n">
+      <c r="BX24" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY24" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>7.6</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G25" t="n">
         <v>2.96</v>
@@ -6729,16 +6729,16 @@
         <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R25" t="n">
         <v>1.63</v>
       </c>
       <c r="S25" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T25" t="n">
         <v>1.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
         <v>1.59</v>
       </c>
       <c r="G26" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H26" t="n">
         <v>3.7</v>
@@ -6977,7 +6977,7 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>2.42</v>
+        <v>1.1</v>
       </c>
       <c r="O26" t="n">
         <v>1.12</v>
@@ -7004,7 +7004,7 @@
         <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -7213,13 +7213,13 @@
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -7721,13 +7721,13 @@
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -8226,19 +8226,19 @@
         <v>2.16</v>
       </c>
       <c r="G31" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I31" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -8247,142 +8247,142 @@
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
         <v>1.25</v>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="T31" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U31" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="X31" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
         <v>4.7</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-25 11:50:03</t>
+          <t>2026-06-25 14:07:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G2" t="n">
         <v>2.96</v>
@@ -977,7 +977,7 @@
         <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
         <v>8.199999999999999</v>
@@ -998,16 +998,16 @@
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>26</v>
       </c>
       <c r="BC2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
         <v>28</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.32</v>
@@ -1144,7 +1144,7 @@
         <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R3" t="n">
         <v>1.47</v>
@@ -1156,7 +1156,7 @@
         <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V3" t="n">
         <v>2.08</v>
@@ -1249,10 +1249,10 @@
         <v>15</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BB3" t="n">
         <v>8.199999999999999</v>
@@ -1264,7 +1264,7 @@
         <v>40</v>
       </c>
       <c r="BE3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>7.4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G4" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.27</v>
@@ -1389,34 +1389,34 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="Q4" t="n">
         <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="U4" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
         <v>3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
         <v>26</v>
@@ -1425,7 +1425,7 @@
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
         <v>970</v>
@@ -1446,7 +1446,7 @@
         <v>90</v>
       </c>
       <c r="AG4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AH4" t="n">
         <v>26</v>
@@ -1458,10 +1458,10 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1473,22 +1473,22 @@
         <v>6.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="AS4" t="n">
         <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV4" t="n">
         <v>7.4</v>
@@ -1497,31 +1497,31 @@
         <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="BG4" t="n">
         <v>4.6</v>
@@ -1530,7 +1530,7 @@
         <v>4.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ4" t="n">
         <v>970</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.66</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="H5" t="n">
         <v>3.9</v>
@@ -1631,7 +1631,7 @@
         <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
         <v>6.4</v>
@@ -1649,7 +1649,7 @@
         <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
         <v>1.38</v>
@@ -1658,19 +1658,19 @@
         <v>1.87</v>
       </c>
       <c r="S5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="T5" t="n">
         <v>1.46</v>
       </c>
       <c r="U5" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V5" t="n">
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X5" t="n">
         <v>46</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -1873,106 +1873,106 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.97</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>1.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>1.23</v>
+        <v>2.78</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN6" t="n">
         <v>1000</v>
@@ -1981,64 +1981,64 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2053,7 +2053,7 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H7" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -2151,61 +2151,61 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="X7" t="n">
         <v>24</v>
       </c>
       <c r="Y7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AB7" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
@@ -2214,85 +2214,85 @@
         <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AK7" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AL7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
         <v>130</v>
       </c>
       <c r="AN7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX7" t="n">
         <v>8</v>
       </c>
-      <c r="AO7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AY7" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD7" t="n">
+      <c r="BE7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF7" t="n">
         <v>5.8</v>
       </c>
-      <c r="BE7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH7" t="n">
         <v>4.7</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ7" t="n">
         <v>12.5</v>
@@ -2310,25 +2310,25 @@
         <v>5</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS7" t="n">
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BV7" t="n">
         <v>65</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -2381,76 +2381,76 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="I8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T8" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
         <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
         <v>14</v>
@@ -2459,13 +2459,13 @@
         <v>36</v>
       </c>
       <c r="AF8" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI8" t="n">
         <v>44</v>
@@ -2474,7 +2474,7 @@
         <v>48</v>
       </c>
       <c r="AK8" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
         <v>42</v>
@@ -2483,128 +2483,128 @@
         <v>65</v>
       </c>
       <c r="AN8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>15</v>
       </c>
-      <c r="AO8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AR8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN8" t="n">
         <v>5.9</v>
       </c>
-      <c r="AS8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV8" t="n">
+      <c r="BO8" t="n">
         <v>5</v>
       </c>
-      <c r="AW8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX8" t="n">
+      <c r="BP8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU8" t="n">
         <v>5.7</v>
       </c>
-      <c r="AY8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
+      <c r="BV8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>8.4</v>
       </c>
-      <c r="BN8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>7</v>
-      </c>
       <c r="BZ8" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="H9" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="I9" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.29</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="U9" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="W9" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AB9" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AC9" t="n">
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AG9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH9" t="n">
         <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AK9" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR9" t="n">
         <v>12</v>
       </c>
-      <c r="AP9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AS9" t="n">
-        <v>5.5</v>
+        <v>19</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.1</v>
+        <v>16.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.2</v>
+        <v>15.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="BD9" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.6</v>
+        <v>22</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH9" t="n">
         <v>4.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN9" t="n">
         <v>8</v>
       </c>
-      <c r="BN9" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BO9" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BP9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BQ9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="CA9" t="n">
         <v>6.6</v>
       </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>5.9</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -2892,55 +2892,55 @@
         <v>4.9</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="I10" t="n">
         <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
         <v>2.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
         <v>24</v>
@@ -2955,7 +2955,7 @@
         <v>21</v>
       </c>
       <c r="AB10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC10" t="n">
         <v>12</v>
@@ -2970,7 +2970,7 @@
         <v>55</v>
       </c>
       <c r="AG10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH10" t="n">
         <v>23</v>
@@ -2979,140 +2979,140 @@
         <v>38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO10" t="n">
         <v>10.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.6</v>
+        <v>16.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="AR10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU10" t="n">
         <v>3.25</v>
       </c>
-      <c r="AS10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="AV10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW10" t="n">
         <v>3.65</v>
       </c>
-      <c r="AU10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AX10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA10" t="n">
         <v>3.95</v>
       </c>
-      <c r="AY10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BB10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="BH10" t="n">
         <v>4.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BN10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>9.4</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT10" t="n">
         <v>4.6</v>
       </c>
-      <c r="BP10" t="n">
-        <v>44</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BU10" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BV10" t="n">
         <v>11.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BX10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY10" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="I11" t="n">
         <v>2.94</v>
       </c>
       <c r="J11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.28</v>
@@ -3167,34 +3167,34 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.57</v>
       </c>
       <c r="S11" t="n">
         <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="U11" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="V11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W11" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
         <v>28</v>
@@ -3206,13 +3206,13 @@
         <v>25</v>
       </c>
       <c r="AA11" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB11" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>70</v>
       </c>
       <c r="AD11" t="n">
         <v>14</v>
@@ -3221,7 +3221,7 @@
         <v>29</v>
       </c>
       <c r="AF11" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AG11" t="n">
         <v>13.5</v>
@@ -3251,52 +3251,52 @@
         <v>970</v>
       </c>
       <c r="AP11" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR11" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU11" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE11" t="n">
         <v>5.9</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6.6</v>
       </c>
       <c r="BF11" t="n">
         <v>12.5</v>
@@ -3305,28 +3305,28 @@
         <v>14.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ11" t="n">
         <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN11" t="n">
         <v>6.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
@@ -3344,19 +3344,19 @@
         <v>6.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -3397,85 +3397,85 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R12" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="V12" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="X12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB12" t="n">
         <v>14.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG12" t="n">
         <v>12.5</v>
@@ -3484,143 +3484,143 @@
         <v>18</v>
       </c>
       <c r="AI12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
         <v>75</v>
       </c>
       <c r="AN12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT12" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4</v>
-      </c>
       <c r="AU12" t="n">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="BA12" t="n">
         <v>5</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="BC12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH12" t="n">
         <v>4.3</v>
       </c>
-      <c r="BD12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BI12" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR12" t="n">
         <v>25</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BT12" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="BV12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>18</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -3654,13 +3654,13 @@
         <v>2.84</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
@@ -3675,13 +3675,13 @@
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
         <v>1.5</v>
@@ -3699,16 +3699,16 @@
         <v>2.46</v>
       </c>
       <c r="V13" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
         <v>32</v>
       </c>
       <c r="Y13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z13" t="n">
         <v>21</v>
@@ -3723,7 +3723,7 @@
         <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
         <v>24</v>
@@ -3759,58 +3759,58 @@
         <v>12.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AV13" t="n">
         <v>4</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC13" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC13" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BH13" t="n">
         <v>4.8</v>
@@ -3852,7 +3852,7 @@
         <v>6.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="BV13" t="n">
         <v>16.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.33</v>
@@ -3929,7 +3929,7 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
         <v>1.24</v>
@@ -3938,13 +3938,13 @@
         <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R14" t="n">
         <v>1.49</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T14" t="n">
         <v>1.91</v>
@@ -3956,16 +3956,16 @@
         <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="X14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z14" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA14" t="n">
         <v>290</v>
@@ -3974,10 +3974,10 @@
         <v>9</v>
       </c>
       <c r="AC14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE14" t="n">
         <v>120</v>
@@ -3986,10 +3986,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
         <v>110</v>
@@ -3998,7 +3998,7 @@
         <v>13.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL14" t="n">
         <v>34</v>
@@ -4010,43 +4010,43 @@
         <v>6.8</v>
       </c>
       <c r="AO14" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AP14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS14" t="n">
         <v>15</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR14" t="n">
+      <c r="AT14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU14" t="n">
         <v>10</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AV14" t="n">
         <v>25</v>
       </c>
       <c r="AW14" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB14" t="n">
         <v>11.5</v>
@@ -4055,16 +4055,16 @@
         <v>13</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BF14" t="n">
         <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH14" t="n">
         <v>4.5</v>
@@ -4076,13 +4076,13 @@
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BL14" t="n">
         <v>160</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BN14" t="n">
         <v>4.5</v>
@@ -4091,7 +4091,7 @@
         <v>3.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ14" t="n">
         <v>3.7</v>
@@ -4100,25 +4100,25 @@
         <v>27</v>
       </c>
       <c r="BS14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BT14" t="n">
         <v>13</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV14" t="n">
         <v>70</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BX14" t="n">
         <v>75</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
@@ -4273,7 +4273,7 @@
         <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS15" t="n">
         <v>9</v>
@@ -4300,7 +4300,7 @@
         <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BB15" t="n">
         <v>13</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>1.53</v>
       </c>
       <c r="G16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I16" t="n">
         <v>7.2</v>
@@ -4428,7 +4428,7 @@
         <v>4.6</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.23</v>
@@ -4437,40 +4437,40 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O16" t="n">
         <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
         <v>1.16</v>
       </c>
       <c r="W16" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X16" t="n">
         <v>29</v>
       </c>
       <c r="Y16" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Z16" t="n">
         <v>70</v>
@@ -4497,7 +4497,7 @@
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI16" t="n">
         <v>80</v>
@@ -4509,7 +4509,7 @@
         <v>18</v>
       </c>
       <c r="AL16" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM16" t="n">
         <v>100</v>
@@ -4521,16 +4521,16 @@
         <v>80</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.3</v>
+        <v>3.75</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -4539,13 +4539,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY16" t="n">
         <v>8.800000000000001</v>
@@ -4554,25 +4554,25 @@
         <v>4.8</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BD16" t="n">
-        <v>19</v>
+        <v>5.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="BH16" t="n">
         <v>4.8</v>
@@ -4602,7 +4602,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4614,7 +4614,7 @@
         <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -4667,28 +4667,28 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G17" t="n">
         <v>2.54</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I17" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
         <v>1.46</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
         <v>3.05</v>
@@ -4700,7 +4700,7 @@
         <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
         <v>1.26</v>
@@ -4736,7 +4736,7 @@
         <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
         <v>17</v>
@@ -4751,19 +4751,19 @@
         <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM17" t="n">
         <v>150</v>
@@ -4775,61 +4775,61 @@
         <v>60</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR17" t="n">
         <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.6</v>
+        <v>34</v>
       </c>
       <c r="AX17" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>4.8</v>
       </c>
       <c r="BD17" t="n">
         <v>34</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG17" t="n">
         <v>38</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI17" t="n">
         <v>2.56</v>
@@ -4838,7 +4838,7 @@
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4853,16 +4853,16 @@
         <v>4.1</v>
       </c>
       <c r="BP17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT17" t="n">
         <v>6.8</v>
@@ -4874,13 +4874,13 @@
         <v>32</v>
       </c>
       <c r="BW17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -4924,37 +4924,37 @@
         <v>1.91</v>
       </c>
       <c r="G18" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H18" t="n">
         <v>3.95</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R18" t="n">
         <v>1.36</v>
@@ -4963,16 +4963,16 @@
         <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
         <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="X18" t="n">
         <v>18</v>
@@ -5017,7 +5017,7 @@
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
         <v>120</v>
@@ -5044,7 +5044,7 @@
         <v>7.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
         <v>13</v>
@@ -5053,7 +5053,7 @@
         <v>5.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AY18" t="n">
         <v>8.199999999999999</v>
@@ -5062,7 +5062,7 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB18" t="n">
         <v>17.5</v>
@@ -5074,7 +5074,7 @@
         <v>5.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF18" t="n">
         <v>10.5</v>
@@ -5086,7 +5086,7 @@
         <v>3.6</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ18" t="n">
         <v>10</v>
@@ -5104,7 +5104,7 @@
         <v>5</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP18" t="n">
         <v>15</v>
@@ -5122,7 +5122,7 @@
         <v>7.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BV18" t="n">
         <v>36</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G19" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I19" t="n">
         <v>6.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
         <v>4.4</v>
@@ -5199,7 +5199,7 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
         <v>1.3</v>
@@ -5208,25 +5208,25 @@
         <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V19" t="n">
         <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -5235,7 +5235,7 @@
         <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
@@ -5259,7 +5259,7 @@
         <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
         <v>90</v>
@@ -5277,7 +5277,7 @@
         <v>140</v>
       </c>
       <c r="AN19" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AO19" t="n">
         <v>110</v>
@@ -5298,7 +5298,7 @@
         <v>7.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV19" t="n">
         <v>1.01</v>
@@ -5313,7 +5313,7 @@
         <v>7.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA19" t="n">
         <v>1.01</v>
@@ -5322,7 +5322,7 @@
         <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
         <v>1.01</v>
@@ -5340,13 +5340,13 @@
         <v>4.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ19" t="n">
         <v>12.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL19" t="n">
         <v>160</v>
@@ -5358,25 +5358,25 @@
         <v>5.1</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BP19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BR19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS19" t="n">
         <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV19" t="n">
         <v>60</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -5432,16 +5432,16 @@
         <v>1.61</v>
       </c>
       <c r="G20" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I20" t="n">
         <v>6.2</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
         <v>4.7</v>
@@ -5453,13 +5453,13 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
         <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
         <v>1.67</v>
@@ -5468,19 +5468,19 @@
         <v>1.47</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T20" t="n">
         <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V20" t="n">
         <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X20" t="n">
         <v>23</v>
@@ -5537,10 +5537,10 @@
         <v>90</v>
       </c>
       <c r="AP20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
         <v>1.01</v>
@@ -5561,19 +5561,19 @@
         <v>1.01</v>
       </c>
       <c r="AX20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY20" t="n">
         <v>8.4</v>
       </c>
-      <c r="AY20" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
         <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC20" t="n">
         <v>12</v>
@@ -5585,13 +5585,13 @@
         <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG20" t="n">
         <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI20" t="n">
         <v>3.05</v>
@@ -5600,13 +5600,13 @@
         <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BN20" t="n">
         <v>4.5</v>
@@ -5618,31 +5618,31 @@
         <v>11</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BT20" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H21" t="n">
         <v>4.9</v>
@@ -5695,10 +5695,10 @@
         <v>5.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.32</v>
@@ -5707,7 +5707,7 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
         <v>1.3</v>
@@ -5722,19 +5722,19 @@
         <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
         <v>1.22</v>
       </c>
       <c r="W21" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X21" t="n">
         <v>19</v>
@@ -5749,10 +5749,10 @@
         <v>160</v>
       </c>
       <c r="AB21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD21" t="n">
         <v>25</v>
@@ -5776,7 +5776,7 @@
         <v>23</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
         <v>42</v>
@@ -5785,10 +5785,10 @@
         <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO21" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP21" t="n">
         <v>11.5</v>
@@ -5797,70 +5797,70 @@
         <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV21" t="n">
         <v>15</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY21" t="n">
         <v>9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB21" t="n">
         <v>13.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
         <v>9.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH21" t="n">
         <v>3.55</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="BJ21" t="n">
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN21" t="n">
         <v>4.4</v>
@@ -5878,10 +5878,10 @@
         <v>27</v>
       </c>
       <c r="BS21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU21" t="n">
         <v>6.8</v>
@@ -5896,7 +5896,7 @@
         <v>55</v>
       </c>
       <c r="BY21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -5940,43 +5940,43 @@
         <v>2.78</v>
       </c>
       <c r="G22" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="H22" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="I22" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
         <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
         <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
         <v>1.83</v>
@@ -5988,10 +5988,10 @@
         <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X22" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y22" t="n">
         <v>11.5</v>
@@ -6006,7 +6006,7 @@
         <v>11</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
         <v>13.5</v>
@@ -6066,7 +6066,7 @@
         <v>10.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX22" t="n">
         <v>15.5</v>
@@ -6081,19 +6081,19 @@
         <v>38</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD22" t="n">
         <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG22" t="n">
         <v>22</v>
@@ -6102,19 +6102,19 @@
         <v>3.3</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ22" t="n">
         <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN22" t="n">
         <v>6</v>
@@ -6129,7 +6129,7 @@
         <v>7.2</v>
       </c>
       <c r="BR22" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
         <v>8</v>
@@ -6147,7 +6147,7 @@
         <v>7.2</v>
       </c>
       <c r="BX22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY22" t="n">
         <v>8</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H23" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="I23" t="n">
         <v>4.5</v>
@@ -6209,58 +6209,58 @@
         <v>4.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P23" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R23" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S23" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="T23" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U23" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="V23" t="n">
         <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA23" t="n">
         <v>95</v>
       </c>
       <c r="AB23" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD23" t="n">
         <v>22</v>
@@ -6269,16 +6269,16 @@
         <v>42</v>
       </c>
       <c r="AF23" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG23" t="n">
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ23" t="n">
         <v>22</v>
@@ -6287,76 +6287,76 @@
         <v>17</v>
       </c>
       <c r="AL23" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AM23" t="n">
         <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP23" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ23" t="n">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="AR23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF23" t="n">
         <v>6.2</v>
       </c>
-      <c r="AS23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BG23" t="n">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BJ23" t="n">
         <v>8.800000000000001</v>
@@ -6371,40 +6371,40 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BP23" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR23" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BS23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT23" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU23" t="n">
         <v>5.2</v>
       </c>
       <c r="BV23" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY23" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -6445,58 +6445,58 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="G24" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="H24" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L24" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="O24" t="n">
         <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R24" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="S24" t="n">
         <v>2.28</v>
       </c>
       <c r="T24" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="U24" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="V24" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W24" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="X24" t="n">
         <v>28</v>
@@ -6511,13 +6511,13 @@
         <v>50</v>
       </c>
       <c r="AB24" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE24" t="n">
         <v>34</v>
@@ -6532,7 +6532,7 @@
         <v>16.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AJ24" t="n">
         <v>38</v>
@@ -6541,10 +6541,10 @@
         <v>25</v>
       </c>
       <c r="AL24" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN24" t="n">
         <v>14.5</v>
@@ -6553,112 +6553,112 @@
         <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="AQ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV24" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AW24" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF24" t="n">
         <v>4.2</v>
       </c>
-      <c r="AY24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC24" t="n">
+      <c r="BG24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK24" t="n">
         <v>4.3</v>
       </c>
-      <c r="BD24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH24" t="n">
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU24" t="n">
         <v>5</v>
       </c>
-      <c r="BI24" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BV24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BW24" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BX24" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BY24" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G25" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="H25" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I25" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="J25" t="n">
         <v>3.85</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.23</v>
@@ -6723,34 +6723,34 @@
         <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="O25" t="n">
         <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R25" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S25" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="T25" t="n">
         <v>1.5</v>
       </c>
       <c r="U25" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V25" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W25" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X25" t="n">
         <v>34</v>
@@ -6789,130 +6789,130 @@
         <v>34</v>
       </c>
       <c r="AJ25" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK25" t="n">
         <v>32</v>
       </c>
       <c r="AL25" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM25" t="n">
         <v>65</v>
       </c>
       <c r="AN25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO25" t="n">
         <v>15.5</v>
       </c>
       <c r="AP25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR25" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AS25" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AT25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF25" t="n">
         <v>3.55</v>
       </c>
-      <c r="AU25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BG25" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BH25" t="n">
         <v>4.7</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ25" t="n">
         <v>8.6</v>
       </c>
       <c r="BK25" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>3.2</v>
+        <v>9.4</v>
       </c>
       <c r="BN25" t="n">
         <v>6.6</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR25" t="n">
         <v>25</v>
       </c>
       <c r="BS25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU25" t="n">
         <v>4</v>
       </c>
       <c r="BV25" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX25" t="n">
         <v>24</v>
       </c>
       <c r="BY25" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G26" t="n">
         <v>2.04</v>
       </c>
       <c r="H26" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J26" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K26" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>1.18</v>
@@ -6977,16 +6977,16 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1</v>
+        <v>2.44</v>
       </c>
       <c r="O26" t="n">
         <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R26" t="n">
         <v>1.6</v>
@@ -7001,10 +7001,10 @@
         <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W26" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -7213,13 +7213,13 @@
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7485,7 +7485,7 @@
         <v>1.02</v>
       </c>
       <c r="N28" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O28" t="n">
         <v>1.12</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -7715,19 +7715,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G29" t="n">
         <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="K29" t="n">
         <v>1000</v>
@@ -7757,7 +7757,7 @@
         <v>1.05</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="U29" t="n">
         <v>1.11</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -8223,25 +8223,25 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="G31" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="H31" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I31" t="n">
         <v>3.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K31" t="n">
         <v>4.1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
@@ -8262,7 +8262,7 @@
         <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T31" t="n">
         <v>1.64</v>
@@ -8271,121 +8271,121 @@
         <v>2.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BH31" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI31" t="n">
         <v>2.64</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>
@@ -8486,13 +8486,13 @@
         <v>4.7</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L32" t="n">
         <v>1.44</v>
@@ -8501,10 +8501,10 @@
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O32" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P32" t="n">
         <v>1.67</v>
@@ -8513,19 +8513,19 @@
         <v>2.32</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S32" t="n">
         <v>4.6</v>
       </c>
       <c r="T32" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V32" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W32" t="n">
         <v>1.98</v>
@@ -8546,7 +8546,7 @@
         <v>7</v>
       </c>
       <c r="AC32" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD32" t="n">
         <v>21</v>
@@ -8561,7 +8561,7 @@
         <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI32" t="n">
         <v>110</v>
@@ -8576,7 +8576,7 @@
         <v>70</v>
       </c>
       <c r="AM32" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN32" t="n">
         <v>21</v>
@@ -8594,7 +8594,7 @@
         <v>24</v>
       </c>
       <c r="AS32" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT32" t="n">
         <v>6.2</v>
@@ -8606,7 +8606,7 @@
         <v>17.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX32" t="n">
         <v>9.800000000000001</v>
@@ -8618,7 +8618,7 @@
         <v>20</v>
       </c>
       <c r="BA32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB32" t="n">
         <v>21</v>
@@ -8630,13 +8630,13 @@
         <v>40</v>
       </c>
       <c r="BE32" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF32" t="n">
         <v>15.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH32" t="n">
         <v>2.94</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-25 14:07:25</t>
+          <t>2026-06-25 16:22:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G2" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
@@ -896,7 +896,7 @@
         <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T2" t="n">
         <v>1.53</v>
@@ -905,16 +905,16 @@
         <v>2.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
         <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
         <v>21</v>
@@ -956,19 +956,19 @@
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="AN2" t="n">
         <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP2" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
         <v>17</v>
@@ -977,7 +977,7 @@
         <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU2" t="n">
         <v>8.199999999999999</v>
@@ -1010,10 +1010,10 @@
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG2" t="n">
         <v>11.5</v>
@@ -1034,53 +1034,53 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU2" t="n">
         <v>4.6</v>
       </c>
       <c r="BV2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2" t="n">
         <v>16.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>4.2</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H3" t="n">
         <v>1.85</v>
@@ -1144,13 +1144,13 @@
         <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R3" t="n">
         <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T3" t="n">
         <v>1.68</v>
@@ -1171,7 +1171,7 @@
         <v>11.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA3" t="n">
         <v>21</v>
@@ -1201,19 +1201,19 @@
         <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
         <v>70</v>
       </c>
       <c r="AM3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="AO3" t="n">
         <v>10.5</v>
@@ -1243,7 +1243,7 @@
         <v>13</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY3" t="n">
         <v>15</v>
@@ -1252,22 +1252,22 @@
         <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="BD3" t="n">
         <v>40</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK3" t="n">
         <v>4.9</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN3" t="n">
         <v>8.6</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>4.9</v>
@@ -1324,17 +1324,17 @@
         <v>25</v>
       </c>
       <c r="BY3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>7.4</v>
       </c>
       <c r="G4" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I4" t="n">
         <v>1.49</v>
@@ -1380,10 +1380,10 @@
         <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
@@ -1398,7 +1398,7 @@
         <v>2.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="R4" t="n">
         <v>1.57</v>
@@ -1416,7 +1416,7 @@
         <v>3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
         <v>26</v>
@@ -1425,7 +1425,7 @@
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AA4" t="n">
         <v>970</v>
@@ -1434,7 +1434,7 @@
         <v>38</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
@@ -1452,7 +1452,7 @@
         <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1476,10 +1476,10 @@
         <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AS4" t="n">
         <v>4.2</v>
@@ -1497,37 +1497,37 @@
         <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY4" t="n">
         <v>4.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
         <v>5.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
         <v>4.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI4" t="n">
         <v>3.3</v>
@@ -1575,7 +1575,7 @@
         <v>6.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BY4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.19</v>
@@ -1643,58 +1643,58 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
         <v>1.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T5" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="U5" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X5" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB5" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
         <v>970</v>
@@ -1706,79 +1706,79 @@
         <v>970</v>
       </c>
       <c r="AI5" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
         <v>970</v>
       </c>
       <c r="AL5" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.6</v>
+        <v>2.34</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="AR5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.4</v>
       </c>
       <c r="BH5" t="n">
         <v>5.6</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1876,10 @@
         <v>1.74</v>
       </c>
       <c r="G6" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
         <v>5.6</v>
@@ -1924,31 +1924,31 @@
         <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X6" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB6" t="n">
         <v>970</v>
       </c>
-      <c r="Y6" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>10</v>
-      </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
         <v>970</v>
@@ -1957,22 +1957,22 @@
         <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
         <v>1000</v>
@@ -1981,58 +1981,58 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH6" t="n">
         <v>3.65</v>
@@ -2044,49 +2044,49 @@
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BN6" t="n">
         <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -2127,31 +2127,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="G7" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I7" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="J7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K7" t="n">
         <v>4.4</v>
       </c>
-      <c r="K7" t="n">
-        <v>5</v>
-      </c>
       <c r="L7" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
@@ -2160,142 +2160,142 @@
         <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="X7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA7" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AB7" t="n">
         <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
         <v>20</v>
       </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AO7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AV7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT7" t="n">
+      <c r="BD7" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF7" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BG7" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7" t="n">
         <v>4.7</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK7" t="n">
         <v>1.01</v>
@@ -2307,37 +2307,37 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS7" t="n">
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BW7" t="n">
         <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -2480,13 +2480,13 @@
         <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
         <v>12.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AP8" t="n">
         <v>19.5</v>
@@ -2510,7 +2510,7 @@
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AX8" t="n">
         <v>16</v>
@@ -2522,16 +2522,16 @@
         <v>12.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="BC8" t="n">
         <v>19</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BE8" t="n">
         <v>9.199999999999999</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G9" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="I9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
@@ -2671,31 +2671,31 @@
         <v>1.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
         <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA9" t="n">
         <v>23</v>
@@ -2725,22 +2725,22 @@
         <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
         <v>50</v>
       </c>
       <c r="AL9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN9" t="n">
         <v>60</v>
       </c>
-      <c r="AM9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>38</v>
-      </c>
       <c r="AO9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AP9" t="n">
         <v>19</v>
@@ -2767,7 +2767,7 @@
         <v>15.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="AY9" t="n">
         <v>14</v>
@@ -2776,10 +2776,10 @@
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC9" t="n">
         <v>29</v>
@@ -2788,16 +2788,16 @@
         <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF9" t="n">
         <v>22</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI9" t="n">
         <v>3.35</v>
@@ -2806,13 +2806,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
         <v>8</v>
@@ -2824,16 +2824,16 @@
         <v>32</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU9" t="n">
         <v>4.4</v>
@@ -2842,23 +2842,23 @@
         <v>13</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX9" t="n">
         <v>23</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>16.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -2943,16 +2943,16 @@
         <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="n">
         <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AB10" t="n">
         <v>25</v>
@@ -2964,31 +2964,31 @@
         <v>12.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AG10" t="n">
         <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ10" t="n">
         <v>140</v>
       </c>
       <c r="AK10" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AL10" t="n">
         <v>75</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN10" t="n">
         <v>75</v>
@@ -3006,46 +3006,46 @@
         <v>8.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
         <v>17.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="AV10" t="n">
         <v>7.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AY10" t="n">
         <v>17.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG10" t="n">
         <v>6.6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="I11" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
         <v>1.28</v>
@@ -3170,7 +3170,7 @@
         <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
@@ -3185,7 +3185,7 @@
         <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U11" t="n">
         <v>2.66</v>
@@ -3197,112 +3197,112 @@
         <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="Y11" t="n">
         <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
         <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AO11" t="n">
         <v>970</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>15</v>
+        <v>7.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF11" t="n">
         <v>5.8</v>
       </c>
-      <c r="AY11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BG11" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH11" t="n">
         <v>4.4</v>
@@ -3314,7 +3314,7 @@
         <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3326,13 +3326,13 @@
         <v>6.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -3397,82 +3397,82 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
         <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
         <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M12" t="n">
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U12" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
         <v>14.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AF12" t="n">
         <v>17.5</v>
@@ -3481,28 +3481,28 @@
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="AJ12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK12" t="n">
         <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM12" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AN12" t="n">
         <v>12.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AP12" t="n">
         <v>16</v>
@@ -3511,10 +3511,10 @@
         <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT12" t="n">
         <v>10.5</v>
@@ -3526,7 +3526,7 @@
         <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
         <v>12.5</v>
@@ -3538,7 +3538,7 @@
         <v>12</v>
       </c>
       <c r="BA12" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BB12" t="n">
         <v>19</v>
@@ -3547,16 +3547,16 @@
         <v>16.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH12" t="n">
         <v>4.3</v>
@@ -3577,16 +3577,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR12" t="n">
         <v>25</v>
@@ -3595,16 +3595,16 @@
         <v>7</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX12" t="n">
         <v>34</v>
@@ -3613,14 +3613,14 @@
         <v>7.6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -3660,10 +3660,10 @@
         <v>2.14</v>
       </c>
       <c r="I13" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
         <v>4.8</v>
@@ -3699,13 +3699,13 @@
         <v>2.46</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="W13" t="n">
         <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="Y13" t="n">
         <v>17</v>
@@ -3741,16 +3741,16 @@
         <v>38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AK13" t="n">
         <v>44</v>
       </c>
       <c r="AL13" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM13" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
         <v>23</v>
@@ -3762,55 +3762,55 @@
         <v>5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX13" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW13" t="n">
+      <c r="AY13" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH13" t="n">
         <v>4.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -3938,13 +3938,13 @@
         <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
         <v>1.49</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T14" t="n">
         <v>1.91</v>
@@ -3962,7 +3962,7 @@
         <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="Z14" t="n">
         <v>75</v>
@@ -4004,7 +4004,7 @@
         <v>34</v>
       </c>
       <c r="AM14" t="n">
-        <v>150</v>
+        <v>390</v>
       </c>
       <c r="AN14" t="n">
         <v>6.8</v>
@@ -4022,7 +4022,7 @@
         <v>60</v>
       </c>
       <c r="AS14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
@@ -4034,7 +4034,7 @@
         <v>25</v>
       </c>
       <c r="AW14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX14" t="n">
         <v>8.4</v>
@@ -4046,7 +4046,7 @@
         <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB14" t="n">
         <v>11.5</v>
@@ -4055,16 +4055,16 @@
         <v>13</v>
       </c>
       <c r="BD14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BE14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF14" t="n">
         <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH14" t="n">
         <v>4.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>1.59</v>
       </c>
       <c r="G15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H15" t="n">
         <v>6.6</v>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -4189,10 +4189,10 @@
         <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="R15" t="n">
         <v>1.35</v>
@@ -4210,7 +4210,7 @@
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="X15" t="n">
         <v>15.5</v>
@@ -4219,10 +4219,10 @@
         <v>30</v>
       </c>
       <c r="Z15" t="n">
-        <v>65</v>
+        <v>230</v>
       </c>
       <c r="AA15" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AB15" t="n">
         <v>8</v>
@@ -4234,7 +4234,7 @@
         <v>38</v>
       </c>
       <c r="AE15" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF15" t="n">
         <v>9.800000000000001</v>
@@ -4246,7 +4246,7 @@
         <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AJ15" t="n">
         <v>16.5</v>
@@ -4258,13 +4258,13 @@
         <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AN15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AP15" t="n">
         <v>12</v>
@@ -4273,10 +4273,10 @@
         <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT15" t="n">
         <v>6.8</v>
@@ -4288,7 +4288,7 @@
         <v>19</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX15" t="n">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15" t="n">
         <v>13</v>
@@ -4312,19 +4312,19 @@
         <v>27</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH15" t="n">
         <v>3.95</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ15" t="n">
         <v>13.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -4467,13 +4467,13 @@
         <v>2.72</v>
       </c>
       <c r="X16" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="Y16" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="Z16" t="n">
-        <v>70</v>
+        <v>420</v>
       </c>
       <c r="AA16" t="n">
         <v>190</v>
@@ -4488,7 +4488,7 @@
         <v>32</v>
       </c>
       <c r="AE16" t="n">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="AF16" t="n">
         <v>14</v>
@@ -4497,40 +4497,40 @@
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AI16" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AJ16" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AK16" t="n">
         <v>18</v>
       </c>
       <c r="AL16" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="AN16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO16" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>22</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -4539,40 +4539,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AY16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC16" t="n">
         <v>12</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF16" t="n">
         <v>5</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="n">
         <v>4.8</v>
@@ -4596,7 +4596,7 @@
         <v>4.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BP16" t="n">
         <v>9.800000000000001</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -4721,13 +4721,13 @@
         <v>1.64</v>
       </c>
       <c r="X17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y17" t="n">
         <v>13.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
         <v>80</v>
@@ -4739,13 +4739,13 @@
         <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE17" t="n">
         <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG17" t="n">
         <v>13.5</v>
@@ -4754,25 +4754,25 @@
         <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>370</v>
       </c>
       <c r="AJ17" t="n">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="AK17" t="n">
         <v>32</v>
       </c>
       <c r="AL17" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO17" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AP17" t="n">
         <v>8.800000000000001</v>
@@ -4784,13 +4784,13 @@
         <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT17" t="n">
         <v>7.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV17" t="n">
         <v>12.5</v>
@@ -4808,19 +4808,19 @@
         <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.2</v>
+        <v>28</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="BD17" t="n">
         <v>34</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF17" t="n">
         <v>20</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -4924,22 +4924,22 @@
         <v>1.91</v>
       </c>
       <c r="G18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
         <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
@@ -4963,16 +4963,16 @@
         <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="V18" t="n">
         <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X18" t="n">
         <v>18</v>
@@ -5005,10 +5005,10 @@
         <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
         <v>27</v>
@@ -5017,16 +5017,16 @@
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
         <v>16</v>
       </c>
       <c r="AO18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP18" t="n">
         <v>11.5</v>
@@ -5035,10 +5035,10 @@
         <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT18" t="n">
         <v>7.4</v>
@@ -5050,7 +5050,7 @@
         <v>13</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX18" t="n">
         <v>9.4</v>
@@ -5062,7 +5062,7 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB18" t="n">
         <v>17.5</v>
@@ -5071,16 +5071,16 @@
         <v>15.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF18" t="n">
         <v>10.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH18" t="n">
         <v>3.6</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.66</v>
       </c>
       <c r="G19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H19" t="n">
         <v>5.4</v>
@@ -5199,7 +5199,7 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>1.3</v>
@@ -5211,7 +5211,7 @@
         <v>1.88</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
         <v>3.25</v>
@@ -5226,19 +5226,19 @@
         <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z19" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB19" t="n">
         <v>10.5</v>
@@ -5247,10 +5247,10 @@
         <v>13.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AE19" t="n">
-        <v>95</v>
+        <v>700</v>
       </c>
       <c r="AF19" t="n">
         <v>12.5</v>
@@ -5259,22 +5259,22 @@
         <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI19" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AJ19" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AK19" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AN19" t="n">
         <v>13</v>
@@ -5283,16 +5283,16 @@
         <v>110</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT19" t="n">
         <v>7.2</v>
@@ -5301,10 +5301,10 @@
         <v>5.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX19" t="n">
         <v>7.8</v>
@@ -5316,25 +5316,25 @@
         <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF19" t="n">
         <v>8</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH19" t="n">
         <v>4.1</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.61</v>
       </c>
       <c r="G20" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H20" t="n">
         <v>5.3</v>
@@ -5459,7 +5459,7 @@
         <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
         <v>1.67</v>
@@ -5480,61 +5480,61 @@
         <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X20" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Y20" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="Z20" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA20" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
         <v>26</v>
       </c>
       <c r="AE20" t="n">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AJ20" t="n">
-        <v>19.5</v>
+        <v>44</v>
       </c>
       <c r="AK20" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
         <v>9.6</v>
       </c>
       <c r="AO20" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AP20" t="n">
         <v>14.5</v>
@@ -5543,10 +5543,10 @@
         <v>16</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT20" t="n">
         <v>8.6</v>
@@ -5555,10 +5555,10 @@
         <v>7.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX20" t="n">
         <v>9.6</v>
@@ -5570,7 +5570,7 @@
         <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB20" t="n">
         <v>11.5</v>
@@ -5579,16 +5579,16 @@
         <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF20" t="n">
         <v>6.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="G21" t="n">
         <v>1.81</v>
@@ -5692,7 +5692,7 @@
         <v>4.9</v>
       </c>
       <c r="I21" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
@@ -5707,13 +5707,13 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
         <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
         <v>1.87</v>
@@ -5725,16 +5725,16 @@
         <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X21" t="n">
         <v>19</v>
@@ -5833,7 +5833,7 @@
         <v>13</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="BE21" t="n">
         <v>5</v>
@@ -5884,7 +5884,7 @@
         <v>8.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -5940,16 +5940,16 @@
         <v>2.78</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H22" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I22" t="n">
         <v>3.05</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K22" t="n">
         <v>3.35</v>
@@ -5961,31 +5961,31 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="R22" t="n">
         <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
         <v>2.08</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W22" t="n">
         <v>1.53</v>
@@ -6015,7 +6015,7 @@
         <v>50</v>
       </c>
       <c r="AF22" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG22" t="n">
         <v>13.5</v>
@@ -6024,22 +6024,22 @@
         <v>19</v>
       </c>
       <c r="AI22" t="n">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="AJ22" t="n">
-        <v>65</v>
+        <v>280</v>
       </c>
       <c r="AK22" t="n">
         <v>50</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AO22" t="n">
         <v>34</v>
@@ -6066,7 +6066,7 @@
         <v>10.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX22" t="n">
         <v>15.5</v>
@@ -6084,7 +6084,7 @@
         <v>8</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="BD22" t="n">
         <v>38</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -6194,121 +6194,121 @@
         <v>1.78</v>
       </c>
       <c r="G23" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H23" t="n">
         <v>3.95</v>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K23" t="n">
         <v>4.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="R23" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="S23" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="T23" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="U23" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="V23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W23" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X23" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z23" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA23" t="n">
         <v>95</v>
       </c>
       <c r="AB23" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AC23" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD23" t="n">
         <v>22</v>
       </c>
       <c r="AE23" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AF23" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI23" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AJ23" t="n">
         <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AM23" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO23" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AT23" t="n">
         <v>13</v>
@@ -6320,7 +6320,7 @@
         <v>15.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="AX23" t="n">
         <v>13.5</v>
@@ -6329,37 +6329,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BB23" t="n">
         <v>18.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="BF23" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BJ23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK23" t="n">
         <v>5.4</v>
@@ -6368,28 +6368,28 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP23" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR23" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU23" t="n">
         <v>5.2</v>
@@ -6398,13 +6398,13 @@
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>10</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -6445,82 +6445,82 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="G24" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="H24" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K24" t="n">
         <v>4.7</v>
       </c>
       <c r="L24" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q24" t="n">
         <v>1.51</v>
       </c>
       <c r="R24" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="S24" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T24" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U24" t="n">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="V24" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W24" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="X24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Y24" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA24" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AB24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC24" t="n">
         <v>11</v>
       </c>
       <c r="AD24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AF24" t="n">
         <v>21</v>
@@ -6529,94 +6529,94 @@
         <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="AK24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL24" t="n">
         <v>30</v>
       </c>
       <c r="AM24" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AN24" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AP24" t="n">
         <v>21</v>
       </c>
       <c r="AQ24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.3</v>
+        <v>30</v>
       </c>
       <c r="AT24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="BC24" t="n">
         <v>18</v>
       </c>
       <c r="BD24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH24" t="n">
         <v>4.9</v>
       </c>
-      <c r="BE24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BI24" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="BJ24" t="n">
         <v>9</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
@@ -6625,10 +6625,10 @@
         <v>7.4</v>
       </c>
       <c r="BN24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="BP24" t="n">
         <v>16.5</v>
@@ -6637,25 +6637,25 @@
         <v>5.5</v>
       </c>
       <c r="BR24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS24" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BT24" t="n">
         <v>7</v>
       </c>
       <c r="BU24" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BV24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BX24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY24" t="n">
         <v>6.2</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -6708,10 +6708,10 @@
         <v>2.4</v>
       </c>
       <c r="I25" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J25" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K25" t="n">
         <v>4.4</v>
@@ -6732,7 +6732,7 @@
         <v>2.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R25" t="n">
         <v>1.64</v>
@@ -6741,10 +6741,10 @@
         <v>2.28</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U25" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V25" t="n">
         <v>1.58</v>
@@ -6753,19 +6753,19 @@
         <v>1.53</v>
       </c>
       <c r="X25" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Z25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA25" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB25" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AC25" t="n">
         <v>12.5</v>
@@ -6774,10 +6774,10 @@
         <v>15.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF25" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AG25" t="n">
         <v>16</v>
@@ -6786,13 +6786,13 @@
         <v>18</v>
       </c>
       <c r="AI25" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK25" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AL25" t="n">
         <v>32</v>
@@ -6807,64 +6807,64 @@
         <v>15.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AT25" t="n">
         <v>15</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="AV25" t="n">
         <v>10.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.8</v>
+        <v>19</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
         <v>12.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.9</v>
+        <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="BH25" t="n">
         <v>4.7</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BJ25" t="n">
         <v>8.6</v>
@@ -6882,7 +6882,7 @@
         <v>6.6</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BP25" t="n">
         <v>18.5</v>
@@ -6900,7 +6900,7 @@
         <v>6.4</v>
       </c>
       <c r="BU25" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BV25" t="n">
         <v>17.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -6962,13 +6962,13 @@
         <v>3.75</v>
       </c>
       <c r="I26" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="L26" t="n">
         <v>1.18</v>
@@ -6977,7 +6977,7 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>2.44</v>
+        <v>4.8</v>
       </c>
       <c r="O26" t="n">
         <v>1.12</v>
@@ -6986,10 +6986,10 @@
         <v>2.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S26" t="n">
         <v>1.96</v>
@@ -7001,58 +7001,58 @@
         <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="W26" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN26" t="n">
         <v>1000</v>
@@ -7061,58 +7061,58 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>1.64</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>1.66</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>1.66</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -7207,230 +7207,230 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H27" t="n">
-        <v>1.09</v>
+        <v>2.24</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="P27" t="n">
-        <v>1.25</v>
+        <v>3.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="S27" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="T27" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="U27" t="n">
-        <v>1.11</v>
+        <v>3.6</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.77</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH27" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP27" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR27" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV27" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BX27" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -7461,25 +7461,25 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="H28" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
-        <v>1.09</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M28" t="n">
         <v>1.02</v>
@@ -7491,148 +7491,148 @@
         <v>1.12</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="S28" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="T28" t="n">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="U28" t="n">
-        <v>1.11</v>
+        <v>3.05</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN28" t="n">
         <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7644,13 +7644,13 @@
         <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
@@ -7662,29 +7662,29 @@
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -7715,25 +7715,25 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="H29" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
@@ -7742,148 +7742,148 @@
         <v>1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="S29" t="n">
-        <v>1.05</v>
+        <v>1.52</v>
       </c>
       <c r="T29" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>3.15</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BH29" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BI29" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK29" t="n">
         <v>1.01</v>
@@ -7895,7 +7895,7 @@
         <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BO29" t="n">
         <v>1.01</v>
@@ -7907,38 +7907,38 @@
         <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS29" t="n">
         <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU29" t="n">
         <v>1.01</v>
       </c>
       <c r="BV29" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BW29" t="n">
         <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BY29" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="CA29" t="n">
         <v>1.01</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="H30" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="J30" t="n">
-        <v>1.09</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -7993,22 +7993,22 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="O30" t="n">
         <v>1.04</v>
       </c>
       <c r="P30" t="n">
-        <v>1.08</v>
+        <v>2.34</v>
       </c>
       <c r="Q30" t="n">
         <v>1.04</v>
       </c>
       <c r="R30" t="n">
-        <v>1.08</v>
+        <v>2.34</v>
       </c>
       <c r="S30" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8017,112 +8017,112 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
         <v>1.01</v>
       </c>
-      <c r="W30" t="n">
+      <c r="AQ30" t="n">
         <v>1.01</v>
       </c>
-      <c r="X30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
         <v>1.01</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -8226,16 +8226,16 @@
         <v>2.1</v>
       </c>
       <c r="G31" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="H31" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J31" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K31" t="n">
         <v>4.1</v>
@@ -8253,10 +8253,10 @@
         <v>1.25</v>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R31" t="n">
         <v>1.44</v>
@@ -8274,31 +8274,31 @@
         <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="X31" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="Y31" t="n">
-        <v>19</v>
+        <v>500</v>
       </c>
       <c r="Z31" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AA31" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AB31" t="n">
         <v>14.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>500</v>
       </c>
       <c r="AE31" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AF31" t="n">
         <v>18.5</v>
@@ -8307,82 +8307,82 @@
         <v>13.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="AI31" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AJ31" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AK31" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AL31" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM31" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AN31" t="n">
         <v>16.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AQ31" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AU31" t="n">
         <v>7.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="AW31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX31" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX31" t="n">
-        <v>11</v>
-      </c>
       <c r="AY31" t="n">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
         <v>1.67</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R32" t="n">
         <v>1.24</v>
@@ -8552,7 +8552,7 @@
         <v>21</v>
       </c>
       <c r="AE32" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AF32" t="n">
         <v>11.5</v>
@@ -8576,7 +8576,7 @@
         <v>70</v>
       </c>
       <c r="AM32" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN32" t="n">
         <v>21</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
@@ -881,28 +881,28 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
         <v>1.53</v>
       </c>
       <c r="U2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="V2" t="n">
         <v>1.66</v>
@@ -914,16 +914,16 @@
         <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
         <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC2" t="n">
         <v>9.4</v>
@@ -932,22 +932,22 @@
         <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AF2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
         <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AK2" t="n">
         <v>42</v>
@@ -956,19 +956,19 @@
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
         <v>13</v>
       </c>
       <c r="AP2" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
         <v>17</v>
@@ -977,43 +977,43 @@
         <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BB2" t="n">
         <v>26</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BE2" t="n">
         <v>29</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG2" t="n">
         <v>11.5</v>
@@ -1022,37 +1022,37 @@
         <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP2" t="n">
         <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6</v>
@@ -1064,10 +1064,10 @@
         <v>16.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY2" t="n">
         <v>7.2</v>
@@ -1076,11 +1076,11 @@
         <v>16.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>1.85</v>
       </c>
       <c r="I3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="J3" t="n">
         <v>3.9</v>
@@ -1129,31 +1129,31 @@
         <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="U3" t="n">
         <v>2.38</v>
@@ -1165,19 +1165,19 @@
         <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA3" t="n">
         <v>21</v>
       </c>
       <c r="AB3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
@@ -1186,91 +1186,91 @@
         <v>11</v>
       </c>
       <c r="AE3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG3" t="n">
         <v>18.5</v>
       </c>
-      <c r="AF3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>19</v>
-      </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
         <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="AO3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AP3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>10</v>
-      </c>
       <c r="AS3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW3" t="n">
         <v>14</v>
       </c>
-      <c r="AT3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW3" t="n">
+      <c r="AX3" t="n">
         <v>13</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7.4</v>
       </c>
       <c r="AY3" t="n">
         <v>15</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BC3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE3" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
         <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="n">
         <v>4.1</v>
@@ -1282,7 +1282,7 @@
         <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,7 +1294,7 @@
         <v>8.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1306,22 +1306,22 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
         <v>4.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BV3" t="n">
         <v>12.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="BX3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
         <v>7.2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -1371,70 +1371,70 @@
         <v>10.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="I4" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
         <v>2.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T4" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AC4" t="n">
         <v>970</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>42</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
@@ -1443,13 +1443,13 @@
         <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AG4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1458,10 +1458,10 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1470,61 +1470,61 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR4" t="n">
         <v>6.6</v>
       </c>
-      <c r="AP4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>9</v>
-      </c>
       <c r="AS4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT4" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT4" t="n">
-        <v>5</v>
-      </c>
       <c r="AU4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX4" t="n">
         <v>4.2</v>
       </c>
-      <c r="AV4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW4" t="n">
+      <c r="AY4" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.6</v>
+        <v>2.48</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="n">
         <v>5</v>
@@ -1536,7 +1536,7 @@
         <v>970</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>150</v>
@@ -1545,10 +1545,10 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>80</v>
@@ -1563,16 +1563,16 @@
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="BV4" t="n">
         <v>10.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>25</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
         <v>4.7</v>
@@ -1634,7 +1634,7 @@
         <v>4.6</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.19</v>
@@ -1646,25 +1646,25 @@
         <v>6.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R5" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="T5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U5" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="V5" t="n">
         <v>1.27</v>
@@ -1682,7 +1682,7 @@
         <v>500</v>
       </c>
       <c r="AA5" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
@@ -1700,16 +1700,16 @@
         <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>970</v>
@@ -1718,25 +1718,25 @@
         <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="AT5" t="n">
         <v>6</v>
@@ -1745,37 +1745,37 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY5" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BB5" t="n">
         <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BG5" t="n">
         <v>4.7</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G6" t="n">
         <v>1.95</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>5.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1936,10 +1936,10 @@
         <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AC6" t="n">
         <v>42</v>
@@ -1951,10 +1951,10 @@
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH6" t="n">
         <v>500</v>
@@ -1963,7 +1963,7 @@
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
         <v>500</v>
@@ -1972,10 +1972,10 @@
         <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1990,13 +1990,13 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.6</v>
+        <v>3.95</v>
       </c>
       <c r="AV6" t="n">
         <v>5.2</v>
@@ -2005,10 +2005,10 @@
         <v>6.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AZ6" t="n">
         <v>5.2</v>
@@ -2032,13 +2032,13 @@
         <v>4.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH6" t="n">
         <v>3.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
         <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
@@ -2154,43 +2154,43 @@
         <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
         <v>1.72</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="X7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z7" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA7" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB7" t="n">
         <v>11.5</v>
@@ -2199,28 +2199,28 @@
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
         <v>34</v>
@@ -2229,70 +2229,70 @@
         <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AO7" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB7" t="n">
         <v>17</v>
       </c>
-      <c r="BA7" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>15</v>
-      </c>
       <c r="BC7" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD7" t="n">
         <v>24</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
         <v>12</v>
@@ -2301,19 +2301,19 @@
         <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM7" t="n">
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ7" t="n">
         <v>1.01</v>
@@ -2325,19 +2325,19 @@
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU7" t="n">
         <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW7" t="n">
         <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -2381,145 +2381,145 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P8" t="n">
         <v>2.26</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.48</v>
-      </c>
       <c r="Q8" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="R8" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="S8" t="n">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="T8" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="U8" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AA8" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD8" t="n">
         <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AF8" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG8" t="n">
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ8" t="n">
-        <v>48</v>
+        <v>170</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP8" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW8" t="n">
         <v>14.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA8" t="n">
         <v>16</v>
@@ -2528,83 +2528,83 @@
         <v>14.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD8" t="n">
         <v>14.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>5.9</v>
       </c>
-      <c r="BO8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BZ8" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -2638,22 +2638,22 @@
         <v>3.85</v>
       </c>
       <c r="G9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K9" t="n">
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
@@ -2668,34 +2668,34 @@
         <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
         <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
         <v>23</v>
@@ -2716,31 +2716,31 @@
         <v>48</v>
       </c>
       <c r="AG9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
         <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AL9" t="n">
         <v>150</v>
       </c>
       <c r="AM9" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN9" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="AO9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP9" t="n">
         <v>19</v>
@@ -2752,7 +2752,7 @@
         <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT9" t="n">
         <v>16.5</v>
@@ -2761,13 +2761,13 @@
         <v>8.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
         <v>15.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AY9" t="n">
         <v>14</v>
@@ -2779,86 +2779,86 @@
         <v>14.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>29</v>
+        <v>7.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>30</v>
+        <v>7.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG9" t="n">
         <v>8</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G10" t="n">
         <v>5.6</v>
@@ -2898,7 +2898,7 @@
         <v>1.69</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2907,7 +2907,7 @@
         <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -2922,22 +2922,22 @@
         <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R10" t="n">
         <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T10" t="n">
         <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="W10" t="n">
         <v>1.22</v>
@@ -2979,16 +2979,16 @@
         <v>32</v>
       </c>
       <c r="AJ10" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="AL10" t="n">
         <v>75</v>
       </c>
       <c r="AM10" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>75</v>
@@ -3006,7 +3006,7 @@
         <v>8.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT10" t="n">
         <v>17.5</v>
@@ -3018,16 +3018,16 @@
         <v>7.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY10" t="n">
         <v>17.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA10" t="n">
         <v>4.9</v>
@@ -3045,74 +3045,74 @@
         <v>5.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG10" t="n">
         <v>6.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G11" t="n">
         <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I11" t="n">
         <v>2.98</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
         <v>3.85</v>
@@ -3170,16 +3170,16 @@
         <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
         <v>2.48</v>
@@ -3188,10 +3188,10 @@
         <v>1.48</v>
       </c>
       <c r="U11" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="V11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
         <v>1.58</v>
@@ -3209,7 +3209,7 @@
         <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AC11" t="n">
         <v>9</v>
@@ -3221,10 +3221,10 @@
         <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AH11" t="n">
         <v>14.5</v>
@@ -3242,13 +3242,13 @@
         <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>42</v>
       </c>
       <c r="AO11" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
@@ -3257,7 +3257,7 @@
         <v>15.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS11" t="n">
         <v>7.8</v>
@@ -3275,10 +3275,10 @@
         <v>7.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AZ11" t="n">
         <v>8.4</v>
@@ -3287,10 +3287,10 @@
         <v>16</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD11" t="n">
         <v>7.2</v>
@@ -3302,61 +3302,61 @@
         <v>5.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -3397,230 +3397,230 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J12" t="n">
         <v>3.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.7</v>
       </c>
       <c r="K12" t="n">
         <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="S12" t="n">
-        <v>2.84</v>
+        <v>2.54</v>
       </c>
       <c r="T12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y12" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z12" t="n">
         <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
         <v>38</v>
       </c>
       <c r="AF12" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
         <v>16.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AP12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR12" t="n">
         <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT12" t="n">
         <v>10.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX12" t="n">
         <v>13</v>
       </c>
-      <c r="AW12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD12" t="n">
         <v>14.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.9</v>
+        <v>1.93</v>
       </c>
       <c r="BR12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>3.45</v>
       </c>
       <c r="H13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I13" t="n">
         <v>2.48</v>
@@ -3687,16 +3687,16 @@
         <v>1.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="T13" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="U13" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V13" t="n">
         <v>1.67</v>
@@ -3708,16 +3708,16 @@
         <v>70</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AB13" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AC13" t="n">
         <v>11.5</v>
@@ -3726,52 +3726,52 @@
         <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AF13" t="n">
         <v>32</v>
       </c>
       <c r="AG13" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AK13" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="n">
         <v>60</v>
       </c>
       <c r="AM13" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="AO13" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU13" t="n">
         <v>5.6</v>
@@ -3780,37 +3780,37 @@
         <v>6.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD13" t="n">
         <v>5.8</v>
       </c>
-      <c r="BC13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BE13" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH13" t="n">
         <v>4.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G14" t="n">
         <v>1.48</v>
       </c>
       <c r="H14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.33</v>
@@ -3932,25 +3932,25 @@
         <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="T14" t="n">
         <v>1.91</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -3962,13 +3962,13 @@
         <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="Z14" t="n">
-        <v>75</v>
+        <v>540</v>
       </c>
       <c r="AA14" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB14" t="n">
         <v>9</v>
@@ -3983,88 +3983,88 @@
         <v>120</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG14" t="n">
         <v>9.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>110</v>
       </c>
       <c r="AJ14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK14" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL14" t="n">
         <v>34</v>
       </c>
       <c r="AM14" t="n">
-        <v>390</v>
+        <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO14" t="n">
         <v>140</v>
       </c>
       <c r="AP14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AS14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AV14" t="n">
         <v>25</v>
       </c>
       <c r="AW14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY14" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BB14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="BE14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH14" t="n">
         <v>4.5</v>
@@ -4073,16 +4073,16 @@
         <v>3.6</v>
       </c>
       <c r="BJ14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BL14" t="n">
         <v>160</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN14" t="n">
         <v>4.5</v>
@@ -4091,34 +4091,34 @@
         <v>3.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BR14" t="n">
         <v>27</v>
       </c>
       <c r="BS14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BT14" t="n">
         <v>13</v>
       </c>
       <c r="BU14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV14" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX14" t="n">
         <v>75</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H15" t="n">
         <v>6.6</v>
@@ -4174,7 +4174,7 @@
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.39</v>
@@ -4183,13 +4183,13 @@
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
         <v>1.94</v>
@@ -4198,40 +4198,40 @@
         <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="X15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Z15" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="AA15" t="n">
         <v>700</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
         <v>700</v>
@@ -4240,7 +4240,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
         <v>25</v>
@@ -4255,7 +4255,7 @@
         <v>19</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AM15" t="n">
         <v>700</v>
@@ -4267,16 +4267,16 @@
         <v>700</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT15" t="n">
         <v>6.8</v>
@@ -4285,10 +4285,10 @@
         <v>8</v>
       </c>
       <c r="AV15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
         <v>8</v>
@@ -4300,25 +4300,25 @@
         <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB15" t="n">
         <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD15" t="n">
-        <v>27</v>
+        <v>7.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="n">
         <v>3.95</v>
@@ -4330,7 +4330,7 @@
         <v>13.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
         <v>190</v>
@@ -4342,13 +4342,13 @@
         <v>4.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BP15" t="n">
         <v>13</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
         <v>34</v>
@@ -4360,7 +4360,7 @@
         <v>12</v>
       </c>
       <c r="BU15" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
         <v>75</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>6.4</v>
       </c>
       <c r="I16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
         <v>4.6</v>
@@ -4449,7 +4449,7 @@
         <v>1.52</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S16" t="n">
         <v>2.3</v>
@@ -4476,28 +4476,28 @@
         <v>420</v>
       </c>
       <c r="AA16" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB16" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AC16" t="n">
         <v>12.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AE16" t="n">
         <v>400</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH16" t="n">
         <v>970</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>36</v>
       </c>
       <c r="AI16" t="n">
         <v>300</v>
@@ -4506,7 +4506,7 @@
         <v>500</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AL16" t="n">
         <v>500</v>
@@ -4521,16 +4521,16 @@
         <v>170</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -4539,22 +4539,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>6.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AZ16" t="n">
         <v>10.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB16" t="n">
         <v>8.4</v>
@@ -4563,16 +4563,16 @@
         <v>12</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
         <v>5</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BH16" t="n">
         <v>4.8</v>
@@ -4596,13 +4596,13 @@
         <v>4.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BP16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4614,7 +4614,7 @@
         <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
         <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
         <v>1.7</v>
@@ -4709,13 +4709,13 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
         <v>1.64</v>
@@ -4724,16 +4724,16 @@
         <v>12</v>
       </c>
       <c r="Y17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
         <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC17" t="n">
         <v>8</v>
@@ -4742,19 +4742,19 @@
         <v>15.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF17" t="n">
         <v>15.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
         <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>370</v>
+        <v>150</v>
       </c>
       <c r="AJ17" t="n">
         <v>130</v>
@@ -4763,10 +4763,10 @@
         <v>32</v>
       </c>
       <c r="AL17" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
         <v>28</v>
@@ -4775,16 +4775,16 @@
         <v>90</v>
       </c>
       <c r="AP17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AR17" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT17" t="n">
         <v>7.6</v>
@@ -4796,19 +4796,19 @@
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="AX17" t="n">
         <v>12.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>28</v>
+        <v>7.8</v>
       </c>
       <c r="BB17" t="n">
         <v>14.5</v>
@@ -4817,70 +4817,70 @@
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>38</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G18" t="n">
         <v>2.06</v>
@@ -4936,37 +4936,37 @@
         <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
         <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
         <v>1.27</v>
@@ -4975,19 +4975,19 @@
         <v>1.94</v>
       </c>
       <c r="X18" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
         <v>34</v>
       </c>
       <c r="AA18" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC18" t="n">
         <v>9</v>
@@ -4996,25 +4996,25 @@
         <v>18</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
         <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AJ18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
         <v>38</v>
@@ -5023,13 +5023,13 @@
         <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO18" t="n">
         <v>60</v>
       </c>
       <c r="AP18" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ18" t="n">
         <v>12</v>
@@ -5038,103 +5038,103 @@
         <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AT18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW18" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AX18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA18" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BB18" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BC18" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD18" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG18" t="n">
         <v>9.4</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.66</v>
       </c>
       <c r="G19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H19" t="n">
         <v>5.4</v>
@@ -5190,7 +5190,7 @@
         <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L19" t="n">
         <v>1.38</v>
@@ -5205,7 +5205,7 @@
         <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
         <v>1.88</v>
@@ -5217,34 +5217,34 @@
         <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V19" t="n">
         <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
       </c>
       <c r="Y19" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
         <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="AC19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD19" t="n">
         <v>500</v>
@@ -5253,10 +5253,10 @@
         <v>700</v>
       </c>
       <c r="AF19" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH19" t="n">
         <v>60</v>
@@ -5265,76 +5265,76 @@
         <v>700</v>
       </c>
       <c r="AJ19" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL19" t="n">
         <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AO19" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP19" t="n">
         <v>7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AR19" t="n">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="AT19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD19" t="n">
         <v>7.2</v>
       </c>
-      <c r="AU19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE19" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="BH19" t="n">
         <v>4.1</v>
@@ -5346,7 +5346,7 @@
         <v>12.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
         <v>160</v>
@@ -5358,13 +5358,13 @@
         <v>5.1</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="BP19" t="n">
         <v>14</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR19" t="n">
         <v>32</v>
@@ -5376,7 +5376,7 @@
         <v>11</v>
       </c>
       <c r="BU19" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
         <v>60</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G20" t="n">
         <v>1.71</v>
@@ -5441,10 +5441,10 @@
         <v>6.2</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.28</v>
@@ -5453,13 +5453,13 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
         <v>1.67</v>
@@ -5468,22 +5468,22 @@
         <v>1.47</v>
       </c>
       <c r="S20" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T20" t="n">
         <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W20" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X20" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="Y20" t="n">
         <v>40</v>
@@ -5501,7 +5501,7 @@
         <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AE20" t="n">
         <v>700</v>
@@ -5525,40 +5525,40 @@
         <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO20" t="n">
         <v>700</v>
       </c>
       <c r="AP20" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW20" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>6.4</v>
       </c>
       <c r="AX20" t="n">
         <v>9.6</v>
@@ -5567,82 +5567,82 @@
         <v>8.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF20" t="n">
         <v>6.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BP20" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="G21" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H21" t="n">
         <v>4.9</v>
       </c>
       <c r="I21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
         <v>1.32</v>
@@ -5707,7 +5707,7 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O21" t="n">
         <v>1.3</v>
@@ -5722,31 +5722,31 @@
         <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
         <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W21" t="n">
         <v>2.22</v>
       </c>
       <c r="X21" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AA21" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
         <v>9</v>
@@ -5755,52 +5755,52 @@
         <v>9.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AJ21" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM21" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
         <v>95</v>
       </c>
       <c r="AP21" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AQ21" t="n">
         <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AT21" t="n">
         <v>7.8</v>
@@ -5809,10 +5809,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AX21" t="n">
         <v>8.199999999999999</v>
@@ -5821,28 +5821,28 @@
         <v>9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="BB21" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BD21" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BF21" t="n">
         <v>9.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BH21" t="n">
         <v>3.55</v>
@@ -5866,7 +5866,7 @@
         <v>4.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BP21" t="n">
         <v>12</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -5949,10 +5949,10 @@
         <v>3.05</v>
       </c>
       <c r="J22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L22" t="n">
         <v>1.44</v>
@@ -5961,13 +5961,13 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P22" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q22" t="n">
         <v>2.24</v>
@@ -5976,16 +5976,16 @@
         <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W22" t="n">
         <v>1.53</v>
@@ -6000,7 +6000,7 @@
         <v>19.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>65</v>
+        <v>280</v>
       </c>
       <c r="AB22" t="n">
         <v>11</v>
@@ -6012,7 +6012,7 @@
         <v>13.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AF22" t="n">
         <v>19</v>
@@ -6024,52 +6024,52 @@
         <v>19</v>
       </c>
       <c r="AI22" t="n">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
         <v>280</v>
       </c>
       <c r="AK22" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AL22" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
         <v>75</v>
       </c>
       <c r="AO22" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AP22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR22" t="n">
         <v>15.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>36</v>
+        <v>7.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
         <v>14.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
@@ -6078,25 +6078,25 @@
         <v>15.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB22" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BC22" t="n">
         <v>16</v>
       </c>
       <c r="BD22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE22" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>22</v>
+        <v>7.4</v>
       </c>
       <c r="BH22" t="n">
         <v>3.3</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G23" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H23" t="n">
         <v>3.95</v>
       </c>
       <c r="I23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="n">
         <v>4.4</v>
       </c>
       <c r="K23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
         <v>1.2</v>
@@ -6221,40 +6221,40 @@
         <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R23" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="S23" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U23" t="n">
         <v>2.78</v>
       </c>
       <c r="V23" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X23" t="n">
         <v>36</v>
       </c>
       <c r="Y23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z23" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AA23" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AB23" t="n">
         <v>17</v>
@@ -6263,22 +6263,22 @@
         <v>12.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
         <v>17</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH23" t="n">
         <v>15</v>
       </c>
       <c r="AI23" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="n">
         <v>22</v>
@@ -6290,121 +6290,121 @@
         <v>23</v>
       </c>
       <c r="AM23" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS23" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AU23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY23" t="n">
         <v>10</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
         <v>13</v>
       </c>
       <c r="BA23" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC23" t="n">
         <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH23" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -6451,16 +6451,16 @@
         <v>2.58</v>
       </c>
       <c r="H24" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J24" t="n">
         <v>3.8</v>
       </c>
       <c r="K24" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
         <v>1.22</v>
@@ -6469,7 +6469,7 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.17</v>
@@ -6478,7 +6478,7 @@
         <v>2.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R24" t="n">
         <v>1.62</v>
@@ -6487,13 +6487,13 @@
         <v>2.26</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U24" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="V24" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W24" t="n">
         <v>1.63</v>
@@ -6502,16 +6502,16 @@
         <v>30</v>
       </c>
       <c r="Y24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA24" t="n">
-        <v>500</v>
+        <v>280</v>
       </c>
       <c r="AB24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC24" t="n">
         <v>11</v>
@@ -6520,22 +6520,22 @@
         <v>15</v>
       </c>
       <c r="AE24" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AF24" t="n">
         <v>21</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH24" t="n">
         <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AJ24" t="n">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="AK24" t="n">
         <v>24</v>
@@ -6553,22 +6553,22 @@
         <v>17.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR24" t="n">
         <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>30</v>
+        <v>6.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV24" t="n">
         <v>11.5</v>
@@ -6577,7 +6577,7 @@
         <v>14.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
@@ -6598,10 +6598,10 @@
         <v>14.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>23</v>
+        <v>6.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG24" t="n">
         <v>13</v>
@@ -6628,7 +6628,7 @@
         <v>6.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP24" t="n">
         <v>16.5</v>
@@ -6646,13 +6646,13 @@
         <v>7</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BV24" t="n">
         <v>21</v>
       </c>
       <c r="BW24" t="n">
-        <v>14</v>
+        <v>5.9</v>
       </c>
       <c r="BX24" t="n">
         <v>27</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -6732,13 +6732,13 @@
         <v>2.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R25" t="n">
         <v>1.64</v>
       </c>
       <c r="S25" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T25" t="n">
         <v>1.49</v>
@@ -6753,112 +6753,112 @@
         <v>1.53</v>
       </c>
       <c r="X25" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="Y25" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Z25" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AA25" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AB25" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC25" t="n">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="AD25" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE25" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AF25" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AG25" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH25" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI25" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AJ25" t="n">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AK25" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AL25" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
-        <v>65</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AO25" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AP25" t="n">
-        <v>13</v>
+        <v>1.69</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.4</v>
+        <v>2.46</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.5</v>
+        <v>2.02</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.9</v>
+        <v>1.76</v>
       </c>
       <c r="AT25" t="n">
-        <v>15</v>
+        <v>2.64</v>
       </c>
       <c r="AU25" t="n">
         <v>5.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>10.5</v>
+        <v>2.66</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="AX25" t="n">
-        <v>19</v>
+        <v>2.04</v>
       </c>
       <c r="AY25" t="n">
-        <v>11</v>
+        <v>2.66</v>
       </c>
       <c r="AZ25" t="n">
-        <v>12.5</v>
+        <v>2.72</v>
       </c>
       <c r="BA25" t="n">
-        <v>14.5</v>
+        <v>1.75</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.4</v>
+        <v>1.77</v>
       </c>
       <c r="BC25" t="n">
-        <v>21</v>
+        <v>1.68</v>
       </c>
       <c r="BD25" t="n">
-        <v>21</v>
+        <v>1.75</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.5</v>
+        <v>1.78</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="BH25" t="n">
         <v>4.7</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -6953,25 +6953,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="G26" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="H26" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K26" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
@@ -6986,7 +6986,7 @@
         <v>2.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R26" t="n">
         <v>1.59</v>
@@ -7001,10 +7001,10 @@
         <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W26" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="X26" t="n">
         <v>500</v>
@@ -7016,13 +7016,13 @@
         <v>500</v>
       </c>
       <c r="AA26" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB26" t="n">
         <v>500</v>
       </c>
       <c r="AC26" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD26" t="n">
         <v>500</v>
@@ -7037,13 +7037,13 @@
         <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI26" t="n">
         <v>500</v>
       </c>
       <c r="AJ26" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK26" t="n">
         <v>500</v>
@@ -7052,61 +7052,61 @@
         <v>500</v>
       </c>
       <c r="AM26" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN26" t="n">
         <v>500</v>
       </c>
-      <c r="AN26" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="AV26" t="n">
         <v>1.67</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AY26" t="n">
         <v>2.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BA26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BB26" t="n">
         <v>1.65</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BC26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD26" t="n">
         <v>1.63</v>
       </c>
-      <c r="BC26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BE26" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="BF26" t="n">
         <v>1.87</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -7207,64 +7207,64 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="G27" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H27" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K27" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P27" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R27" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="T27" t="n">
         <v>1.37</v>
       </c>
       <c r="U27" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="W27" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X27" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="Y27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z27" t="n">
         <v>25</v>
@@ -7273,10 +7273,10 @@
         <v>34</v>
       </c>
       <c r="AB27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD27" t="n">
         <v>14</v>
@@ -7285,22 +7285,22 @@
         <v>21</v>
       </c>
       <c r="AF27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI27" t="n">
         <v>23</v>
       </c>
       <c r="AJ27" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL27" t="n">
         <v>27</v>
@@ -7312,125 +7312,125 @@
         <v>13.5</v>
       </c>
       <c r="AO27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE27" t="n">
         <v>7.6</v>
       </c>
-      <c r="AP27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY27" t="n">
+      <c r="BF27" t="n">
         <v>5.6</v>
       </c>
-      <c r="AZ27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB27" t="n">
+      <c r="BG27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN27" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BN27" t="n">
+      <c r="BO27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ27" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>6.4</v>
       </c>
       <c r="BR27" t="n">
         <v>22</v>
       </c>
       <c r="BS27" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BT27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>14</v>
+      </c>
+      <c r="BW27" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BU27" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BV27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BW27" t="n">
-        <v>5.8</v>
       </c>
       <c r="BX27" t="n">
         <v>18.5</v>
       </c>
       <c r="BY27" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BZ27" t="n">
         <v>10.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -7464,16 +7464,16 @@
         <v>2.58</v>
       </c>
       <c r="G28" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="H28" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J28" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K28" t="n">
         <v>7</v>
@@ -7491,16 +7491,16 @@
         <v>1.12</v>
       </c>
       <c r="P28" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="R28" t="n">
         <v>1.85</v>
       </c>
       <c r="S28" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="T28" t="n">
         <v>1.39</v>
@@ -7509,10 +7509,10 @@
         <v>3.05</v>
       </c>
       <c r="V28" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="W28" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="X28" t="n">
         <v>500</v>
@@ -7524,13 +7524,13 @@
         <v>500</v>
       </c>
       <c r="AA28" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
         <v>500</v>
       </c>
       <c r="AC28" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
@@ -7545,13 +7545,13 @@
         <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI28" t="n">
         <v>500</v>
       </c>
       <c r="AJ28" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK28" t="n">
         <v>500</v>
@@ -7560,22 +7560,22 @@
         <v>500</v>
       </c>
       <c r="AM28" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO28" t="n">
         <v>38</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AQ28" t="n">
         <v>3.9</v>
       </c>
       <c r="AR28" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS28" t="n">
         <v>4.2</v>
@@ -7587,25 +7587,25 @@
         <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="AW28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA28" t="n">
         <v>3.95</v>
       </c>
-      <c r="AX28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4</v>
-      </c>
       <c r="BB28" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC28" t="n">
         <v>4.1</v>
@@ -7614,10 +7614,10 @@
         <v>4.1</v>
       </c>
       <c r="BE28" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BF28" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BG28" t="n">
         <v>3.2</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -7721,13 +7721,13 @@
         <v>7.6</v>
       </c>
       <c r="H29" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="I29" t="n">
         <v>1.5</v>
       </c>
       <c r="J29" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="K29" t="n">
         <v>7.4</v>
@@ -7760,10 +7760,10 @@
         <v>1.39</v>
       </c>
       <c r="U29" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="V29" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="W29" t="n">
         <v>1.15</v>
@@ -7772,19 +7772,19 @@
         <v>95</v>
       </c>
       <c r="Y29" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="Z29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA29" t="n">
         <v>19.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AC29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD29" t="n">
         <v>14.5</v>
@@ -7799,19 +7799,19 @@
         <v>34</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AJ29" t="n">
         <v>200</v>
       </c>
       <c r="AK29" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AL29" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM29" t="n">
         <v>55</v>
@@ -7823,34 +7823,34 @@
         <v>3.25</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.58</v>
+        <v>6.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AR29" t="n">
         <v>5.4</v>
       </c>
       <c r="AS29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU29" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AV29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX29" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AY29" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AZ29" t="n">
         <v>5.4</v>
@@ -7859,86 +7859,86 @@
         <v>5.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="BH29" t="n">
         <v>8</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ29" t="n">
         <v>9.6</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BN29" t="n">
         <v>13</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR29" t="n">
         <v>34</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT29" t="n">
         <v>5.8</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV29" t="n">
         <v>9</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BX29" t="n">
         <v>15</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BZ29" t="n">
         <v>6.6</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -7972,16 +7972,16 @@
         <v>3.25</v>
       </c>
       <c r="G30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H30" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I30" t="n">
         <v>2.06</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K30" t="n">
         <v>8</v>
@@ -7993,28 +7993,28 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O30" t="n">
         <v>1.04</v>
       </c>
       <c r="P30" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q30" t="n">
         <v>1.04</v>
       </c>
       <c r="R30" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="S30" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T30" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="U30" t="n">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="V30" t="n">
         <v>1.94</v>
@@ -8023,52 +8023,52 @@
         <v>1.28</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN30" t="n">
         <v>1000</v>
@@ -8077,58 +8077,58 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -8238,10 +8238,10 @@
         <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
@@ -8256,7 +8256,7 @@
         <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R31" t="n">
         <v>1.44</v>
@@ -8280,34 +8280,34 @@
         <v>500</v>
       </c>
       <c r="Y31" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="Z31" t="n">
         <v>500</v>
       </c>
       <c r="AA31" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB31" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AC31" t="n">
         <v>9</v>
       </c>
       <c r="AD31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF31" t="n">
         <v>500</v>
       </c>
-      <c r="AE31" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AG31" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI31" t="n">
         <v>500</v>
@@ -8322,25 +8322,25 @@
         <v>500</v>
       </c>
       <c r="AM31" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="AO31" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="AQ31" t="n">
         <v>13.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -8349,13 +8349,13 @@
         <v>7.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
         <v>9.6</v>
@@ -8364,25 +8364,25 @@
         <v>13.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF31" t="n">
         <v>11.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
@@ -8480,13 +8480,13 @@
         <v>1.93</v>
       </c>
       <c r="G32" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H32" t="n">
         <v>4.7</v>
       </c>
       <c r="I32" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
         <v>3.25</v>
@@ -8501,58 +8501,58 @@
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="O32" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
         <v>1.67</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R32" t="n">
         <v>1.24</v>
       </c>
       <c r="S32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U32" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V32" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W32" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="X32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="n">
         <v>14</v>
       </c>
       <c r="Z32" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AA32" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC32" t="n">
         <v>7.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE32" t="n">
-        <v>700</v>
+        <v>480</v>
       </c>
       <c r="AF32" t="n">
         <v>11.5</v>
@@ -8564,7 +8564,7 @@
         <v>23</v>
       </c>
       <c r="AI32" t="n">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="AJ32" t="n">
         <v>24</v>
@@ -8573,40 +8573,40 @@
         <v>25</v>
       </c>
       <c r="AL32" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AM32" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN32" t="n">
         <v>21</v>
       </c>
       <c r="AO32" t="n">
-        <v>140</v>
+        <v>290</v>
       </c>
       <c r="AP32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AS32" t="n">
         <v>12.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU32" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV32" t="n">
         <v>17.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AX32" t="n">
         <v>9.800000000000001</v>
@@ -8615,7 +8615,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA32" t="n">
         <v>12</v>
@@ -8633,7 +8633,7 @@
         <v>12.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG32" t="n">
         <v>12.5</v>
@@ -8654,16 +8654,16 @@
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>2.48</v>
+        <v>15</v>
       </c>
       <c r="BN32" t="n">
         <v>4.5</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP32" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ32" t="n">
         <v>8</v>
@@ -8681,16 +8681,16 @@
         <v>5.4</v>
       </c>
       <c r="BV32" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX32" t="n">
         <v>65</v>
       </c>
       <c r="BY32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ32" t="n">
         <v>36</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="H2" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I2" t="n">
         <v>2.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.28</v>
@@ -881,106 +881,106 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R2" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U2" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="V2" t="n">
         <v>1.66</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AB2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>46</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>100</v>
-      </c>
       <c r="AK2" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AL2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM2" t="n">
         <v>55</v>
       </c>
-      <c r="AM2" t="n">
-        <v>140</v>
-      </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP2" t="n">
         <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
@@ -992,95 +992,95 @@
         <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG2" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>29</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>11.5</v>
       </c>
       <c r="BH2" t="n">
         <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
         <v>16.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BX2" t="n">
         <v>25</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>16.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H3" t="n">
         <v>1.85</v>
@@ -1162,7 +1162,7 @@
         <v>2.08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
         <v>23</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="J4" t="n">
         <v>5.3</v>
@@ -1404,19 +1404,19 @@
         <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
         <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
         <v>75</v>
@@ -1473,7 +1473,7 @@
         <v>29</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>2.76</v>
       </c>
       <c r="AQ4" t="n">
         <v>7.4</v>
@@ -1482,19 +1482,19 @@
         <v>6.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
         <v>4.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AV4" t="n">
         <v>7.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AX4" t="n">
         <v>4.2</v>
@@ -1503,10 +1503,10 @@
         <v>4.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="BB4" t="n">
         <v>4.2</v>
@@ -1518,10 +1518,10 @@
         <v>4.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG4" t="n">
         <v>4.3</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G5" t="n">
         <v>1.8</v>
@@ -1634,7 +1634,7 @@
         <v>4.6</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.19</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
         <v>1.13</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
         <v>1.39</v>
@@ -1661,7 +1661,7 @@
         <v>1.94</v>
       </c>
       <c r="T5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U5" t="n">
         <v>2.76</v>
@@ -1670,7 +1670,7 @@
         <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X5" t="n">
         <v>500</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
         <v>5.1</v>
@@ -2142,7 +2142,7 @@
         <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.28</v>
@@ -2151,7 +2151,7 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.25</v>
@@ -2160,37 +2160,37 @@
         <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T7" t="n">
         <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V7" t="n">
         <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB7" t="n">
         <v>11.5</v>
@@ -2199,7 +2199,7 @@
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
         <v>60</v>
@@ -2217,7 +2217,7 @@
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
         <v>17</v>
@@ -2229,7 +2229,7 @@
         <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO7" t="n">
         <v>55</v>
@@ -2244,16 +2244,16 @@
         <v>32</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW7" t="n">
         <v>44</v>
@@ -2268,10 +2268,10 @@
         <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC7" t="n">
         <v>16</v>
@@ -2295,7 +2295,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
         <v>1.01</v>
@@ -2307,31 +2307,31 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ7" t="n">
         <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS7" t="n">
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU7" t="n">
         <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I8" t="n">
         <v>3.15</v>
@@ -2396,7 +2396,7 @@
         <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.22</v>
@@ -2432,10 +2432,10 @@
         <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="Y8" t="n">
         <v>16</v>
@@ -2450,7 +2450,7 @@
         <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>14</v>
@@ -2465,7 +2465,7 @@
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>42</v>
@@ -2498,7 +2498,7 @@
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
         <v>12</v>
@@ -2534,7 +2534,7 @@
         <v>14.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
         <v>12</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
         <v>320</v>
       </c>
       <c r="AN9" t="n">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="AO9" t="n">
         <v>9.800000000000001</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>1.69</v>
       </c>
       <c r="I10" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2910,7 +2910,7 @@
         <v>1.11</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
         <v>4.5</v>
@@ -2925,10 +2925,10 @@
         <v>1.69</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
         <v>1.73</v>
@@ -2937,7 +2937,7 @@
         <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="W10" t="n">
         <v>1.22</v>
@@ -2958,7 +2958,7 @@
         <v>25</v>
       </c>
       <c r="AC10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
         <v>12.5</v>
@@ -3006,7 +3006,7 @@
         <v>8.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
         <v>17.5</v>
@@ -3018,34 +3018,34 @@
         <v>7.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY10" t="n">
         <v>17.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG10" t="n">
         <v>6.6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.52</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H11" t="n">
         <v>2.78</v>
@@ -3158,7 +3158,7 @@
         <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.28</v>
@@ -3179,7 +3179,7 @@
         <v>1.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
         <v>2.48</v>
@@ -3194,7 +3194,7 @@
         <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
         <v>500</v>
@@ -3248,7 +3248,7 @@
         <v>42</v>
       </c>
       <c r="AO11" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
@@ -3344,7 +3344,7 @@
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
         <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
         <v>13</v>
@@ -3538,7 +3538,7 @@
         <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
         <v>11.5</v>
@@ -3556,7 +3556,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
         <v>70</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Z13" t="n">
         <v>34</v>
@@ -3762,16 +3762,16 @@
         <v>5.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS13" t="n">
         <v>5.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AU13" t="n">
         <v>5.6</v>
@@ -3786,10 +3786,10 @@
         <v>5.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA13" t="n">
         <v>5.6</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I14" t="n">
         <v>8.4</v>
@@ -3920,7 +3920,7 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.33</v>
@@ -3929,7 +3929,7 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.25</v>
@@ -3941,22 +3941,22 @@
         <v>1.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
         <v>2.92</v>
       </c>
       <c r="T14" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X14" t="n">
         <v>22</v>
@@ -3971,31 +3971,31 @@
         <v>280</v>
       </c>
       <c r="AB14" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
         <v>28</v>
       </c>
       <c r="AE14" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="AF14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG14" t="n">
         <v>9.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>110</v>
+        <v>470</v>
       </c>
       <c r="AJ14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK14" t="n">
         <v>15.5</v>
@@ -4022,22 +4022,22 @@
         <v>55</v>
       </c>
       <c r="AS14" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV14" t="n">
         <v>25</v>
       </c>
       <c r="AW14" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY14" t="n">
         <v>8.6</v>
@@ -4046,7 +4046,7 @@
         <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BB14" t="n">
         <v>12</v>
@@ -4058,7 +4058,7 @@
         <v>29</v>
       </c>
       <c r="BE14" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF14" t="n">
         <v>6.2</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H15" t="n">
         <v>6.6</v>
@@ -4210,7 +4210,7 @@
         <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X15" t="n">
         <v>16</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="G16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H16" t="n">
         <v>6.4</v>
@@ -4425,22 +4425,22 @@
         <v>7.4</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
         <v>1.23</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
         <v>5.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P16" t="n">
         <v>2.64</v>
@@ -4449,7 +4449,7 @@
         <v>1.52</v>
       </c>
       <c r="R16" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S16" t="n">
         <v>2.3</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
         <v>15.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
         <v>21</v>
@@ -4784,7 +4784,7 @@
         <v>19.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT17" t="n">
         <v>7.6</v>
@@ -4796,7 +4796,7 @@
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX17" t="n">
         <v>12.5</v>
@@ -4808,7 +4808,7 @@
         <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB17" t="n">
         <v>14.5</v>
@@ -4820,10 +4820,10 @@
         <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG17" t="n">
         <v>8.6</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -4930,13 +4930,13 @@
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
         <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
         <v>1.31</v>
@@ -4969,7 +4969,7 @@
         <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
         <v>1.94</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.66</v>
       </c>
       <c r="G19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H19" t="n">
         <v>5.4</v>
@@ -5226,7 +5226,7 @@
         <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -5364,7 +5364,7 @@
         <v>14</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
         <v>32</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G20" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I20" t="n">
         <v>6.2</v>
@@ -5444,7 +5444,7 @@
         <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.28</v>
@@ -5480,7 +5480,7 @@
         <v>1.19</v>
       </c>
       <c r="W20" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X20" t="n">
         <v>500</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G21" t="n">
         <v>1.82</v>
@@ -5698,7 +5698,7 @@
         <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.32</v>
@@ -5707,7 +5707,7 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
         <v>1.3</v>
@@ -5794,7 +5794,7 @@
         <v>14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR21" t="n">
         <v>9.199999999999999</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G22" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H22" t="n">
         <v>2.88</v>
@@ -5964,13 +5964,13 @@
         <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
         <v>1.29</v>
@@ -5979,7 +5979,7 @@
         <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
         <v>2.06</v>
@@ -6012,13 +6012,13 @@
         <v>13.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AF22" t="n">
         <v>19</v>
       </c>
       <c r="AG22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
         <v>19</v>
@@ -6054,7 +6054,7 @@
         <v>15.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT22" t="n">
         <v>8.800000000000001</v>
@@ -6090,13 +6090,13 @@
         <v>40</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH22" t="n">
         <v>3.3</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -6451,16 +6451,16 @@
         <v>2.58</v>
       </c>
       <c r="H24" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="I24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>3.8</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L24" t="n">
         <v>1.22</v>
@@ -6469,7 +6469,7 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O24" t="n">
         <v>1.17</v>
@@ -6493,10 +6493,10 @@
         <v>2.58</v>
       </c>
       <c r="V24" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W24" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X24" t="n">
         <v>30</v>
@@ -6634,7 +6634,7 @@
         <v>16.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="BR24" t="n">
         <v>24</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -6807,52 +6807,52 @@
         <v>970</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2.46</v>
+        <v>1.59</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.64</v>
+        <v>1.6</v>
       </c>
       <c r="AU25" t="n">
         <v>5.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.66</v>
+        <v>1.58</v>
       </c>
       <c r="AW25" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AX25" t="n">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="AY25" t="n">
-        <v>2.66</v>
+        <v>1.64</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="BF25" t="n">
         <v>3</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         <v>2.36</v>
       </c>
       <c r="J27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
         <v>5</v>
@@ -7231,7 +7231,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O27" t="n">
         <v>1.11</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -7485,13 +7485,13 @@
         <v>1.02</v>
       </c>
       <c r="N28" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="O28" t="n">
         <v>1.12</v>
       </c>
       <c r="P28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q28" t="n">
         <v>1.36</v>
@@ -7500,7 +7500,7 @@
         <v>1.85</v>
       </c>
       <c r="S28" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="T28" t="n">
         <v>1.39</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
         <v>1.52</v>
       </c>
       <c r="T29" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="U29" t="n">
         <v>2.92</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
         <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L31" t="n">
         <v>1.27</v>
@@ -8337,7 +8337,7 @@
         <v>13.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS31" t="n">
         <v>9.4</v>
@@ -8364,16 +8364,16 @@
         <v>13.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB31" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC31" t="n">
         <v>10.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE31" t="n">
         <v>9.6</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>
@@ -8477,16 +8477,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G32" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H32" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>3.25</v>
@@ -8501,7 +8501,7 @@
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O32" t="n">
         <v>1.44</v>
@@ -8516,7 +8516,7 @@
         <v>1.24</v>
       </c>
       <c r="S32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T32" t="n">
         <v>2.02</v>
@@ -8525,10 +8525,10 @@
         <v>1.86</v>
       </c>
       <c r="V32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W32" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X32" t="n">
         <v>11</v>
@@ -8549,7 +8549,7 @@
         <v>7.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE32" t="n">
         <v>480</v>
@@ -8588,7 +8588,7 @@
         <v>9.4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR32" t="n">
         <v>27</v>
@@ -8606,7 +8606,7 @@
         <v>17.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX32" t="n">
         <v>9.800000000000001</v>
@@ -8630,7 +8630,7 @@
         <v>40</v>
       </c>
       <c r="BE32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF32" t="n">
         <v>17.5</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-25 20:53:07</t>
+          <t>2026-06-25 23:09:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.95</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U2" t="n">
         <v>2.72</v>
       </c>
       <c r="V2" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="W2" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
         <v>23</v>
@@ -917,28 +917,28 @@
         <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE2" t="n">
         <v>22</v>
       </c>
-      <c r="AC2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>23</v>
-      </c>
       <c r="AF2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
         <v>14.5</v>
@@ -947,10 +947,10 @@
         <v>29</v>
       </c>
       <c r="AJ2" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL2" t="n">
         <v>32</v>
@@ -959,25 +959,25 @@
         <v>55</v>
       </c>
       <c r="AN2" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP2" t="n">
         <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU2" t="n">
         <v>8.800000000000001</v>
@@ -986,37 +986,37 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BC2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="n">
         <v>4.6</v>
@@ -1037,16 +1037,16 @@
         <v>10.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR2" t="n">
         <v>26</v>
@@ -1055,32 +1055,32 @@
         <v>8.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="I3" t="n">
         <v>1.92</v>
@@ -1126,34 +1126,34 @@
         <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="T3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
         <v>2.38</v>
@@ -1162,13 +1162,13 @@
         <v>2.08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
         <v>13.5</v>
@@ -1192,10 +1192,10 @@
         <v>50</v>
       </c>
       <c r="AG3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI3" t="n">
         <v>32</v>
@@ -1204,13 +1204,13 @@
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="n">
         <v>60</v>
@@ -1225,37 +1225,37 @@
         <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC3" t="n">
         <v>34</v>
@@ -1264,61 +1264,61 @@
         <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.6</v>
       </c>
       <c r="BK3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT3" t="n">
         <v>5</v>
       </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BU3" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BV3" t="n">
         <v>12.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1327,14 +1327,14 @@
         <v>7.2</v>
       </c>
       <c r="BZ3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -1365,55 +1365,55 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="G4" t="n">
         <v>9.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="I4" t="n">
         <v>1.44</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S4" t="n">
         <v>2.52</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T4" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="V4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
@@ -1422,154 +1422,154 @@
         <v>75</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>15</v>
       </c>
       <c r="AB4" t="n">
         <v>85</v>
       </c>
       <c r="AC4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>310</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>210</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>140</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
         <v>970</v>
       </c>
-      <c r="AD4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>970</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>150</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BP4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="BV4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="n">
         <v>1.8</v>
@@ -1628,28 +1628,28 @@
         <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
         <v>4.6</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.13</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q5" t="n">
         <v>1.39</v>
@@ -1670,7 +1670,7 @@
         <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X5" t="n">
         <v>500</v>
@@ -1721,61 +1721,61 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY5" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="BB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC5" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC5" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BG5" t="n">
         <v>4.7</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -1891,13 +1891,13 @@
         <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.05</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.3</v>
@@ -1915,10 +1915,10 @@
         <v>2.78</v>
       </c>
       <c r="T6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V6" t="n">
         <v>1.21</v>
@@ -1981,7 +1981,7 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.2</v>
@@ -1990,31 +1990,31 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="AT6" t="n">
         <v>3.95</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AV6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW6" t="n">
         <v>5.2</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
         <v>4.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA6" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.2</v>
       </c>
       <c r="BB6" t="n">
         <v>5.2</v>
@@ -2023,16 +2023,16 @@
         <v>5.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH6" t="n">
         <v>3.65</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G7" t="n">
         <v>1.82</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
         <v>4.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
@@ -2157,22 +2157,22 @@
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
         <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
         <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
         <v>1.25</v>
@@ -2181,7 +2181,7 @@
         <v>2.2</v>
       </c>
       <c r="X7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
         <v>19.5</v>
@@ -2196,7 +2196,7 @@
         <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD7" t="n">
         <v>19</v>
@@ -2217,7 +2217,7 @@
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK7" t="n">
         <v>17</v>
@@ -2229,7 +2229,7 @@
         <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO7" t="n">
         <v>55</v>
@@ -2247,7 +2247,7 @@
         <v>12</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU7" t="n">
         <v>8.6</v>
@@ -2268,22 +2268,22 @@
         <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BB7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC7" t="n">
         <v>16</v>
       </c>
       <c r="BD7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG7" t="n">
         <v>40</v>
@@ -2292,7 +2292,7 @@
         <v>4.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
@@ -2319,7 +2319,7 @@
         <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
         <v>2.82</v>
@@ -2393,31 +2393,31 @@
         <v>3.15</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
         <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
         <v>1.66</v>
       </c>
       <c r="R8" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
         <v>2.64</v>
@@ -2432,7 +2432,7 @@
         <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
         <v>50</v>
@@ -2552,7 +2552,7 @@
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2564,47 +2564,47 @@
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I9" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="J9" t="n">
         <v>3.95</v>
@@ -2653,7 +2653,7 @@
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
@@ -2665,28 +2665,28 @@
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R9" t="n">
         <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
         <v>1.66</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X9" t="n">
         <v>24</v>
@@ -2695,10 +2695,10 @@
         <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB9" t="n">
         <v>21</v>
@@ -2707,7 +2707,7 @@
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2722,7 +2722,7 @@
         <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AJ9" t="n">
         <v>900</v>
@@ -2740,7 +2740,7 @@
         <v>60</v>
       </c>
       <c r="AO9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AP9" t="n">
         <v>19</v>
@@ -2779,16 +2779,16 @@
         <v>14.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF9" t="n">
         <v>21</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -2892,10 +2892,10 @@
         <v>4.8</v>
       </c>
       <c r="G10" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="I10" t="n">
         <v>1.8</v>
@@ -2904,31 +2904,31 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R10" t="n">
         <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="T10" t="n">
         <v>1.73</v>
@@ -2940,7 +2940,7 @@
         <v>2.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X10" t="n">
         <v>21</v>
@@ -3051,68 +3051,68 @@
         <v>6.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -3143,25 +3143,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H11" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="I11" t="n">
         <v>2.98</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.04</v>
@@ -3170,25 +3170,25 @@
         <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.58</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.6</v>
-      </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="T11" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="U11" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="V11" t="n">
         <v>1.51</v>
@@ -3197,112 +3197,112 @@
         <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z11" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AB11" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AF11" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>14.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AJ11" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AK11" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>42</v>
+        <v>15.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>970</v>
+        <v>46</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
         <v>15.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU11" t="n">
         <v>7.8</v>
       </c>
-      <c r="AT11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AV11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB11" t="n">
         <v>16</v>
       </c>
-      <c r="BB11" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BC11" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
@@ -3344,7 +3344,7 @@
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -3397,61 +3397,61 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="M12" t="n">
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O12" t="n">
         <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="R12" t="n">
         <v>1.54</v>
       </c>
       <c r="S12" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="X12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y12" t="n">
         <v>18.5</v>
@@ -3463,22 +3463,22 @@
         <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD12" t="n">
         <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
         <v>16.5</v>
@@ -3487,7 +3487,7 @@
         <v>42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -3511,10 +3511,10 @@
         <v>14.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT12" t="n">
         <v>10.5</v>
@@ -3526,7 +3526,7 @@
         <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
         <v>13</v>
@@ -3538,25 +3538,25 @@
         <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC12" t="n">
         <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3568,7 +3568,7 @@
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3586,13 +3586,13 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
@@ -3616,11 +3616,11 @@
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -3651,76 +3651,76 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="G13" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="I13" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="M13" t="n">
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P13" t="n">
         <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S13" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="T13" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="U13" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="V13" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W13" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X13" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="Z13" t="n">
         <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AC13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
         <v>13</v>
@@ -3732,7 +3732,7 @@
         <v>32</v>
       </c>
       <c r="AG13" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AH13" t="n">
         <v>22</v>
@@ -3753,25 +3753,25 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AR13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS13" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS13" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AT13" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AU13" t="n">
         <v>5.6</v>
@@ -3780,101 +3780,101 @@
         <v>6.4</v>
       </c>
       <c r="AW13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD13" t="n">
         <v>5.3</v>
       </c>
-      <c r="AX13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC13" t="n">
+      <c r="BE13" t="n">
         <v>5.7</v>
       </c>
-      <c r="BD13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BF13" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG13" t="n">
         <v>4.3</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU13" t="n">
         <v>4.3</v>
       </c>
       <c r="BV13" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BZ13" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H14" t="n">
         <v>7.6</v>
@@ -3923,40 +3923,40 @@
         <v>5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
         <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
         <v>1.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
         <v>2.92</v>
       </c>
       <c r="T14" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X14" t="n">
         <v>22</v>
@@ -3965,10 +3965,10 @@
         <v>32</v>
       </c>
       <c r="Z14" t="n">
-        <v>540</v>
+        <v>160</v>
       </c>
       <c r="AA14" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AB14" t="n">
         <v>8.6</v>
@@ -3989,16 +3989,16 @@
         <v>9.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>470</v>
       </c>
       <c r="AJ14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL14" t="n">
         <v>34</v>
@@ -4019,7 +4019,7 @@
         <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>55</v>
+        <v>14.5</v>
       </c>
       <c r="AS14" t="n">
         <v>17</v>
@@ -4037,7 +4037,7 @@
         <v>15.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
         <v>8.6</v>
@@ -4067,7 +4067,7 @@
         <v>16.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI14" t="n">
         <v>3.6</v>
@@ -4076,13 +4076,13 @@
         <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BL14" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BN14" t="n">
         <v>4.5</v>
@@ -4094,31 +4094,31 @@
         <v>10.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BR14" t="n">
         <v>27</v>
       </c>
       <c r="BS14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BT14" t="n">
         <v>13</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV14" t="n">
         <v>75</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX14" t="n">
         <v>75</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H15" t="n">
         <v>6.6</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -4177,43 +4177,43 @@
         <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
         <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T15" t="n">
         <v>1.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W15" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y15" t="n">
         <v>24</v>
@@ -4225,7 +4225,7 @@
         <v>700</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC15" t="n">
         <v>9.800000000000001</v>
@@ -4255,7 +4255,7 @@
         <v>19</v>
       </c>
       <c r="AL15" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="AM15" t="n">
         <v>700</v>
@@ -4273,13 +4273,13 @@
         <v>18.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU15" t="n">
         <v>8</v>
@@ -4288,19 +4288,19 @@
         <v>21</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX15" t="n">
         <v>8</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
         <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
         <v>13</v>
@@ -4309,22 +4309,22 @@
         <v>15</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF15" t="n">
         <v>8.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH15" t="n">
         <v>3.95</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BJ15" t="n">
         <v>13.5</v>
@@ -4369,7 +4369,7 @@
         <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BY15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -4413,46 +4413,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="G16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H16" t="n">
         <v>6.4</v>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J16" t="n">
         <v>4.7</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T16" t="n">
         <v>1.66</v>
@@ -4461,7 +4461,7 @@
         <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W16" t="n">
         <v>2.72</v>
@@ -4512,7 +4512,7 @@
         <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>260</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
         <v>6</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -4667,58 +4667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G17" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="H17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I17" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.4</v>
       </c>
-      <c r="P17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.37</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="X17" t="n">
         <v>12</v>
@@ -4736,7 +4736,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
         <v>15.5</v>
@@ -4751,7 +4751,7 @@
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
         <v>150</v>
@@ -4760,7 +4760,7 @@
         <v>130</v>
       </c>
       <c r="AK17" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL17" t="n">
         <v>50</v>
@@ -4769,7 +4769,7 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AO17" t="n">
         <v>90</v>
@@ -4784,7 +4784,7 @@
         <v>19.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT17" t="n">
         <v>7.6</v>
@@ -4796,7 +4796,7 @@
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX17" t="n">
         <v>12.5</v>
@@ -4808,7 +4808,7 @@
         <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB17" t="n">
         <v>14.5</v>
@@ -4820,10 +4820,10 @@
         <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG17" t="n">
         <v>8.6</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
         <v>2.06</v>
@@ -4930,67 +4930,67 @@
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J18" t="n">
         <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="R18" t="n">
         <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W18" t="n">
         <v>1.94</v>
       </c>
       <c r="X18" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y18" t="n">
         <v>16.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>17</v>
       </c>
       <c r="Z18" t="n">
         <v>34</v>
       </c>
       <c r="AA18" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>18</v>
@@ -5005,7 +5005,7 @@
         <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
         <v>130</v>
@@ -5020,13 +5020,13 @@
         <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN18" t="n">
         <v>14.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AP18" t="n">
         <v>13</v>
@@ -5038,7 +5038,7 @@
         <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT18" t="n">
         <v>8.199999999999999</v>
@@ -5050,7 +5050,7 @@
         <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -5062,7 +5062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB18" t="n">
         <v>19</v>
@@ -5071,10 +5071,10 @@
         <v>17</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18" t="n">
         <v>11.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -5175,64 +5175,64 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="G19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I19" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
         <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P19" t="n">
         <v>1.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="R19" t="n">
         <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U19" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="V19" t="n">
         <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="Z19" t="n">
         <v>500</v>
@@ -5241,10 +5241,10 @@
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>500</v>
@@ -5286,13 +5286,13 @@
         <v>7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AT19" t="n">
         <v>4.9</v>
@@ -5301,10 +5301,10 @@
         <v>4.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX19" t="n">
         <v>5.6</v>
@@ -5313,61 +5313,61 @@
         <v>5.8</v>
       </c>
       <c r="AZ19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB19" t="n">
         <v>6.4</v>
       </c>
-      <c r="BA19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BC19" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BJ19" t="n">
         <v>12.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL19" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BM19" t="n">
         <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO19" t="n">
         <v>3.35</v>
       </c>
       <c r="BP19" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS19" t="n">
         <v>1.01</v>
@@ -5385,7 +5385,7 @@
         <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -5429,64 +5429,64 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I20" t="n">
         <v>6.2</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
         <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
         <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R20" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="T20" t="n">
         <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V20" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="X20" t="n">
         <v>500</v>
       </c>
       <c r="Y20" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="Z20" t="n">
         <v>500</v>
@@ -5507,7 +5507,7 @@
         <v>700</v>
       </c>
       <c r="AF20" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>10.5</v>
@@ -5519,19 +5519,19 @@
         <v>700</v>
       </c>
       <c r="AJ20" t="n">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="AK20" t="n">
         <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO20" t="n">
         <v>700</v>
@@ -5543,13 +5543,13 @@
         <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
         <v>8.800000000000001</v>
@@ -5558,7 +5558,7 @@
         <v>15</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX20" t="n">
         <v>9.6</v>
@@ -5570,7 +5570,7 @@
         <v>11.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB20" t="n">
         <v>8.4</v>
@@ -5579,16 +5579,16 @@
         <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF20" t="n">
         <v>6.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G21" t="n">
         <v>1.82</v>
@@ -5692,7 +5692,7 @@
         <v>4.9</v>
       </c>
       <c r="I21" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
@@ -5701,13 +5701,13 @@
         <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>1.3</v>
@@ -5716,46 +5716,46 @@
         <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W21" t="n">
         <v>2.22</v>
       </c>
       <c r="X21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z21" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AA21" t="n">
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
         <v>320</v>
@@ -5767,7 +5767,7 @@
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI21" t="n">
         <v>320</v>
@@ -5779,7 +5779,7 @@
         <v>18.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AM21" t="n">
         <v>580</v>
@@ -5797,10 +5797,10 @@
         <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT21" t="n">
         <v>7.8</v>
@@ -5812,7 +5812,7 @@
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>8.199999999999999</v>
@@ -5824,7 +5824,7 @@
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB21" t="n">
         <v>16.5</v>
@@ -5833,25 +5833,25 @@
         <v>16</v>
       </c>
       <c r="BD21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BE21" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF21" t="n">
         <v>9.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI21" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK21" t="n">
         <v>6.2</v>
@@ -5860,43 +5860,43 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN21" t="n">
         <v>4.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BP21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR21" t="n">
         <v>27</v>
       </c>
       <c r="BS21" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT21" t="n">
         <v>8.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX21" t="n">
         <v>55</v>
       </c>
       <c r="BY21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -5940,40 +5940,40 @@
         <v>2.76</v>
       </c>
       <c r="G22" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H22" t="n">
         <v>2.88</v>
       </c>
       <c r="I22" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
         <v>3.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
         <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -5985,10 +5985,10 @@
         <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W22" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X22" t="n">
         <v>12.5</v>
@@ -6000,7 +6000,7 @@
         <v>19.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>280</v>
+        <v>48</v>
       </c>
       <c r="AB22" t="n">
         <v>11</v>
@@ -6042,7 +6042,7 @@
         <v>75</v>
       </c>
       <c r="AO22" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AP22" t="n">
         <v>10</v>
@@ -6090,10 +6090,10 @@
         <v>40</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG22" t="n">
         <v>7.6</v>
@@ -6102,55 +6102,55 @@
         <v>3.3</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN22" t="n">
         <v>6</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS22" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT22" t="n">
         <v>6</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BV22" t="n">
         <v>24</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="BX22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY22" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G23" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
         <v>4.5</v>
@@ -6209,7 +6209,7 @@
         <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
@@ -6224,22 +6224,22 @@
         <v>3.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R23" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="T23" t="n">
         <v>1.48</v>
       </c>
       <c r="U23" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W23" t="n">
         <v>2.12</v>
@@ -6272,7 +6272,7 @@
         <v>17</v>
       </c>
       <c r="AG23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
         <v>15</v>
@@ -6293,7 +6293,7 @@
         <v>200</v>
       </c>
       <c r="AN23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO23" t="n">
         <v>25</v>
@@ -6305,13 +6305,13 @@
         <v>13</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU23" t="n">
         <v>10.5</v>
@@ -6344,7 +6344,7 @@
         <v>19.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF23" t="n">
         <v>5.7</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -6445,127 +6445,127 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="G24" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K24" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="M24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P24" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T24" t="n">
         <v>1.5</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.48</v>
       </c>
-      <c r="U24" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.46</v>
-      </c>
       <c r="W24" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="X24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA24" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AB24" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AF24" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AG24" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AJ24" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AK24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AM24" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="AR24" t="n">
         <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU24" t="n">
         <v>8.6</v>
@@ -6598,7 +6598,7 @@
         <v>14.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF24" t="n">
         <v>9.6</v>
@@ -6616,31 +6616,31 @@
         <v>9</v>
       </c>
       <c r="BK24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BN24" t="n">
         <v>6.2</v>
       </c>
-      <c r="BL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BO24" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BP24" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="BR24" t="n">
         <v>24</v>
       </c>
       <c r="BS24" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT24" t="n">
         <v>7</v>
@@ -6652,13 +6652,13 @@
         <v>21</v>
       </c>
       <c r="BW24" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX24" t="n">
         <v>27</v>
       </c>
       <c r="BY24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -6699,58 +6699,58 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G25" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="H25" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="I25" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
         <v>4.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="O25" t="n">
         <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R25" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S25" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="T25" t="n">
         <v>1.49</v>
       </c>
       <c r="U25" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V25" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W25" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X25" t="n">
         <v>500</v>
@@ -6807,58 +6807,58 @@
         <v>970</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.59</v>
+        <v>2.18</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="AS25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.66</v>
       </c>
       <c r="BF25" t="n">
         <v>3</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.94</v>
+        <v>9.6</v>
       </c>
       <c r="BH25" t="n">
         <v>4.7</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -6953,46 +6953,46 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="G26" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="H26" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="R26" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="S26" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -7001,10 +7001,10 @@
         <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="W26" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X26" t="n">
         <v>500</v>
@@ -7037,7 +7037,7 @@
         <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI26" t="n">
         <v>500</v>
@@ -7055,7 +7055,7 @@
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -7064,49 +7064,49 @@
         <v>1.65</v>
       </c>
       <c r="AQ26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR26" t="n">
         <v>1.65</v>
       </c>
-      <c r="AR26" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AS26" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AU26" t="n">
         <v>5.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AY26" t="n">
         <v>2.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BB26" t="n">
         <v>1.65</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="BF26" t="n">
         <v>1.87</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -7207,28 +7207,28 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H27" t="n">
         <v>2.12</v>
       </c>
       <c r="I27" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="J27" t="n">
         <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N27" t="n">
         <v>8.199999999999999</v>
@@ -7240,49 +7240,49 @@
         <v>3.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S27" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="T27" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="U27" t="n">
         <v>3.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W27" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X27" t="n">
         <v>110</v>
       </c>
       <c r="Y27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB27" t="n">
         <v>28</v>
       </c>
       <c r="AC27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF27" t="n">
         <v>32</v>
@@ -7300,7 +7300,7 @@
         <v>120</v>
       </c>
       <c r="AK27" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AL27" t="n">
         <v>27</v>
@@ -7312,7 +7312,7 @@
         <v>13.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP27" t="n">
         <v>7.8</v>
@@ -7330,31 +7330,31 @@
         <v>7</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AW27" t="n">
         <v>6.4</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AZ27" t="n">
         <v>5.7</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB27" t="n">
         <v>8</v>
       </c>
       <c r="BC27" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BD27" t="n">
         <v>7</v>
@@ -7366,19 +7366,19 @@
         <v>5.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH27" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BI27" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
@@ -7387,16 +7387,16 @@
         <v>10</v>
       </c>
       <c r="BN27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO27" t="n">
         <v>5.8</v>
       </c>
       <c r="BP27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BQ27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR27" t="n">
         <v>22</v>
@@ -7405,10 +7405,10 @@
         <v>8</v>
       </c>
       <c r="BT27" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV27" t="n">
         <v>14</v>
@@ -7420,17 +7420,17 @@
         <v>18.5</v>
       </c>
       <c r="BY27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ27" t="n">
         <v>10.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -7461,58 +7461,58 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="G28" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="I28" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="J28" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="K28" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M28" t="n">
         <v>1.02</v>
       </c>
       <c r="N28" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P28" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="Q28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T28" t="n">
         <v>1.36</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.39</v>
-      </c>
       <c r="U28" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="V28" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="X28" t="n">
         <v>500</v>
@@ -7530,7 +7530,7 @@
         <v>500</v>
       </c>
       <c r="AC28" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
@@ -7545,7 +7545,7 @@
         <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI28" t="n">
         <v>500</v>
@@ -7566,73 +7566,73 @@
         <v>55</v>
       </c>
       <c r="AO28" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AU28" t="n">
         <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="BE28" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="BF28" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="BG28" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.65</v>
+        <v>1.95</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.68</v>
+        <v>1.23</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7644,13 +7644,13 @@
         <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.63</v>
+        <v>5.4</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
@@ -7662,29 +7662,29 @@
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.95</v>
+        <v>1.99</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.07</v>
+        <v>5.5</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
         <v>7.6</v>
@@ -7724,46 +7724,46 @@
         <v>1.39</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="J29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="O29" t="n">
         <v>1.06</v>
       </c>
       <c r="P29" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R29" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="S29" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="T29" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="U29" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="V29" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="W29" t="n">
         <v>1.15</v>
@@ -7772,7 +7772,7 @@
         <v>95</v>
       </c>
       <c r="Y29" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="Z29" t="n">
         <v>23</v>
@@ -7787,16 +7787,16 @@
         <v>21</v>
       </c>
       <c r="AD29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF29" t="n">
         <v>110</v>
       </c>
       <c r="AG29" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AH29" t="n">
         <v>23</v>
@@ -7820,58 +7820,58 @@
         <v>34</v>
       </c>
       <c r="AO29" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.4</v>
+        <v>15.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY29" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU29" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>5.4</v>
+        <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="BB29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD29" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BE29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF29" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>5.8</v>
       </c>
       <c r="BG29" t="n">
         <v>2.52</v>
@@ -7883,7 +7883,7 @@
         <v>4</v>
       </c>
       <c r="BJ29" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK29" t="n">
         <v>4.4</v>
@@ -7892,7 +7892,7 @@
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BN29" t="n">
         <v>13</v>
@@ -7916,13 +7916,13 @@
         <v>5.8</v>
       </c>
       <c r="BU29" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="BV29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BX29" t="n">
         <v>15</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -7969,58 +7969,58 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G30" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="I30" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="J30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K30" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="P30" t="n">
-        <v>2.36</v>
+        <v>4.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="R30" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="S30" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="T30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="U30" t="n">
         <v>3.7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X30" t="n">
         <v>500</v>
@@ -8077,58 +8077,58 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="BF30" t="n">
         <v>1.55</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -8226,10 +8226,10 @@
         <v>2.1</v>
       </c>
       <c r="G31" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H31" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I31" t="n">
         <v>3.85</v>
@@ -8238,16 +8238,16 @@
         <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O31" t="n">
         <v>1.25</v>
@@ -8256,16 +8256,16 @@
         <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S31" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T31" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U31" t="n">
         <v>2.3</v>
@@ -8274,7 +8274,7 @@
         <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X31" t="n">
         <v>500</v>
@@ -8316,7 +8316,7 @@
         <v>500</v>
       </c>
       <c r="AK31" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL31" t="n">
         <v>500</v>
@@ -8328,7 +8328,7 @@
         <v>34</v>
       </c>
       <c r="AO31" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP31" t="n">
         <v>9</v>
@@ -8355,7 +8355,7 @@
         <v>16</v>
       </c>
       <c r="AX31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
         <v>9.6</v>
@@ -8376,7 +8376,7 @@
         <v>8.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF31" t="n">
         <v>11.5</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>
@@ -8477,58 +8477,58 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G32" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H32" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K32" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M32" t="n">
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O32" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P32" t="n">
         <v>1.67</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T32" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V32" t="n">
         <v>1.25</v>
       </c>
       <c r="W32" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X32" t="n">
         <v>11</v>
@@ -8546,10 +8546,10 @@
         <v>7.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE32" t="n">
         <v>480</v>
@@ -8561,19 +8561,19 @@
         <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI32" t="n">
         <v>450</v>
       </c>
       <c r="AJ32" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK32" t="n">
         <v>25</v>
       </c>
       <c r="AL32" t="n">
-        <v>290</v>
+        <v>48</v>
       </c>
       <c r="AM32" t="n">
         <v>580</v>
@@ -8594,7 +8594,7 @@
         <v>27</v>
       </c>
       <c r="AS32" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT32" t="n">
         <v>6.4</v>
@@ -8603,7 +8603,7 @@
         <v>6.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW32" t="n">
         <v>14</v>
@@ -8618,7 +8618,7 @@
         <v>19.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB32" t="n">
         <v>21</v>
@@ -8630,16 +8630,16 @@
         <v>40</v>
       </c>
       <c r="BE32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF32" t="n">
         <v>17.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BI32" t="n">
         <v>2.5</v>
@@ -8648,13 +8648,13 @@
         <v>11</v>
       </c>
       <c r="BK32" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN32" t="n">
         <v>4.5</v>
@@ -8666,19 +8666,19 @@
         <v>15.5</v>
       </c>
       <c r="BQ32" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR32" t="n">
         <v>36</v>
       </c>
       <c r="BS32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT32" t="n">
         <v>8</v>
       </c>
       <c r="BU32" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV32" t="n">
         <v>46</v>
@@ -8696,11 +8696,11 @@
         <v>36</v>
       </c>
       <c r="CA32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-25 23:09:09</t>
+          <t>2026-06-26 01:25:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G2" t="n">
         <v>3.05</v>
@@ -866,7 +866,7 @@
         <v>2.38</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="J2" t="n">
         <v>3.95</v>
@@ -881,34 +881,34 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X2" t="n">
         <v>23</v>
@@ -917,7 +917,7 @@
         <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA2" t="n">
         <v>34</v>
@@ -926,7 +926,7 @@
         <v>18.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
         <v>12</v>
@@ -935,10 +935,10 @@
         <v>22</v>
       </c>
       <c r="AF2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>14.5</v>
@@ -956,7 +956,7 @@
         <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN2" t="n">
         <v>18.5</v>
@@ -1001,7 +1001,7 @@
         <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BC2" t="n">
         <v>25</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>4.4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="I3" t="n">
         <v>1.92</v>
@@ -1141,19 +1141,19 @@
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R3" t="n">
         <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="U3" t="n">
         <v>2.38</v>
@@ -1162,16 +1162,16 @@
         <v>2.08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
         <v>21</v>
@@ -1204,7 +1204,7 @@
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
         <v>65</v>
@@ -1231,7 +1231,7 @@
         <v>17.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AU3" t="n">
         <v>8.4</v>
@@ -1246,16 +1246,16 @@
         <v>29</v>
       </c>
       <c r="AY3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BC3" t="n">
         <v>34</v>
@@ -1264,7 +1264,7 @@
         <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
         <v>32</v>
@@ -1282,7 +1282,7 @@
         <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,7 +1294,7 @@
         <v>8.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1303,7 +1303,7 @@
         <v>7.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
         <v>8.199999999999999</v>
@@ -1321,20 +1321,20 @@
         <v>9.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="BZ3" t="n">
         <v>18</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="I4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="J4" t="n">
         <v>5.2</v>
@@ -1383,7 +1383,7 @@
         <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
@@ -1407,7 +1407,7 @@
         <v>2.52</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U4" t="n">
         <v>2.04</v>
@@ -1434,7 +1434,7 @@
         <v>85</v>
       </c>
       <c r="AC4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD4" t="n">
         <v>12</v>
@@ -1443,7 +1443,7 @@
         <v>17.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="n">
         <v>40</v>
@@ -1473,19 +1473,19 @@
         <v>5.9</v>
       </c>
       <c r="AP4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR4" t="n">
         <v>8</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AS4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="AU4" t="n">
         <v>10</v>
@@ -1494,13 +1494,13 @@
         <v>7.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AZ4" t="n">
         <v>18</v>
@@ -1512,16 +1512,16 @@
         <v>5.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BF4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG4" t="n">
         <v>4.4</v>
@@ -1566,7 +1566,7 @@
         <v>4.1</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV4" t="n">
         <v>10</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H5" t="n">
         <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.2</v>
@@ -1658,19 +1658,19 @@
         <v>1.89</v>
       </c>
       <c r="S5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
         <v>2.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X5" t="n">
         <v>500</v>
@@ -1721,58 +1721,58 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.66</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY5" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="BF5" t="n">
         <v>3.6</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -1879,10 +1879,10 @@
         <v>1.95</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>3.65</v>
@@ -1891,13 +1891,13 @@
         <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.3</v>
@@ -1912,7 +1912,7 @@
         <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
         <v>1.8</v>
@@ -1921,7 +1921,7 @@
         <v>1.95</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
         <v>2.04</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2127,154 +2127,154 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N7" t="n">
         <v>4.3</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AA7" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="n">
         <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AG7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT7" t="n">
         <v>10</v>
       </c>
-      <c r="AH7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW7" t="n">
         <v>34</v>
       </c>
-      <c r="AM7" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ7" t="n">
+      <c r="AX7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC7" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>16</v>
       </c>
       <c r="BD7" t="n">
         <v>25</v>
@@ -2283,61 +2283,61 @@
         <v>34</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>40</v>
+        <v>11.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
         <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM7" t="n">
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BS7" t="n">
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BW7" t="n">
         <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BY7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2387,10 +2387,10 @@
         <v>2.52</v>
       </c>
       <c r="H8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -2423,7 +2423,7 @@
         <v>2.64</v>
       </c>
       <c r="T8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U8" t="n">
         <v>2.44</v>
@@ -2444,10 +2444,10 @@
         <v>65</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC8" t="n">
         <v>9.199999999999999</v>
@@ -2471,7 +2471,7 @@
         <v>42</v>
       </c>
       <c r="AJ8" t="n">
-        <v>170</v>
+        <v>38</v>
       </c>
       <c r="AK8" t="n">
         <v>29</v>
@@ -2489,7 +2489,7 @@
         <v>21</v>
       </c>
       <c r="AP8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
         <v>13.5</v>
@@ -2498,43 +2498,43 @@
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AW8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX8" t="n">
         <v>14.5</v>
       </c>
-      <c r="AX8" t="n">
-        <v>15</v>
-      </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="BA8" t="n">
-        <v>16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8" t="n">
         <v>14.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BD8" t="n">
         <v>14.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
         <v>12</v>
@@ -2543,68 +2543,68 @@
         <v>17</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>4.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="I9" t="n">
         <v>1.98</v>
@@ -2653,7 +2653,7 @@
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
@@ -2671,16 +2671,16 @@
         <v>1.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
         <v>1.66</v>
       </c>
       <c r="U9" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
         <v>2.02</v>
@@ -2689,16 +2689,16 @@
         <v>1.29</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
         <v>14.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB9" t="n">
         <v>21</v>
@@ -2719,40 +2719,40 @@
         <v>18</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ9" t="n">
         <v>900</v>
       </c>
       <c r="AK9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL9" t="n">
         <v>100</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>150</v>
       </c>
       <c r="AM9" t="n">
         <v>320</v>
       </c>
       <c r="AN9" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AO9" t="n">
         <v>9.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT9" t="n">
         <v>16.5</v>
@@ -2764,101 +2764,101 @@
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>14</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA9" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="BF9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG9" t="n">
         <v>8</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>4.8</v>
       </c>
       <c r="G10" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.33</v>
@@ -2931,16 +2931,16 @@
         <v>2.84</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
         <v>21</v>
@@ -2994,37 +2994,37 @@
         <v>75</v>
       </c>
       <c r="AO10" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AP10" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.9</v>
+        <v>15.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>15.5</v>
@@ -3033,22 +3033,22 @@
         <v>16</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH10" t="n">
         <v>4.1</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G11" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H11" t="n">
         <v>2.84</v>
       </c>
       <c r="I11" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
         <v>3.75</v>
@@ -3176,19 +3176,19 @@
         <v>2.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U11" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="V11" t="n">
         <v>1.51</v>
@@ -3197,19 +3197,19 @@
         <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB11" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AC11" t="n">
         <v>8.800000000000001</v>
@@ -3227,7 +3227,7 @@
         <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI11" t="n">
         <v>32</v>
@@ -3236,7 +3236,7 @@
         <v>40</v>
       </c>
       <c r="AK11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL11" t="n">
         <v>32</v>
@@ -3245,13 +3245,13 @@
         <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO11" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>15.5</v>
@@ -3260,10 +3260,10 @@
         <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AT11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU11" t="n">
         <v>7.8</v>
@@ -3275,19 +3275,19 @@
         <v>23</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.6</v>
+        <v>17</v>
       </c>
       <c r="AY11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA11" t="n">
         <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="BC11" t="n">
         <v>21</v>
@@ -3296,67 +3296,67 @@
         <v>26</v>
       </c>
       <c r="BE11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ11" t="n">
         <v>9</v>
       </c>
-      <c r="BH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -3403,13 +3403,13 @@
         <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
         <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
         <v>4.3</v>
@@ -3427,19 +3427,19 @@
         <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R12" t="n">
         <v>1.54</v>
       </c>
       <c r="S12" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U12" t="n">
         <v>2.36</v>
@@ -3451,16 +3451,16 @@
         <v>1.84</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z12" t="n">
         <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AB12" t="n">
         <v>13</v>
@@ -3481,13 +3481,13 @@
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
         <v>42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -3499,128 +3499,128 @@
         <v>200</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO12" t="n">
         <v>29</v>
       </c>
       <c r="AP12" t="n">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>14.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AV12" t="n">
         <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BA12" t="n">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
         <v>17</v>
       </c>
       <c r="BD12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP12" t="n">
         <v>15</v>
       </c>
-      <c r="BE12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="G13" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H13" t="n">
         <v>2.26</v>
       </c>
       <c r="I13" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
@@ -3669,109 +3669,109 @@
         <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P13" t="n">
         <v>2.48</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.58</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.59</v>
-      </c>
       <c r="S13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.48</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.64</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="W13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
         <v>500</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z13" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC13" t="n">
         <v>11</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AF13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH13" t="n">
         <v>16</v>
       </c>
-      <c r="AH13" t="n">
-        <v>22</v>
-      </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AJ13" t="n">
         <v>200</v>
       </c>
       <c r="AK13" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM13" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AP13" t="n">
         <v>5.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
         <v>5.6</v>
@@ -3780,19 +3780,19 @@
         <v>6.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
         <v>5.1</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB13" t="n">
         <v>5.6</v>
@@ -3810,13 +3810,13 @@
         <v>4.7</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH13" t="n">
         <v>4.7</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.4</v>
@@ -3834,7 +3834,7 @@
         <v>7</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="BP13" t="n">
         <v>22</v>
@@ -3852,7 +3852,7 @@
         <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="BV13" t="n">
         <v>18</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -3905,127 +3905,127 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="G14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
         <v>8.4</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K14" t="n">
         <v>5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="V14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z14" t="n">
-        <v>160</v>
+        <v>540</v>
       </c>
       <c r="AA14" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC14" t="n">
         <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE14" t="n">
         <v>240</v>
       </c>
       <c r="AF14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH14" t="n">
         <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>470</v>
+        <v>110</v>
       </c>
       <c r="AJ14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>390</v>
       </c>
       <c r="AN14" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AP14" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.5</v>
+        <v>40</v>
       </c>
       <c r="AS14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AU14" t="n">
         <v>10</v>
@@ -4034,10 +4034,10 @@
         <v>25</v>
       </c>
       <c r="AW14" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="AX14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY14" t="n">
         <v>8.6</v>
@@ -4046,7 +4046,7 @@
         <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.5</v>
+        <v>48</v>
       </c>
       <c r="BB14" t="n">
         <v>12</v>
@@ -4058,67 +4058,67 @@
         <v>29</v>
       </c>
       <c r="BE14" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BJ14" t="n">
         <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BL14" t="n">
         <v>150</v>
       </c>
       <c r="BM14" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BO14" t="n">
         <v>3.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="BR14" t="n">
         <v>27</v>
       </c>
       <c r="BS14" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BT14" t="n">
         <v>13</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV14" t="n">
         <v>75</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BX14" t="n">
         <v>75</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G15" t="n">
         <v>1.65</v>
@@ -4168,7 +4168,7 @@
         <v>6.6</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -4189,10 +4189,10 @@
         <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R15" t="n">
         <v>1.36</v>
@@ -4201,13 +4201,13 @@
         <v>3.55</v>
       </c>
       <c r="T15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U15" t="n">
         <v>1.94</v>
       </c>
       <c r="V15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
         <v>2.52</v>
@@ -4216,7 +4216,7 @@
         <v>15.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z15" t="n">
         <v>130</v>
@@ -4240,7 +4240,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AH15" t="n">
         <v>25</v>
@@ -4249,7 +4249,7 @@
         <v>700</v>
       </c>
       <c r="AJ15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK15" t="n">
         <v>19</v>
@@ -4267,16 +4267,16 @@
         <v>700</v>
       </c>
       <c r="AP15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ15" t="n">
         <v>18.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
         <v>6.6</v>
@@ -4288,7 +4288,7 @@
         <v>21</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX15" t="n">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BB15" t="n">
         <v>13</v>
@@ -4309,16 +4309,16 @@
         <v>15</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF15" t="n">
         <v>8.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH15" t="n">
         <v>3.95</v>
@@ -4327,10 +4327,10 @@
         <v>2.72</v>
       </c>
       <c r="BJ15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL15" t="n">
         <v>190</v>
@@ -4339,16 +4339,16 @@
         <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BP15" t="n">
         <v>13</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR15" t="n">
         <v>34</v>
@@ -4357,10 +4357,10 @@
         <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BV15" t="n">
         <v>75</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>6.8</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K16" t="n">
         <v>4.8</v>
@@ -4440,25 +4440,25 @@
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="Q16" t="n">
         <v>1.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T16" t="n">
         <v>1.66</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
         <v>1.17</v>
@@ -4470,13 +4470,13 @@
         <v>70</v>
       </c>
       <c r="Y16" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="Z16" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB16" t="n">
         <v>24</v>
@@ -4488,19 +4488,19 @@
         <v>75</v>
       </c>
       <c r="AE16" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AF16" t="n">
         <v>21</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH16" t="n">
         <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="AJ16" t="n">
         <v>500</v>
@@ -4512,25 +4512,25 @@
         <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN16" t="n">
         <v>6</v>
       </c>
       <c r="AO16" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AP16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
         <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -4539,40 +4539,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AZ16" t="n">
         <v>10.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC16" t="n">
         <v>12</v>
       </c>
       <c r="BD16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
         <v>5</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH16" t="n">
         <v>4.8</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G17" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I17" t="n">
         <v>3.5</v>
@@ -4694,13 +4694,13 @@
         <v>3.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P17" t="n">
         <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R17" t="n">
         <v>1.27</v>
@@ -4712,13 +4712,13 @@
         <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V17" t="n">
         <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X17" t="n">
         <v>12</v>
@@ -4727,7 +4727,7 @@
         <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
         <v>900</v>
@@ -4769,25 +4769,25 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AO17" t="n">
         <v>90</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS17" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AT17" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="AU17" t="n">
         <v>6.4</v>
@@ -4796,91 +4796,91 @@
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AX17" t="n">
         <v>12.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA17" t="n">
         <v>8.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
         <v>8.6</v>
       </c>
-      <c r="BH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
         <v>3.65</v>
@@ -4945,31 +4945,31 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
         <v>1.94</v>
@@ -4981,10 +4981,10 @@
         <v>16.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB18" t="n">
         <v>10</v>
@@ -4993,10 +4993,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AF18" t="n">
         <v>13</v>
@@ -5005,7 +5005,7 @@
         <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI18" t="n">
         <v>130</v>
@@ -5014,16 +5014,16 @@
         <v>24</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM18" t="n">
         <v>500</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>110</v>
@@ -5038,7 +5038,7 @@
         <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT18" t="n">
         <v>8.199999999999999</v>
@@ -5050,7 +5050,7 @@
         <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -5062,7 +5062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB18" t="n">
         <v>19</v>
@@ -5071,70 +5071,70 @@
         <v>17</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF18" t="n">
         <v>11.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>5.5</v>
       </c>
       <c r="I19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J19" t="n">
         <v>3.95</v>
@@ -5193,7 +5193,7 @@
         <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -5217,10 +5217,10 @@
         <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="V19" t="n">
         <v>1.2</v>
@@ -5289,7 +5289,7 @@
         <v>6.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS19" t="n">
         <v>3.6</v>
@@ -5304,7 +5304,7 @@
         <v>7</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="AX19" t="n">
         <v>5.6</v>
@@ -5313,19 +5313,19 @@
         <v>5.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="BB19" t="n">
         <v>6.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE19" t="n">
         <v>3.6</v>
@@ -5343,7 +5343,7 @@
         <v>2.76</v>
       </c>
       <c r="BJ19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK19" t="n">
         <v>7.8</v>
@@ -5355,28 +5355,28 @@
         <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BP19" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="BQ19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BR19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS19" t="n">
         <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV19" t="n">
         <v>60</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H20" t="n">
         <v>5.5</v>
@@ -5453,25 +5453,25 @@
         <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
         <v>1.71</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U20" t="n">
         <v>2.16</v>
@@ -5579,7 +5579,7 @@
         <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE20" t="n">
         <v>8.800000000000001</v>
@@ -5591,58 +5591,58 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5683,64 +5683,64 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G21" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H21" t="n">
         <v>4.9</v>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
         <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
         <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S21" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
         <v>1.84</v>
       </c>
       <c r="U21" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V21" t="n">
         <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z21" t="n">
         <v>120</v>
@@ -5749,7 +5749,7 @@
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC21" t="n">
         <v>9.199999999999999</v>
@@ -5758,10 +5758,10 @@
         <v>20</v>
       </c>
       <c r="AE21" t="n">
-        <v>320</v>
+        <v>190</v>
       </c>
       <c r="AF21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
@@ -5773,10 +5773,10 @@
         <v>320</v>
       </c>
       <c r="AJ21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL21" t="n">
         <v>95</v>
@@ -5788,7 +5788,7 @@
         <v>11</v>
       </c>
       <c r="AO21" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP21" t="n">
         <v>14</v>
@@ -5797,10 +5797,10 @@
         <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT21" t="n">
         <v>7.8</v>
@@ -5824,7 +5824,7 @@
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB21" t="n">
         <v>16.5</v>
@@ -5833,52 +5833,52 @@
         <v>16</v>
       </c>
       <c r="BD21" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ21" t="n">
         <v>10</v>
       </c>
       <c r="BK21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="BP21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR21" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT21" t="n">
         <v>8.6</v>
@@ -5890,13 +5890,13 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
         <v>12</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>12.5</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -5943,16 +5943,16 @@
         <v>2.84</v>
       </c>
       <c r="H22" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I22" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L22" t="n">
         <v>1.46</v>
@@ -5961,10 +5961,10 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P22" t="n">
         <v>1.8</v>
@@ -5985,7 +5985,7 @@
         <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
         <v>1.54</v>
@@ -6021,43 +6021,43 @@
         <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
         <v>55</v>
       </c>
       <c r="AJ22" t="n">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="AL22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AO22" t="n">
         <v>36</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR22" t="n">
         <v>15.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>8</v>
+        <v>18.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU22" t="n">
         <v>6.2</v>
@@ -6066,7 +6066,7 @@
         <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AX22" t="n">
         <v>15</v>
@@ -6084,22 +6084,22 @@
         <v>36</v>
       </c>
       <c r="BC22" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BD22" t="n">
         <v>40</v>
       </c>
       <c r="BE22" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="BF22" t="n">
         <v>7.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI22" t="n">
         <v>2.58</v>
@@ -6114,10 +6114,10 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN22" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO22" t="n">
         <v>4.9</v>
@@ -6132,7 +6132,7 @@
         <v>38</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT22" t="n">
         <v>6</v>
@@ -6150,7 +6150,7 @@
         <v>38</v>
       </c>
       <c r="BY22" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -6191,16 +6191,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G23" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J23" t="n">
         <v>4.4</v>
@@ -6221,16 +6221,16 @@
         <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R23" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S23" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="T23" t="n">
         <v>1.48</v>
@@ -6266,7 +6266,7 @@
         <v>19</v>
       </c>
       <c r="AE23" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AF23" t="n">
         <v>17</v>
@@ -6290,25 +6290,25 @@
         <v>23</v>
       </c>
       <c r="AM23" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="n">
         <v>6.4</v>
       </c>
       <c r="AO23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
         <v>13</v>
       </c>
       <c r="AR23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT23" t="n">
         <v>15</v>
@@ -6344,67 +6344,67 @@
         <v>19.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF23" t="n">
         <v>5.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL23" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -6448,16 +6448,16 @@
         <v>2.36</v>
       </c>
       <c r="G24" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H24" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="I24" t="n">
         <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K24" t="n">
         <v>4.2</v>
@@ -6469,115 +6469,115 @@
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R24" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S24" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U24" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="V24" t="n">
         <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X24" t="n">
         <v>29</v>
       </c>
       <c r="Y24" t="n">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="Z24" t="n">
         <v>26</v>
       </c>
       <c r="AA24" t="n">
-        <v>500</v>
+        <v>280</v>
       </c>
       <c r="AB24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
         <v>65</v>
       </c>
       <c r="AF24" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AG24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AJ24" t="n">
         <v>120</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL24" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AM24" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AN24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AQ24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS24" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AT24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW24" t="n">
         <v>14.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
         <v>14.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF24" t="n">
         <v>9.6</v>
@@ -6616,7 +6616,7 @@
         <v>9</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="G25" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="H25" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I25" t="n">
         <v>2.64</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.27</v>
@@ -6735,10 +6735,10 @@
         <v>1.53</v>
       </c>
       <c r="R25" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S25" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T25" t="n">
         <v>1.49</v>
@@ -6747,118 +6747,118 @@
         <v>2.66</v>
       </c>
       <c r="V25" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X25" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="Y25" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z25" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AA25" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AB25" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AD25" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AF25" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AG25" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AJ25" t="n">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AL25" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AM25" t="n">
-        <v>580</v>
+        <v>160</v>
       </c>
       <c r="AN25" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AO25" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.2</v>
+        <v>13</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2.18</v>
+        <v>14.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.16</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.89</v>
+        <v>16</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.3</v>
+        <v>15</v>
       </c>
       <c r="AU25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE25" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BF25" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH25" t="n">
         <v>4.7</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -6956,25 +6956,25 @@
         <v>1.75</v>
       </c>
       <c r="G26" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I26" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
         <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
         <v>1.25</v>
       </c>
       <c r="M26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N26" t="n">
         <v>6.2</v>
@@ -6986,187 +6986,187 @@
         <v>2.88</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R26" t="n">
         <v>1.75</v>
       </c>
       <c r="S26" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T26" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>2.6</v>
       </c>
       <c r="V26" t="n">
         <v>1.27</v>
       </c>
       <c r="W26" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X26" t="n">
         <v>500</v>
       </c>
       <c r="Y26" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="Z26" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AA26" t="n">
-        <v>900</v>
+        <v>470</v>
       </c>
       <c r="AB26" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AC26" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="AD26" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
         <v>500</v>
       </c>
       <c r="AF26" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AJ26" t="n">
-        <v>900</v>
+        <v>22</v>
       </c>
       <c r="AK26" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AM26" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.65</v>
+        <v>7.2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.63</v>
+        <v>21</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.65</v>
+        <v>28</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.66</v>
+        <v>8.4</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.58</v>
+        <v>5.9</v>
       </c>
       <c r="AU26" t="n">
         <v>5.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.65</v>
+        <v>15.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.66</v>
+        <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.58</v>
+        <v>7.6</v>
       </c>
       <c r="AY26" t="n">
-        <v>2.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.56</v>
+        <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.65</v>
+        <v>29</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.65</v>
+        <v>6.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.58</v>
+        <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.61</v>
+        <v>20</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.87</v>
+        <v>4.1</v>
       </c>
       <c r="BG26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH26" t="n">
         <v>5.1</v>
       </c>
-      <c r="BH26" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI26" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR26" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV26" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G27" t="n">
         <v>3.25</v>
       </c>
       <c r="H27" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I27" t="n">
         <v>2.28</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K27" t="n">
         <v>4.9</v>
@@ -7228,7 +7228,7 @@
         <v>1.21</v>
       </c>
       <c r="M27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
         <v>8.199999999999999</v>
@@ -7237,13 +7237,13 @@
         <v>1.11</v>
       </c>
       <c r="P27" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q27" t="n">
         <v>1.35</v>
       </c>
       <c r="R27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S27" t="n">
         <v>1.87</v>
@@ -7252,7 +7252,7 @@
         <v>1.39</v>
       </c>
       <c r="U27" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V27" t="n">
         <v>1.78</v>
@@ -7261,7 +7261,7 @@
         <v>1.45</v>
       </c>
       <c r="X27" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="Y27" t="n">
         <v>23</v>
@@ -7285,7 +7285,7 @@
         <v>19.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG27" t="n">
         <v>16</v>
@@ -7297,10 +7297,10 @@
         <v>23</v>
       </c>
       <c r="AJ27" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AK27" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AL27" t="n">
         <v>27</v>
@@ -7315,58 +7315,58 @@
         <v>7.6</v>
       </c>
       <c r="AP27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA27" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BB27" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD27" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH27" t="n">
         <v>5.8</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -7461,58 +7461,58 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H28" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I28" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K28" t="n">
-        <v>9.4</v>
+        <v>5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M28" t="n">
         <v>1.02</v>
       </c>
       <c r="N28" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O28" t="n">
         <v>1.1</v>
       </c>
       <c r="P28" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R28" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S28" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="T28" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U28" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="V28" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W28" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X28" t="n">
         <v>500</v>
@@ -7542,10 +7542,10 @@
         <v>500</v>
       </c>
       <c r="AG28" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH28" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AI28" t="n">
         <v>500</v>
@@ -7569,112 +7569,112 @@
         <v>55</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="AU28" t="n">
         <v>6.4</v>
       </c>
       <c r="AV28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE28" t="n">
         <v>4.7</v>
       </c>
-      <c r="AW28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX28" t="n">
+      <c r="BF28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
         <v>3.6</v>
       </c>
-      <c r="AY28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BN28" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT28" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.99</v>
+        <v>5</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -7721,73 +7721,73 @@
         <v>7.6</v>
       </c>
       <c r="H29" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="I29" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="J29" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O29" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P29" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="R29" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="S29" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="T29" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="U29" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="V29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="W29" t="n">
         <v>1.15</v>
       </c>
       <c r="X29" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="Y29" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="Z29" t="n">
         <v>23</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AB29" t="n">
         <v>160</v>
       </c>
       <c r="AC29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AD29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
         <v>15</v>
@@ -7802,7 +7802,7 @@
         <v>23</v>
       </c>
       <c r="AI29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ29" t="n">
         <v>200</v>
@@ -7814,16 +7814,16 @@
         <v>120</v>
       </c>
       <c r="AM29" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN29" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ29" t="n">
         <v>21</v>
@@ -7832,34 +7832,34 @@
         <v>15.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="AT29" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="AW29" t="n">
-        <v>11.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ29" t="n">
         <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>16.5</v>
+        <v>6</v>
       </c>
       <c r="BB29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC29" t="n">
         <v>7.2</v>
@@ -7871,22 +7871,22 @@
         <v>7</v>
       </c>
       <c r="BF29" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG29" t="n">
         <v>2.52</v>
       </c>
       <c r="BH29" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BI29" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
@@ -7895,50 +7895,50 @@
         <v>7.2</v>
       </c>
       <c r="BN29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BO29" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR29" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
         <v>6.6</v>
       </c>
       <c r="BT29" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BW29" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BX29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BY29" t="n">
         <v>5.3</v>
       </c>
       <c r="BZ29" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="CA29" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -7969,58 +7969,58 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G30" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="H30" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="I30" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="J30" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K30" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P30" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="R30" t="n">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="S30" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="T30" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="U30" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="V30" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W30" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X30" t="n">
         <v>500</v>
@@ -8032,7 +8032,7 @@
         <v>500</v>
       </c>
       <c r="AA30" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB30" t="n">
         <v>500</v>
@@ -8041,10 +8041,10 @@
         <v>500</v>
       </c>
       <c r="AD30" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE30" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AF30" t="n">
         <v>500</v>
@@ -8053,13 +8053,13 @@
         <v>500</v>
       </c>
       <c r="AH30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>500</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>900</v>
       </c>
       <c r="AK30" t="n">
         <v>500</v>
@@ -8068,67 +8068,67 @@
         <v>500</v>
       </c>
       <c r="AM30" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN30" t="n">
         <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.19</v>
+        <v>1.91</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.2</v>
+        <v>1.88</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.22</v>
+        <v>1.89</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.21</v>
+        <v>1.93</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.19</v>
+        <v>1.94</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.19</v>
+        <v>2.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.21</v>
+        <v>2.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.21</v>
+        <v>1.93</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.21</v>
+        <v>2.42</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.21</v>
+        <v>4.4</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.22</v>
+        <v>2.38</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.22</v>
+        <v>1.98</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.22</v>
+        <v>1.98</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.23</v>
+        <v>1.97</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.23</v>
+        <v>3.35</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8140,7 +8140,7 @@
         <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
@@ -8170,7 +8170,7 @@
         <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
@@ -8188,11 +8188,11 @@
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -8229,16 +8229,16 @@
         <v>2.26</v>
       </c>
       <c r="H31" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I31" t="n">
         <v>3.85</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L31" t="n">
         <v>1.35</v>
@@ -8247,7 +8247,7 @@
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O31" t="n">
         <v>1.25</v>
@@ -8256,16 +8256,16 @@
         <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R31" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S31" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T31" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U31" t="n">
         <v>2.3</v>
@@ -8385,68 +8385,68 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH31" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="BJ31" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN31" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP31" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BT31" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>
@@ -8477,10 +8477,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G32" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H32" t="n">
         <v>4.8</v>
@@ -8492,7 +8492,7 @@
         <v>3.3</v>
       </c>
       <c r="K32" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L32" t="n">
         <v>1.51</v>
@@ -8510,7 +8510,7 @@
         <v>1.67</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R32" t="n">
         <v>1.25</v>
@@ -8528,7 +8528,7 @@
         <v>1.25</v>
       </c>
       <c r="W32" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X32" t="n">
         <v>11</v>
@@ -8582,7 +8582,7 @@
         <v>21</v>
       </c>
       <c r="AO32" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AP32" t="n">
         <v>9.4</v>
@@ -8594,19 +8594,19 @@
         <v>27</v>
       </c>
       <c r="AS32" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU32" t="n">
         <v>6.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX32" t="n">
         <v>9.800000000000001</v>
@@ -8648,25 +8648,25 @@
         <v>11</v>
       </c>
       <c r="BK32" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN32" t="n">
         <v>4.5</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BP32" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ32" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR32" t="n">
         <v>36</v>
@@ -8678,7 +8678,7 @@
         <v>8</v>
       </c>
       <c r="BU32" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BV32" t="n">
         <v>46</v>
@@ -8687,7 +8687,7 @@
         <v>12</v>
       </c>
       <c r="BX32" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY32" t="n">
         <v>13</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-26 01:25:38</t>
+          <t>2026-06-26 03:41:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -866,7 +866,7 @@
         <v>2.38</v>
       </c>
       <c r="I2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J2" t="n">
         <v>3.95</v>
@@ -908,10 +908,10 @@
         <v>1.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
         <v>15.5</v>
@@ -938,16 +938,16 @@
         <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
         <v>28</v>
@@ -965,16 +965,16 @@
         <v>12.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
         <v>17</v>
       </c>
       <c r="AS2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT2" t="n">
         <v>16</v>
@@ -1016,71 +1016,71 @@
         <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM2" t="n">
-        <v>10.5</v>
+        <v>60</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BP2" t="n">
         <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BX2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>4.4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I3" t="n">
         <v>1.92</v>
@@ -1141,22 +1141,22 @@
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q3" t="n">
         <v>1.68</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
         <v>2.08</v>
@@ -1174,13 +1174,13 @@
         <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB3" t="n">
         <v>21</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
@@ -1189,7 +1189,7 @@
         <v>17.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AG3" t="n">
         <v>18</v>
@@ -1198,13 +1198,13 @@
         <v>17.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
         <v>65</v>
@@ -1213,7 +1213,7 @@
         <v>90</v>
       </c>
       <c r="AN3" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AO3" t="n">
         <v>9.6</v>
@@ -1231,7 +1231,7 @@
         <v>17.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU3" t="n">
         <v>8.4</v>
@@ -1252,13 +1252,13 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB3" t="n">
         <v>28</v>
       </c>
       <c r="BC3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD3" t="n">
         <v>34</v>
@@ -1276,10 +1276,10 @@
         <v>4.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK3" t="n">
         <v>6.6</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN3" t="n">
         <v>8.4</v>
@@ -1297,13 +1297,13 @@
         <v>5.8</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ3" t="n">
         <v>7.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS3" t="n">
         <v>8.199999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>5</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
         <v>24</v>
@@ -1327,14 +1327,14 @@
         <v>16</v>
       </c>
       <c r="BZ3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="G4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I4" t="n">
         <v>1.45</v>
@@ -1380,7 +1380,7 @@
         <v>5.2</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.28</v>
@@ -1389,31 +1389,31 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="T4" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U4" t="n">
         <v>2.04</v>
       </c>
       <c r="V4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
@@ -1422,7 +1422,7 @@
         <v>75</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
         <v>11.5</v>
@@ -1443,13 +1443,13 @@
         <v>17.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AG4" t="n">
         <v>40</v>
       </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI4" t="n">
         <v>42</v>
@@ -1461,7 +1461,7 @@
         <v>210</v>
       </c>
       <c r="AL4" t="n">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="AM4" t="n">
         <v>160</v>
@@ -1470,22 +1470,22 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AR4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT4" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AU4" t="n">
         <v>10</v>
@@ -1497,7 +1497,7 @@
         <v>10</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AY4" t="n">
         <v>13</v>
@@ -1509,13 +1509,13 @@
         <v>23</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.2</v>
+        <v>60</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BE4" t="n">
         <v>23</v>
@@ -1527,7 +1527,7 @@
         <v>4.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI4" t="n">
         <v>4</v>
@@ -1536,49 +1536,49 @@
         <v>13</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL4" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BN4" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="BP4" t="n">
         <v>75</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BR4" t="n">
         <v>70</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BU4" t="n">
         <v>3.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -1628,34 +1628,34 @@
         <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>4.7</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.2</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
         <v>6.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P5" t="n">
         <v>3.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S5" t="n">
         <v>1.95</v>
@@ -1667,7 +1667,7 @@
         <v>2.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
         <v>2.28</v>
@@ -1685,7 +1685,7 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC5" t="n">
         <v>42</v>
@@ -1697,10 +1697,10 @@
         <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
         <v>60</v>
@@ -1712,7 +1712,7 @@
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1727,16 +1727,16 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.94</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
         <v>7.8</v>
@@ -1748,7 +1748,7 @@
         <v>9.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AX5" t="n">
         <v>7.4</v>
@@ -1760,22 +1760,22 @@
         <v>7.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC5" t="n">
         <v>7</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BG5" t="n">
         <v>4.7</v>
@@ -1784,65 +1784,65 @@
         <v>5.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -1876,61 +1876,61 @@
         <v>1.73</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
         <v>5.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R6" t="n">
         <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
         <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="X6" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1951,10 +1951,10 @@
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AG6" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
         <v>500</v>
@@ -1981,64 +1981,64 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BF6" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG6" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="BH6" t="n">
         <v>3.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="BN6" t="n">
         <v>4.7</v>
@@ -2068,7 +2068,7 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
@@ -2080,13 +2080,13 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="G7" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.36</v>
@@ -2154,148 +2154,148 @@
         <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB7" t="n">
         <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF7" t="n">
         <v>15</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI7" t="n">
         <v>42</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AJ7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AG7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AO7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
         <v>23</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.5</v>
+        <v>50</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
         <v>34</v>
       </c>
       <c r="AX7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC7" t="n">
         <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE7" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BF7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="BH7" t="n">
         <v>4.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
         <v>1.01</v>
@@ -2307,28 +2307,28 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS7" t="n">
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>36</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -2384,10 +2384,10 @@
         <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H8" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I8" t="n">
         <v>3.2</v>
@@ -2408,46 +2408,46 @@
         <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
         <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
         <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V8" t="n">
         <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X8" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z8" t="n">
         <v>65</v>
       </c>
       <c r="AA8" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC8" t="n">
         <v>9.199999999999999</v>
@@ -2456,7 +2456,7 @@
         <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AF8" t="n">
         <v>18.5</v>
@@ -2465,16 +2465,16 @@
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI8" t="n">
         <v>42</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
@@ -2486,7 +2486,7 @@
         <v>14.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="AP8" t="n">
         <v>18</v>
@@ -2498,7 +2498,7 @@
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="AT8" t="n">
         <v>11.5</v>
@@ -2513,34 +2513,34 @@
         <v>23</v>
       </c>
       <c r="AX8" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY8" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BB8" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BC8" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
         <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BH8" t="n">
         <v>4.4</v>
@@ -2552,7 +2552,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2564,7 +2564,7 @@
         <v>5.9</v>
       </c>
       <c r="BO8" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BP8" t="n">
         <v>16.5</v>
@@ -2591,7 +2591,7 @@
         <v>7.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY8" t="n">
         <v>8.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>3.95</v>
       </c>
       <c r="G9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I9" t="n">
         <v>1.98</v>
@@ -2650,19 +2650,19 @@
         <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
         <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
         <v>2.38</v>
@@ -2671,31 +2671,31 @@
         <v>1.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
         <v>1.66</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
         <v>2.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
         <v>23</v>
@@ -2707,7 +2707,7 @@
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2716,10 +2716,10 @@
         <v>48</v>
       </c>
       <c r="AG9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
         <v>42</v>
@@ -2728,10 +2728,10 @@
         <v>900</v>
       </c>
       <c r="AK9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL9" t="n">
         <v>60</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>100</v>
       </c>
       <c r="AM9" t="n">
         <v>320</v>
@@ -2743,19 +2743,19 @@
         <v>9.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9" t="n">
         <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="n">
         <v>8.4</v>
@@ -2767,43 +2767,43 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY9" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="BA9" t="n">
         <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="BF9" t="n">
         <v>23</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK9" t="n">
         <v>4.9</v>
@@ -2815,13 +2815,13 @@
         <v>9.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ9" t="n">
         <v>8</v>
@@ -2830,13 +2830,13 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BV9" t="n">
         <v>13</v>
@@ -2851,14 +2851,14 @@
         <v>7.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA9" t="n">
         <v>6.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -2898,13 +2898,13 @@
         <v>1.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.33</v>
@@ -2919,25 +2919,25 @@
         <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R10" t="n">
         <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T10" t="n">
         <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="W10" t="n">
         <v>1.22</v>
@@ -2955,10 +2955,10 @@
         <v>18.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
         <v>12.5</v>
@@ -2967,13 +2967,13 @@
         <v>17.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG10" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
         <v>32</v>
@@ -2982,22 +2982,22 @@
         <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="AL10" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AO10" t="n">
         <v>9</v>
       </c>
       <c r="AP10" t="n">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10" t="n">
         <v>5.6</v>
@@ -3009,7 +3009,7 @@
         <v>15.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10" t="n">
         <v>8.6</v>
@@ -3021,7 +3021,7 @@
         <v>14.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="AY10" t="n">
         <v>17</v>
@@ -3033,19 +3033,19 @@
         <v>16</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG10" t="n">
         <v>7.6</v>
@@ -3057,7 +3057,7 @@
         <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK10" t="n">
         <v>5.4</v>
@@ -3072,37 +3072,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP10" t="n">
         <v>40</v>
       </c>
       <c r="BQ10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT10" t="n">
         <v>4.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BV10" t="n">
         <v>11.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX10" t="n">
         <v>24</v>
       </c>
       <c r="BY10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
         <v>17.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H11" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="I11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
@@ -3167,13 +3167,13 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
         <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q11" t="n">
         <v>1.65</v>
@@ -3182,46 +3182,46 @@
         <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="U11" t="n">
         <v>2.68</v>
       </c>
       <c r="V11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X11" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z11" t="n">
         <v>23</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>25</v>
       </c>
       <c r="AA11" t="n">
         <v>46</v>
       </c>
       <c r="AB11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
         <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF11" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
@@ -3230,79 +3230,79 @@
         <v>14</v>
       </c>
       <c r="AI11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM11" t="n">
         <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR11" t="n">
         <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AT11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC11" t="n">
         <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE11" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BF11" t="n">
         <v>13</v>
       </c>
       <c r="BG11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH11" t="n">
         <v>4.3</v>
@@ -3314,49 +3314,49 @@
         <v>9</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO11" t="n">
         <v>5.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT11" t="n">
         <v>6.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -3406,13 +3406,13 @@
         <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.31</v>
@@ -3421,13 +3421,13 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
         <v>1.65</v>
@@ -3439,28 +3439,28 @@
         <v>2.64</v>
       </c>
       <c r="T12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U12" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
         <v>1.84</v>
       </c>
       <c r="X12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA12" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
         <v>13</v>
@@ -3484,10 +3484,10 @@
         <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -3502,10 +3502,10 @@
         <v>12.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="AQ12" t="n">
         <v>14.5</v>
@@ -3517,16 +3517,16 @@
         <v>7.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AV12" t="n">
         <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AX12" t="n">
         <v>6.2</v>
@@ -3535,37 +3535,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC12" t="n">
         <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BG12" t="n">
         <v>6.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK12" t="n">
         <v>6.8</v>
@@ -3577,10 +3577,10 @@
         <v>8.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP12" t="n">
         <v>15</v>
@@ -3595,13 +3595,13 @@
         <v>6.8</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU12" t="n">
         <v>6</v>
       </c>
       <c r="BV12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW12" t="n">
         <v>7</v>
@@ -3613,14 +3613,14 @@
         <v>7.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G13" t="n">
         <v>3.05</v>
@@ -3663,10 +3663,10 @@
         <v>2.56</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -3678,7 +3678,7 @@
         <v>5.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P13" t="n">
         <v>2.48</v>
@@ -3699,31 +3699,31 @@
         <v>2.48</v>
       </c>
       <c r="V13" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
         <v>500</v>
       </c>
       <c r="Y13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z13" t="n">
         <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="n">
         <v>22</v>
       </c>
       <c r="AC13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -3732,7 +3732,7 @@
         <v>30</v>
       </c>
       <c r="AG13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH13" t="n">
         <v>16</v>
@@ -3741,25 +3741,25 @@
         <v>36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="AK13" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AM13" t="n">
         <v>200</v>
       </c>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ13" t="n">
         <v>8.4</v>
@@ -3768,7 +3768,7 @@
         <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
@@ -3780,10 +3780,10 @@
         <v>6.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AY13" t="n">
         <v>7.6</v>
@@ -3792,55 +3792,55 @@
         <v>8.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BE13" t="n">
         <v>5.7</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH13" t="n">
         <v>4.7</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BN13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO13" t="n">
         <v>4.1</v>
       </c>
       <c r="BP13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3849,22 +3849,22 @@
         <v>5.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BV13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BW13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>18.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="H14" t="n">
         <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.36</v>
@@ -3935,61 +3935,61 @@
         <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
         <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Z14" t="n">
-        <v>540</v>
+        <v>70</v>
       </c>
       <c r="AA14" t="n">
         <v>280</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE14" t="n">
         <v>240</v>
       </c>
       <c r="AF14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG14" t="n">
         <v>9.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
         <v>110</v>
@@ -4007,7 +4007,7 @@
         <v>390</v>
       </c>
       <c r="AN14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO14" t="n">
         <v>160</v>
@@ -4016,16 +4016,16 @@
         <v>16.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
         <v>40</v>
       </c>
       <c r="AS14" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU14" t="n">
         <v>10</v>
@@ -4037,7 +4037,7 @@
         <v>29</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
         <v>8.6</v>
@@ -4046,79 +4046,79 @@
         <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="BB14" t="n">
         <v>12</v>
       </c>
       <c r="BC14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BH14" t="n">
         <v>3.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BL14" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BM14" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP14" t="n">
         <v>9</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BR14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BT14" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW14" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BX14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY14" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.61</v>
       </c>
       <c r="G15" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="H15" t="n">
         <v>6.6</v>
@@ -4171,10 +4171,10 @@
         <v>7.2</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.41</v>
@@ -4183,13 +4183,13 @@
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
         <v>1.98</v>
@@ -4201,16 +4201,16 @@
         <v>3.55</v>
       </c>
       <c r="T15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="V15" t="n">
         <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="X15" t="n">
         <v>15.5</v>
@@ -4228,16 +4228,16 @@
         <v>8</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
         <v>27</v>
       </c>
       <c r="AE15" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG15" t="n">
         <v>9.6</v>
@@ -4276,22 +4276,22 @@
         <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV15" t="n">
         <v>21</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY15" t="n">
         <v>8.199999999999999</v>
@@ -4306,28 +4306,28 @@
         <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BJ15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK15" t="n">
         <v>8.4</v>
@@ -4345,31 +4345,31 @@
         <v>3.55</v>
       </c>
       <c r="BP15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR15" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BS15" t="n">
         <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BV15" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BW15" t="n">
         <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BY15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -4413,25 +4413,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="G16" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="H16" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="I16" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K16" t="n">
         <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
@@ -4440,193 +4440,193 @@
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P16" t="n">
         <v>2.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S16" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="X16" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="Y16" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="Z16" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
         <v>700</v>
       </c>
       <c r="AB16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>300</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP16" t="n">
         <v>24</v>
       </c>
-      <c r="AC16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AQ16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ16" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AH16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>10</v>
-      </c>
       <c r="BK16" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP16" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BQ16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU16" t="n">
         <v>4.9</v>
       </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -4670,16 +4670,16 @@
         <v>2.38</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H17" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I17" t="n">
         <v>3.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
         <v>3.5</v>
@@ -4691,49 +4691,49 @@
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
         <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R17" t="n">
         <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
         <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V17" t="n">
         <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y17" t="n">
         <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC17" t="n">
         <v>7.8</v>
@@ -4742,7 +4742,7 @@
         <v>15.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AF17" t="n">
         <v>15.5</v>
@@ -4754,13 +4754,13 @@
         <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AJ17" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AK17" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AL17" t="n">
         <v>50</v>
@@ -4769,31 +4769,31 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AO17" t="n">
         <v>90</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AR17" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AU17" t="n">
         <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
         <v>38</v>
@@ -4802,43 +4802,43 @@
         <v>12.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="BC17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.4</v>
+        <v>19.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="BH17" t="n">
         <v>3.15</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4847,40 +4847,40 @@
         <v>10</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
         <v>6.8</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV17" t="n">
         <v>32</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -4924,70 +4924,70 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.3</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
         <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC18" t="n">
         <v>8.800000000000001</v>
@@ -4996,7 +4996,7 @@
         <v>17.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AF18" t="n">
         <v>13</v>
@@ -5005,10 +5005,10 @@
         <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI18" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
         <v>24</v>
@@ -5017,79 +5017,79 @@
         <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM18" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AP18" t="n">
         <v>13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AS18" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV18" t="n">
         <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AX18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="BB18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
         <v>17</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BE18" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG18" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK18" t="n">
         <v>5.1</v>
@@ -5098,40 +5098,40 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ18" t="n">
         <v>6.2</v>
       </c>
       <c r="BR18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BS18" t="n">
         <v>7.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU18" t="n">
         <v>5.8</v>
       </c>
       <c r="BV18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW18" t="n">
         <v>8</v>
       </c>
       <c r="BX18" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BY18" t="n">
         <v>8.4</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G19" t="n">
         <v>1.75</v>
       </c>
       <c r="H19" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
         <v>3.95</v>
@@ -5193,34 +5193,34 @@
         <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U19" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
         <v>1.2</v>
@@ -5229,13 +5229,13 @@
         <v>2.32</v>
       </c>
       <c r="X19" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y19" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="Z19" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AA19" t="n">
         <v>900</v>
@@ -5247,28 +5247,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AE19" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AF19" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AJ19" t="n">
-        <v>900</v>
+        <v>20</v>
       </c>
       <c r="AK19" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>500</v>
@@ -5277,79 +5277,79 @@
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="AP19" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.6</v>
+        <v>15.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.4</v>
+        <v>19.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.55</v>
+        <v>28</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.55</v>
+        <v>46</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BC19" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BJ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK19" t="n">
         <v>7.8</v>
       </c>
       <c r="BL19" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM19" t="n">
         <v>1.01</v>
@@ -5385,7 +5385,7 @@
         <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -5429,52 +5429,52 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G20" t="n">
         <v>1.68</v>
       </c>
       <c r="H20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I20" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K20" t="n">
         <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
         <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U20" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
         <v>1.2</v>
@@ -5483,46 +5483,46 @@
         <v>2.46</v>
       </c>
       <c r="X20" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="Y20" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="Z20" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AA20" t="n">
         <v>700</v>
       </c>
       <c r="AB20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC20" t="n">
         <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AE20" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
         <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AJ20" t="n">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
         <v>500</v>
@@ -5531,34 +5531,34 @@
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO20" t="n">
         <v>700</v>
       </c>
       <c r="AP20" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="AS20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT20" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>9</v>
       </c>
       <c r="AU20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.6</v>
+        <v>46</v>
       </c>
       <c r="AX20" t="n">
         <v>9.6</v>
@@ -5567,58 +5567,58 @@
         <v>8.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BC20" t="n">
         <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="BJ20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>2.84</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BP20" t="n">
         <v>11</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
@@ -5627,7 +5627,7 @@
         <v>7</v>
       </c>
       <c r="BT20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU20" t="n">
         <v>4.9</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
         <v>1.8</v>
       </c>
       <c r="H21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
         <v>5.4</v>
@@ -5710,25 +5710,25 @@
         <v>4.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P21" t="n">
         <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
         <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
         <v>1.23</v>
@@ -5743,13 +5743,13 @@
         <v>18.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AA21" t="n">
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC21" t="n">
         <v>9.199999999999999</v>
@@ -5758,34 +5758,34 @@
         <v>20</v>
       </c>
       <c r="AE21" t="n">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AF21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>320</v>
+        <v>85</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK21" t="n">
         <v>18</v>
       </c>
       <c r="AL21" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AM21" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="AN21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO21" t="n">
         <v>90</v>
@@ -5797,13 +5797,13 @@
         <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AS21" t="n">
         <v>13.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU21" t="n">
         <v>8.199999999999999</v>
@@ -5812,10 +5812,10 @@
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY21" t="n">
         <v>9</v>
@@ -5824,7 +5824,7 @@
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>12.5</v>
+        <v>44</v>
       </c>
       <c r="BB21" t="n">
         <v>16.5</v>
@@ -5833,7 +5833,7 @@
         <v>16</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BE21" t="n">
         <v>13</v>
@@ -5842,13 +5842,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG21" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ21" t="n">
         <v>10</v>
@@ -5884,7 +5884,7 @@
         <v>8.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -5937,19 +5937,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="G22" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="H22" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
         <v>3.45</v>
@@ -5961,49 +5961,49 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
         <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="X22" t="n">
         <v>12.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC22" t="n">
         <v>7.6</v>
@@ -6015,7 +6015,7 @@
         <v>38</v>
       </c>
       <c r="AF22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG22" t="n">
         <v>13</v>
@@ -6024,43 +6024,43 @@
         <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ22" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AK22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO22" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AP22" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AS22" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV22" t="n">
         <v>11</v>
@@ -6081,10 +6081,10 @@
         <v>40</v>
       </c>
       <c r="BB22" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BC22" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BD22" t="n">
         <v>40</v>
@@ -6093,37 +6093,37 @@
         <v>29</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ22" t="n">
         <v>10</v>
       </c>
       <c r="BK22" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL22" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM22" t="n">
         <v>11</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BO22" t="n">
         <v>4.9</v>
       </c>
       <c r="BP22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ22" t="n">
         <v>15.5</v>
@@ -6132,10 +6132,10 @@
         <v>38</v>
       </c>
       <c r="BS22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU22" t="n">
         <v>5</v>
@@ -6147,7 +6147,7 @@
         <v>16</v>
       </c>
       <c r="BX22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY22" t="n">
         <v>9.199999999999999</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G23" t="n">
         <v>1.88</v>
@@ -6215,22 +6215,22 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R23" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T23" t="n">
         <v>1.48</v>
@@ -6248,13 +6248,13 @@
         <v>36</v>
       </c>
       <c r="Y23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z23" t="n">
         <v>42</v>
       </c>
       <c r="AA23" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AB23" t="n">
         <v>17</v>
@@ -6266,7 +6266,7 @@
         <v>19</v>
       </c>
       <c r="AE23" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AF23" t="n">
         <v>17</v>
@@ -6278,7 +6278,7 @@
         <v>15</v>
       </c>
       <c r="AI23" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AJ23" t="n">
         <v>22</v>
@@ -6290,34 +6290,34 @@
         <v>23</v>
       </c>
       <c r="AM23" t="n">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="AN23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP23" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AR23" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AS23" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="AT23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU23" t="n">
         <v>10.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AW23" t="n">
         <v>32</v>
@@ -6344,7 +6344,7 @@
         <v>19.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BF23" t="n">
         <v>5.7</v>
@@ -6362,10 +6362,10 @@
         <v>8.6</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL23" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM23" t="n">
         <v>11</v>
@@ -6374,13 +6374,13 @@
         <v>5.3</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BP23" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR23" t="n">
         <v>19</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -6445,139 +6445,139 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G24" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H24" t="n">
         <v>2.88</v>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P24" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="T24" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U24" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y24" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z24" t="n">
         <v>28</v>
       </c>
-      <c r="Z24" t="n">
-        <v>26</v>
-      </c>
       <c r="AA24" t="n">
-        <v>280</v>
+        <v>55</v>
       </c>
       <c r="AB24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD24" t="n">
         <v>15</v>
       </c>
       <c r="AE24" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AF24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG24" t="n">
         <v>13</v>
       </c>
       <c r="AH24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO24" t="n">
         <v>16</v>
       </c>
-      <c r="AI24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>18</v>
-      </c>
       <c r="AP24" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR24" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="AT24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AX24" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
@@ -6586,79 +6586,79 @@
         <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BB24" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="BC24" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.8</v>
+        <v>38</v>
       </c>
       <c r="BF24" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH24" t="n">
         <v>4.9</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BJ24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN24" t="n">
         <v>6.2</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BR24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS24" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT24" t="n">
         <v>7</v>
       </c>
       <c r="BU24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV24" t="n">
         <v>21</v>
       </c>
       <c r="BW24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY24" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -6699,16 +6699,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G25" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H25" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I25" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J25" t="n">
         <v>3.9</v>
@@ -6735,22 +6735,22 @@
         <v>1.53</v>
       </c>
       <c r="R25" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S25" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T25" t="n">
         <v>1.49</v>
       </c>
       <c r="U25" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V25" t="n">
         <v>1.6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X25" t="n">
         <v>28</v>
@@ -6783,10 +6783,10 @@
         <v>13.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ25" t="n">
         <v>100</v>
@@ -6795,16 +6795,16 @@
         <v>26</v>
       </c>
       <c r="AL25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM25" t="n">
         <v>160</v>
       </c>
       <c r="AN25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP25" t="n">
         <v>13</v>
@@ -6843,7 +6843,7 @@
         <v>14.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BC25" t="n">
         <v>21</v>
@@ -6852,7 +6852,7 @@
         <v>14.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF25" t="n">
         <v>12</v>
@@ -6861,22 +6861,22 @@
         <v>11</v>
       </c>
       <c r="BH25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ25" t="n">
         <v>8.6</v>
       </c>
       <c r="BK25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN25" t="n">
         <v>6.6</v>
@@ -6888,19 +6888,19 @@
         <v>18.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR25" t="n">
         <v>25</v>
       </c>
       <c r="BS25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT25" t="n">
         <v>6.4</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV25" t="n">
         <v>17.5</v>
@@ -6912,7 +6912,7 @@
         <v>24</v>
       </c>
       <c r="BY25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -6959,16 +6959,16 @@
         <v>1.87</v>
       </c>
       <c r="H26" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>4.7</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.25</v>
@@ -6977,22 +6977,22 @@
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R26" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S26" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T26" t="n">
         <v>1.51</v>
@@ -7004,7 +7004,7 @@
         <v>1.27</v>
       </c>
       <c r="W26" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X26" t="n">
         <v>500</v>
@@ -7028,7 +7028,7 @@
         <v>19</v>
       </c>
       <c r="AE26" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AF26" t="n">
         <v>16</v>
@@ -7046,22 +7046,22 @@
         <v>22</v>
       </c>
       <c r="AK26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL26" t="n">
         <v>26</v>
       </c>
       <c r="AM26" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN26" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>40</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ26" t="n">
         <v>21</v>
@@ -7070,10 +7070,10 @@
         <v>28</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU26" t="n">
         <v>5.8</v>
@@ -7097,7 +7097,7 @@
         <v>29</v>
       </c>
       <c r="BB26" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC26" t="n">
         <v>14</v>
@@ -7106,10 +7106,10 @@
         <v>20</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BG26" t="n">
         <v>9.199999999999999</v>
@@ -7124,7 +7124,7 @@
         <v>9</v>
       </c>
       <c r="BK26" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
@@ -7136,7 +7136,7 @@
         <v>5.3</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP26" t="n">
         <v>12</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G27" t="n">
         <v>3.25</v>
@@ -7219,127 +7219,127 @@
         <v>2.28</v>
       </c>
       <c r="J27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P27" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="R27" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="S27" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="T27" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="U27" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="V27" t="n">
         <v>1.78</v>
       </c>
       <c r="W27" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>90</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>200</v>
       </c>
-      <c r="Y27" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH27" t="n">
+      <c r="AK27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN27" t="n">
         <v>14.5</v>
       </c>
-      <c r="AI27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AO27" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR27" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AT27" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AU27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX27" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>16</v>
       </c>
       <c r="AY27" t="n">
         <v>6.6</v>
@@ -7348,31 +7348,31 @@
         <v>12</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB27" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH27" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BJ27" t="n">
         <v>8.199999999999999</v>
@@ -7384,13 +7384,13 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN27" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO27" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP27" t="n">
         <v>20</v>
@@ -7399,10 +7399,10 @@
         <v>7.8</v>
       </c>
       <c r="BR27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS27" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT27" t="n">
         <v>6.2</v>
@@ -7417,20 +7417,20 @@
         <v>6.6</v>
       </c>
       <c r="BX27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BY27" t="n">
         <v>7.6</v>
       </c>
       <c r="BZ27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CA27" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -7461,211 +7461,211 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G28" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H28" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I28" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L28" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M28" t="n">
         <v>1.02</v>
       </c>
       <c r="N28" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P28" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="R28" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S28" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="T28" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="U28" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W28" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X28" t="n">
         <v>500</v>
       </c>
       <c r="Y28" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="Z28" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AA28" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AB28" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AC28" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="AD28" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AF28" t="n">
         <v>500</v>
       </c>
       <c r="AG28" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AI28" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AJ28" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK28" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AL28" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN28" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="AO28" t="n">
-        <v>55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.4</v>
+        <v>17.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.4</v>
+        <v>19</v>
       </c>
       <c r="AS28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG28" t="n">
         <v>7</v>
       </c>
-      <c r="AT28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF28" t="n">
+      <c r="BH28" t="n">
         <v>5.9</v>
       </c>
-      <c r="BG28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BI28" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BJ28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP28" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ28" t="n">
         <v>7.8</v>
       </c>
       <c r="BR28" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT28" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BV28" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW28" t="n">
         <v>7</v>
@@ -7674,17 +7674,17 @@
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ28" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA28" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="H29" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="I29" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="J29" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="K29" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
         <v>1.12</v>
@@ -7745,40 +7745,40 @@
         <v>1.05</v>
       </c>
       <c r="P29" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R29" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S29" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T29" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="U29" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="V29" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="W29" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="X29" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="Y29" t="n">
         <v>34</v>
       </c>
       <c r="Z29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA29" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AB29" t="n">
         <v>160</v>
@@ -7790,22 +7790,22 @@
         <v>15</v>
       </c>
       <c r="AE29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF29" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AG29" t="n">
         <v>75</v>
       </c>
       <c r="AH29" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AJ29" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AK29" t="n">
         <v>170</v>
@@ -7814,79 +7814,79 @@
         <v>120</v>
       </c>
       <c r="AM29" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO29" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AP29" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AQ29" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
-        <v>15.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.9</v>
+        <v>17.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC29" t="n">
         <v>6.6</v>
       </c>
-      <c r="AZ29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD29" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="BH29" t="n">
         <v>9.4</v>
       </c>
       <c r="BI29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BJ29" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
@@ -7895,34 +7895,34 @@
         <v>7.2</v>
       </c>
       <c r="BN29" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BO29" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR29" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV29" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BW29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX29" t="n">
         <v>14</v>
@@ -7931,14 +7931,14 @@
         <v>5.3</v>
       </c>
       <c r="BZ29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="CA29" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -7972,10 +7972,10 @@
         <v>3.3</v>
       </c>
       <c r="G30" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H30" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I30" t="n">
         <v>1.96</v>
@@ -7987,7 +7987,7 @@
         <v>7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
@@ -7999,7 +7999,7 @@
         <v>1.05</v>
       </c>
       <c r="P30" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q30" t="n">
         <v>1.16</v>
@@ -8008,7 +8008,7 @@
         <v>2.96</v>
       </c>
       <c r="S30" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T30" t="n">
         <v>1.24</v>
@@ -8020,7 +8020,7 @@
         <v>2.04</v>
       </c>
       <c r="W30" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X30" t="n">
         <v>500</v>
@@ -8086,13 +8086,13 @@
         <v>1.88</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AV30" t="n">
         <v>2.5</v>
@@ -8101,16 +8101,16 @@
         <v>2.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AY30" t="n">
-        <v>2.42</v>
+        <v>6</v>
       </c>
       <c r="AZ30" t="n">
         <v>4.4</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BB30" t="n">
         <v>1.98</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -8223,64 +8223,64 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G31" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J31" t="n">
         <v>3.35</v>
       </c>
-      <c r="I31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K31" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="L31" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M31" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="O31" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="P31" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="R31" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="S31" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="T31" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="U31" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="V31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X31" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="Y31" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="Z31" t="n">
         <v>500</v>
@@ -8289,67 +8289,67 @@
         <v>900</v>
       </c>
       <c r="AB31" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD31" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
         <v>90</v>
       </c>
       <c r="AF31" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AI31" t="n">
         <v>500</v>
       </c>
       <c r="AJ31" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AK31" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AL31" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AM31" t="n">
         <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AP31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT31" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>10</v>
-      </c>
       <c r="AU31" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW31" t="n">
         <v>16</v>
@@ -8358,95 +8358,95 @@
         <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB31" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>8.4</v>
       </c>
       <c r="BC31" t="n">
         <v>10.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="BE31" t="n">
         <v>8.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BH31" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="BI31" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="BJ31" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK31" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BN31" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO31" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP31" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ31" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BT31" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU31" t="n">
         <v>5.2</v>
       </c>
       <c r="BV31" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="G32" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="H32" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L32" t="n">
         <v>1.51</v>
@@ -8501,13 +8501,13 @@
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
         <v>1.45</v>
       </c>
       <c r="P32" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q32" t="n">
         <v>2.38</v>
@@ -8522,185 +8522,185 @@
         <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V32" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W32" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="X32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG32" t="n">
         <v>11</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>480</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>10.5</v>
       </c>
       <c r="AH32" t="n">
         <v>22</v>
       </c>
       <c r="AI32" t="n">
-        <v>450</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL32" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM32" t="n">
         <v>580</v>
       </c>
       <c r="AN32" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO32" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AP32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY32" t="n">
         <v>9.4</v>
       </c>
-      <c r="AQ32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW32" t="n">
+      <c r="AZ32" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA32" t="n">
         <v>14.5</v>
       </c>
-      <c r="AX32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ32" t="n">
+      <c r="BB32" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF32" t="n">
         <v>19.5</v>
       </c>
-      <c r="BA32" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BG32" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ32" t="n">
         <v>11</v>
       </c>
       <c r="BK32" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN32" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BO32" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP32" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BQ32" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR32" t="n">
         <v>36</v>
       </c>
       <c r="BS32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT32" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BU32" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV32" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BW32" t="n">
         <v>12</v>
       </c>
       <c r="BX32" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY32" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ32" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-26 03:41:56</t>
+          <t>2026-06-26 05:58:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-26.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H2" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="I2" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.95</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>1.3</v>
@@ -881,43 +881,43 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="R2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="T2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
         <v>34</v>
@@ -926,10 +926,10 @@
         <v>18.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
         <v>22</v>
@@ -938,28 +938,28 @@
         <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI2" t="n">
         <v>28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL2" t="n">
         <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
         <v>12.5</v>
@@ -968,7 +968,7 @@
         <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR2" t="n">
         <v>17</v>
@@ -977,13 +977,13 @@
         <v>30</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
         <v>19.5</v>
@@ -992,10 +992,10 @@
         <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
         <v>25</v>
@@ -1007,19 +1007,19 @@
         <v>25</v>
       </c>
       <c r="BD2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
         <v>48</v>
       </c>
       <c r="BF2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI2" t="n">
         <v>4</v>
@@ -1028,7 +1028,7 @@
         <v>8.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL2" t="n">
         <v>75</v>
@@ -1037,22 +1037,22 @@
         <v>60</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BP2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS2" t="n">
         <v>21</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>11.5</v>
       </c>
       <c r="BT2" t="n">
         <v>5.6</v>
@@ -1064,23 +1064,23 @@
         <v>15.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BZ2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>4.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I3" t="n">
         <v>1.92</v>
@@ -1129,34 +1129,34 @@
         <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="R3" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V3" t="n">
         <v>2.08</v>
@@ -1165,10 +1165,10 @@
         <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
         <v>14</v>
@@ -1177,25 +1177,25 @@
         <v>22</v>
       </c>
       <c r="AB3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AG3" t="n">
         <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI3" t="n">
         <v>40</v>
@@ -1207,49 +1207,49 @@
         <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP3" t="n">
         <v>18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
         <v>17.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY3" t="n">
         <v>15</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
         <v>23</v>
@@ -1264,19 +1264,19 @@
         <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BG3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.4</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN3" t="n">
         <v>8.4</v>
@@ -1300,41 +1300,41 @@
         <v>34</v>
       </c>
       <c r="BQ3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>7.8</v>
       </c>
-      <c r="BR3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BT3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU3" t="n">
         <v>4.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BW3" t="n">
         <v>8.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY3" t="n">
         <v>16</v>
       </c>
       <c r="BZ3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA3" t="n">
         <v>12</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-26 05:58:53</t>
+          <t>2026-06-26 08:16:17</t>
         </is>
       </c>
     </row>
@@ -1368,64 +1368,64 @@
         <v>7.8</v>
       </c>
       <c r="G4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I4" t="n">
         <v>1.42</v>
       </c>
-      <c r="I4" t="n">
-        <v>1.45</v>
-      </c>
       <c r="J4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="R4" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="S4" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="T4" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="Y4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z4" t="n">
         <v>12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>11.5</v>
       </c>
       <c r="AA4" t="n">
         <v>15</v>
@@ -1434,25 +1434,25 @@
         <v>85</v>
       </c>
       <c r="AC4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AD4" t="n">
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AH4" t="n">
         <v>27</v>
       </c>
       <c r="AI4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
         <v>310</v>
@@ -1464,37 +1464,37 @@
         <v>240</v>
       </c>
       <c r="AM4" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN4" t="n">
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AP4" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV4" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AW4" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX4" t="n">
         <v>8.6</v>
@@ -1503,34 +1503,34 @@
         <v>13</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA4" t="n">
         <v>23</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BE4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BF4" t="n">
         <v>15</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ4" t="